--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R254bd48bb93346d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R60d9e2b4f2bc4ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R37b3ae9634934600"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra09084e770f2453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R024cc5533e0d4a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0b7dc1fb380a4e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R507b7c9817a64b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rab8e33ca493b454f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3e9b3d41434ac1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b4eda58df98492c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6119,7 +6119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R180ce137ee1a457a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf09f94751f84ee6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12363,7 +12363,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30d0142cd8d74cb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca02457f42304c03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7770067fd4474c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R26d0a03999ad4a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4f772c1d88a343fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfada0db65444473d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R233a0ac593814c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3746bdf677584d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rfeb421f28c514ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra8e0413f236b47dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
+        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
+        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3eba1931d0d43b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa14e577b764da2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6119,7 +6119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb4ed4f5a1642f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33c0081fac674b11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13467,7 +13467,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R362f73a762f04302"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09b00d028a3444f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0cedef8026044fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8d30074b1f0543d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc0b9ae05d9104e9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R89eaf0aae9a34e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Redff05a6dbb84d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9151886b23134ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R962d956fcb1942b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd6524ad6061e418a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
+        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
+        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a89057441ac44b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15667c8c01704267"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6117,7 +6117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ea637c11f1c419a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ad59a07d4034414"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13657,7 +13657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dae9b6acd4a4183"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1000ddd2e0a3474a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Redff05a6dbb84d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9151886b23134ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R962d956fcb1942b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd6524ad6061e418a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9b8f4ee0dcfb42a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd9c111689d5f4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcee3f43e61b5417d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R08b996ef9b0d4d5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
+        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
+        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15667c8c01704267"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad4f7b05596405c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6117,7 +6117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ad59a07d4034414"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d05df4960546e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13657,7 +13657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1000ddd2e0a3474a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cccce2af4dc439f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9b8f4ee0dcfb42a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd9c111689d5f4ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rcee3f43e61b5417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R08b996ef9b0d4d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R85e0e89779e44e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8729b63cf4e54d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6a6a5e2bb6654867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R92339543a18a4c9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
+        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
+        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad4f7b05596405c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fa480dc72c4849"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6117,7 +6117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d05df4960546e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0993fcbf32264b99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13657,7 +13657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cccce2af4dc439f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b0a15715fd74111"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R85e0e89779e44e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8729b63cf4e54d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6a6a5e2bb6654867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R92339543a18a4c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc0dc39a4aaf04bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb8531ab2cf044a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R62ea98d6a7af4595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2f40127ddacc46ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
+        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3177,7 +3177,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67fa480dc72c4849"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c731e864a64ca9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6117,7 +6117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0993fcbf32264b99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re349f2b7377a47cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13657,7 +13657,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b0a15715fd74111"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97240a61f74444f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc0dc39a4aaf04bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb8531ab2cf044a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R62ea98d6a7af4595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2f40127ddacc46ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf1a2005141dc4ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6eee1d4c752b4ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rda53799242144659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Red4d9f342c714eff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -487,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
+        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
+        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3177,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c731e864a64ca9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra838ec4e70b9457c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3475,7 +3481,7 @@
       </x:c>
       <x:c r="I7" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A7,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>61.27413031117918</x:v>
+        <x:v>65.21813031117918</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -3534,14 +3540,14 @@
       </x:c>
       <x:c r="I8" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A8,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
-        <x:v>61.27413031117918</x:v>
+        <x:v>65.21813031117918</x:v>
       </x:c>
       <x:c r="K8" s="11" t="n">
         <x:f>IF(L8="Full home run",I8+J8,"")</x:f>
-        <x:v>63.80813031117918</x:v>
+        <x:v>67.60813031117918</x:v>
       </x:c>
       <x:c r="L8" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3598,14 +3604,14 @@
       </x:c>
       <x:c r="I9" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A9,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
-        <x:v>56.77413031117918</x:v>
+        <x:v>60.71813031117919</x:v>
       </x:c>
       <x:c r="K9" s="11" t="n">
         <x:f>IF(L9="Full home run",I9+J9,"")</x:f>
-        <x:v>59.30813031117918</x:v>
+        <x:v>63.10813031117919</x:v>
       </x:c>
       <x:c r="L9" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3662,14 +3668,14 @@
       </x:c>
       <x:c r="I10" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A10,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J10" s="11" t="n">
-        <x:v>52.27413031117918</x:v>
+        <x:v>56.21813031117919</x:v>
       </x:c>
       <x:c r="K10" s="11" t="n">
         <x:f>IF(L10="Full home run",I10+J10,"")</x:f>
-        <x:v>54.80813031117918</x:v>
+        <x:v>58.60813031117919</x:v>
       </x:c>
       <x:c r="L10" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3726,14 +3732,14 @@
       </x:c>
       <x:c r="I11" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A11,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J11" s="11" t="n">
-        <x:v>47.77413031117918</x:v>
+        <x:v>51.71813031117919</x:v>
       </x:c>
       <x:c r="K11" s="11" t="n">
         <x:f>IF(L11="Full home run",I11+J11,"")</x:f>
-        <x:v>50.30813031117918</x:v>
+        <x:v>54.10813031117919</x:v>
       </x:c>
       <x:c r="L11" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3790,14 +3796,14 @@
       </x:c>
       <x:c r="I12" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A12,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J12" s="11" t="n">
-        <x:v>43.27413031117918</x:v>
+        <x:v>47.21813031117919</x:v>
       </x:c>
       <x:c r="K12" s="11" t="n">
         <x:f>IF(L12="Full home run",I12+J12,"")</x:f>
-        <x:v>45.80813031117918</x:v>
+        <x:v>49.60813031117919</x:v>
       </x:c>
       <x:c r="L12" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3854,14 +3860,14 @@
       </x:c>
       <x:c r="I13" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A13,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J13" s="11" t="n">
-        <x:v>38.77413031117918</x:v>
+        <x:v>42.71813031117919</x:v>
       </x:c>
       <x:c r="K13" s="11" t="n">
         <x:f>IF(L13="Full home run",I13+J13,"")</x:f>
-        <x:v>41.30813031117918</x:v>
+        <x:v>45.10813031117919</x:v>
       </x:c>
       <x:c r="L13" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3921,11 +3927,11 @@
         <x:v>8.040692614226739</x:v>
       </x:c>
       <x:c r="J14" s="11" t="n">
-        <x:v>28.966999999999995</x:v>
+        <x:v>32.766999999999996</x:v>
       </x:c>
       <x:c r="K14" s="11" t="n">
         <x:f>IF(L14="Full home run",I14+J14,"")</x:f>
-        <x:v>37.007692614226734</x:v>
+        <x:v>40.80769261422674</x:v>
       </x:c>
       <x:c r="L14" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3988,7 +3994,7 @@
       </x:c>
       <x:c r="I15" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A15,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>67.87413031117919</x:v>
+        <x:v>58.61813031117919</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
       <x:c r="K15" s="11" t="str">
@@ -4047,14 +4053,14 @@
       </x:c>
       <x:c r="I16" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A16,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n">
-        <x:v>67.87413031117919</x:v>
+        <x:v>58.61813031117919</x:v>
       </x:c>
       <x:c r="K16" s="11" t="n">
         <x:f>IF(L16="Full home run",I16+J16,"")</x:f>
-        <x:v>70.40813031117919</x:v>
+        <x:v>61.008130311179194</x:v>
       </x:c>
       <x:c r="L16" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4111,14 +4117,14 @@
       </x:c>
       <x:c r="I17" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A17,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J17" s="11" t="n">
-        <x:v>63.37413031117919</x:v>
+        <x:v>54.11813031117919</x:v>
       </x:c>
       <x:c r="K17" s="11" t="n">
         <x:f>IF(L17="Full home run",I17+J17,"")</x:f>
-        <x:v>65.90813031117919</x:v>
+        <x:v>56.508130311179194</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4175,14 +4181,14 @@
       </x:c>
       <x:c r="I18" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A18,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J18" s="11" t="n">
-        <x:v>58.87413031117919</x:v>
+        <x:v>49.61813031117919</x:v>
       </x:c>
       <x:c r="K18" s="11" t="n">
         <x:f>IF(L18="Full home run",I18+J18,"")</x:f>
-        <x:v>61.408130311179185</x:v>
+        <x:v>52.008130311179194</x:v>
       </x:c>
       <x:c r="L18" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4239,14 +4245,14 @@
       </x:c>
       <x:c r="I19" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A19,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J19" s="11" t="n">
-        <x:v>54.37413031117919</x:v>
+        <x:v>45.11813031117919</x:v>
       </x:c>
       <x:c r="K19" s="11" t="n">
         <x:f>IF(L19="Full home run",I19+J19,"")</x:f>
-        <x:v>56.908130311179185</x:v>
+        <x:v>47.508130311179194</x:v>
       </x:c>
       <x:c r="L19" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4303,14 +4309,14 @@
       </x:c>
       <x:c r="I20" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A20,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J20" s="11" t="n">
-        <x:v>49.87413031117919</x:v>
+        <x:v>40.61813031117919</x:v>
       </x:c>
       <x:c r="K20" s="11" t="n">
         <x:f>IF(L20="Full home run",I20+J20,"")</x:f>
-        <x:v>52.408130311179185</x:v>
+        <x:v>43.008130311179194</x:v>
       </x:c>
       <x:c r="L20" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4367,14 +4373,14 @@
       </x:c>
       <x:c r="I21" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A21,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.534</x:v>
+        <x:v>2.3899999999999997</x:v>
       </x:c>
       <x:c r="J21" s="11" t="n">
-        <x:v>45.37413031117919</x:v>
+        <x:v>36.11813031117919</x:v>
       </x:c>
       <x:c r="K21" s="11" t="n">
         <x:f>IF(L21="Full home run",I21+J21,"")</x:f>
-        <x:v>47.908130311179185</x:v>
+        <x:v>38.508130311179194</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4434,11 +4440,11 @@
         <x:v>8.040692614226739</x:v>
       </x:c>
       <x:c r="J22" s="11" t="n">
-        <x:v>35.56699999999999</x:v>
+        <x:v>26.167</x:v>
       </x:c>
       <x:c r="K22" s="11" t="n">
         <x:f>IF(L22="Full home run",I22+J22,"")</x:f>
-        <x:v>43.607692614226735</x:v>
+        <x:v>34.207692614226744</x:v>
       </x:c>
       <x:c r="L22" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4495,7 +4501,7 @@
       </x:c>
       <x:c r="I23" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A23,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>73.06213031117917</x:v>
+        <x:v>77.07013031117918</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
       <x:c r="K23" s="11" t="str">
@@ -4554,14 +4560,14 @@
       </x:c>
       <x:c r="I24" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A24,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>10.613024897171492</x:v>
+        <x:v>10.818705875926424</x:v>
       </x:c>
       <x:c r="J24" s="11" t="n">
-        <x:v>73.06213031117917</x:v>
+        <x:v>77.07013031117918</x:v>
       </x:c>
       <x:c r="K24" s="11" t="n">
         <x:f>IF(L24="Full home run",I24+J24,"")</x:f>
-        <x:v>83.67515520835067</x:v>
+        <x:v>87.88883618710561</x:v>
       </x:c>
       <x:c r="L24" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4618,7 +4624,7 @@
       </x:c>
       <x:c r="I25" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A25,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>79.66213031117918</x:v>
+        <x:v>70.47013031117918</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
       <x:c r="K25" s="11" t="str">
@@ -4677,14 +4683,14 @@
       </x:c>
       <x:c r="I26" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A26,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>10.613024897171492</x:v>
+        <x:v>10.818705875926424</x:v>
       </x:c>
       <x:c r="J26" s="11" t="n">
-        <x:v>79.66213031117918</x:v>
+        <x:v>70.47013031117918</x:v>
       </x:c>
       <x:c r="K26" s="11" t="n">
         <x:f>IF(L26="Full home run",I26+J26,"")</x:f>
-        <x:v>90.27515520835067</x:v>
+        <x:v>81.2888361871056</x:v>
       </x:c>
       <x:c r="L26" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4742,7 +4748,7 @@
       </x:c>
       <x:c r="I27" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A27,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>62.21113031117919</x:v>
+        <x:v>66.17113031117918</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
       <x:c r="K27" s="11" t="str">
@@ -4801,14 +4807,14 @@
       </x:c>
       <x:c r="I28" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A28,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.940734978599284</x:v>
+        <x:v>7.100734978599284</x:v>
       </x:c>
       <x:c r="J28" s="11" t="n">
-        <x:v>62.21113031117919</x:v>
+        <x:v>66.17113031117918</x:v>
       </x:c>
       <x:c r="K28" s="11" t="n">
         <x:f>IF(L28="Full home run",I28+J28,"")</x:f>
-        <x:v>69.15186528977847</x:v>
+        <x:v>73.27186528977848</x:v>
       </x:c>
       <x:c r="L28" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4865,14 +4871,14 @@
       </x:c>
       <x:c r="I29" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A29,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.9407349785992825</x:v>
+        <x:v>7.100734978599283</x:v>
       </x:c>
       <x:c r="J29" s="11" t="n">
-        <x:v>48.71113031117919</x:v>
+        <x:v>52.67113031117918</x:v>
       </x:c>
       <x:c r="K29" s="11" t="n">
         <x:f>IF(L29="Full home run",I29+J29,"")</x:f>
-        <x:v>55.65186528977847</x:v>
+        <x:v>59.77186528977847</x:v>
       </x:c>
       <x:c r="L29" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4930,7 +4936,7 @@
       </x:c>
       <x:c r="I30" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A30,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>68.8111303111792</x:v>
+        <x:v>59.57113031117918</x:v>
       </x:c>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="11" t="str">
@@ -4989,14 +4995,14 @@
       </x:c>
       <x:c r="I31" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A31,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.940734978599284</x:v>
+        <x:v>7.100734978599284</x:v>
       </x:c>
       <x:c r="J31" s="11" t="n">
-        <x:v>68.8111303111792</x:v>
+        <x:v>59.57113031117918</x:v>
       </x:c>
       <x:c r="K31" s="11" t="n">
         <x:f>IF(L31="Full home run",I31+J31,"")</x:f>
-        <x:v>75.75186528977848</x:v>
+        <x:v>66.67186528977847</x:v>
       </x:c>
       <x:c r="L31" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5053,14 +5059,14 @@
       </x:c>
       <x:c r="I32" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A32,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.9407349785992825</x:v>
+        <x:v>7.100734978599283</x:v>
       </x:c>
       <x:c r="J32" s="11" t="n">
-        <x:v>55.31113031117919</x:v>
+        <x:v>46.07113031117918</x:v>
       </x:c>
       <x:c r="K32" s="11" t="n">
         <x:f>IF(L32="Full home run",I32+J32,"")</x:f>
-        <x:v>62.25186528977847</x:v>
+        <x:v>53.17186528977847</x:v>
       </x:c>
       <x:c r="L32" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5120,7 +5126,7 @@
       </x:c>
       <x:c r="I33" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A33,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>73.38313031117919</x:v>
+        <x:v>77.35913031117919</x:v>
       </x:c>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="11" t="str">
@@ -5179,14 +5185,14 @@
       </x:c>
       <x:c r="I34" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A34,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.820000000000001</x:v>
+        <x:v>6.996000000000001</x:v>
       </x:c>
       <x:c r="J34" s="11" t="n">
-        <x:v>73.38313031117919</x:v>
+        <x:v>77.35913031117919</x:v>
       </x:c>
       <x:c r="K34" s="11" t="n">
         <x:f>IF(L34="Full home run",I34+J34,"")</x:f>
-        <x:v>80.2031303111792</x:v>
+        <x:v>84.35513031117918</x:v>
       </x:c>
       <x:c r="L34" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5243,14 +5249,14 @@
       </x:c>
       <x:c r="I35" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A35,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>11.345999999999998</x:v>
+        <x:v>11.522</x:v>
       </x:c>
       <x:c r="J35" s="11" t="n">
-        <x:v>73.38313031117919</x:v>
+        <x:v>77.35913031117919</x:v>
       </x:c>
       <x:c r="K35" s="11" t="n">
         <x:f>IF(L35="Full home run",I35+J35,"")</x:f>
-        <x:v>84.72913031117919</x:v>
+        <x:v>88.88113031117919</x:v>
       </x:c>
       <x:c r="L35" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5307,14 +5313,14 @@
       </x:c>
       <x:c r="I36" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A36,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>5.5181723888610765</x:v>
+        <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J36" s="11" t="n">
-        <x:v>56.75813031117919</x:v>
+        <x:v>60.734130311179186</x:v>
       </x:c>
       <x:c r="K36" s="11" t="n">
         <x:f>IF(L36="Full home run",I36+J36,"")</x:f>
-        <x:v>62.27630270004026</x:v>
+        <x:v>66.42830270004026</x:v>
       </x:c>
       <x:c r="L36" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5371,14 +5377,14 @@
       </x:c>
       <x:c r="I37" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A37,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>5.5181723888610765</x:v>
+        <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J37" s="11" t="n">
-        <x:v>43.25813031117919</x:v>
+        <x:v>47.234130311179186</x:v>
       </x:c>
       <x:c r="K37" s="11" t="n">
         <x:f>IF(L37="Full home run",I37+J37,"")</x:f>
-        <x:v>48.77630270004026</x:v>
+        <x:v>52.92830270004026</x:v>
       </x:c>
       <x:c r="L37" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5438,7 +5444,7 @@
       </x:c>
       <x:c r="I38" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A38,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>79.98313031117918</x:v>
+        <x:v>70.75913031117919</x:v>
       </x:c>
       <x:c r="J38" s="11"/>
       <x:c r="K38" s="11" t="str">
@@ -5497,14 +5503,14 @@
       </x:c>
       <x:c r="I39" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A39,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>6.820000000000001</x:v>
+        <x:v>6.996000000000001</x:v>
       </x:c>
       <x:c r="J39" s="11" t="n">
-        <x:v>79.98313031117918</x:v>
+        <x:v>70.75913031117919</x:v>
       </x:c>
       <x:c r="K39" s="11" t="n">
         <x:f>IF(L39="Full home run",I39+J39,"")</x:f>
-        <x:v>86.80313031117919</x:v>
+        <x:v>77.75513031117919</x:v>
       </x:c>
       <x:c r="L39" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5561,14 +5567,14 @@
       </x:c>
       <x:c r="I40" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A40,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>11.345999999999998</x:v>
+        <x:v>11.522</x:v>
       </x:c>
       <x:c r="J40" s="11" t="n">
-        <x:v>79.98313031117918</x:v>
+        <x:v>70.75913031117919</x:v>
       </x:c>
       <x:c r="K40" s="11" t="n">
         <x:f>IF(L40="Full home run",I40+J40,"")</x:f>
-        <x:v>91.32913031117918</x:v>
+        <x:v>82.2811303111792</x:v>
       </x:c>
       <x:c r="L40" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5625,14 +5631,14 @@
       </x:c>
       <x:c r="I41" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A41,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>5.5181723888610765</x:v>
+        <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J41" s="11" t="n">
-        <x:v>63.35813031117918</x:v>
+        <x:v>54.13413031117919</x:v>
       </x:c>
       <x:c r="K41" s="11" t="n">
         <x:f>IF(L41="Full home run",I41+J41,"")</x:f>
-        <x:v>68.87630270004026</x:v>
+        <x:v>59.82830270004027</x:v>
       </x:c>
       <x:c r="L41" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5689,14 +5695,14 @@
       </x:c>
       <x:c r="I42" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A42,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>5.5181723888610765</x:v>
+        <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J42" s="11" t="n">
-        <x:v>49.85813031117918</x:v>
+        <x:v>40.63413031117919</x:v>
       </x:c>
       <x:c r="K42" s="11" t="n">
         <x:f>IF(L42="Full home run",I42+J42,"")</x:f>
-        <x:v>55.376302700040256</x:v>
+        <x:v>46.32830270004027</x:v>
       </x:c>
       <x:c r="L42" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -6117,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re349f2b7377a47cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b3185fd41f34aff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6273,11 +6279,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:f>SQRT((C9-C8)^2+(D9-D8)^2+(E9-E8)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
         <x:v>Current</x:v>
@@ -6297,7 +6303,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:f>SQRT((C10-C9)^2+(D10-D9)^2+(E10-E9)^2)</x:f>
@@ -6321,7 +6327,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:f>SQRT((C11-C10)^2+(D11-D10)^2+(E11-E10)^2)</x:f>
@@ -6345,7 +6351,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:f>SQRT((C12-C11)^2+(D12-D11)^2+(E12-E11)^2)</x:f>
@@ -6366,14 +6372,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:f>SQRT((C13-C12)^2+(D13-D12)^2+(E13-E12)^2)</x:f>
-        <x:v>1.3639999999999999</x:v>
+        <x:v>1.2199999999999998</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
         <x:v>Current</x:v>
@@ -6390,14 +6396,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:f>SQRT((C14-C13)^2+(D14-D13)^2+(E14-E13)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Current</x:v>
@@ -6414,7 +6420,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6445,7 +6451,7 @@
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:f>SQRT((C16-C15)^2+(D16-D15)^2+(E16-E15)^2)</x:f>
-        <x:v>1.346</x:v>
+        <x:v>1.4900000000000002</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
         <x:v>Current</x:v>
@@ -6606,14 +6612,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:f>SQRT((C23-C22)^2+(D23-D22)^2+(E23-E22)^2)</x:f>
-        <x:v>1.346</x:v>
+        <x:v>1.4900000000000002</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
         <x:v>Current</x:v>
@@ -6630,7 +6636,7 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6654,7 +6660,7 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6685,7 +6691,7 @@
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:f>SQRT((C26-C25)^2+(D26-D25)^2+(E26-E25)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G26" s="8" t="str">
         <x:v>Current</x:v>
@@ -6726,7 +6732,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6757,7 +6763,7 @@
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>Current</x:v>
@@ -6798,7 +6804,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6829,7 +6835,7 @@
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>Current</x:v>
@@ -6870,7 +6876,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6901,7 +6907,7 @@
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>Current</x:v>
@@ -6942,7 +6948,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -6973,7 +6979,7 @@
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -7014,7 +7020,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -7045,7 +7051,7 @@
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>Current</x:v>
@@ -7305,11 +7311,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F52" s="11" t="n">
         <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>Current</x:v>
@@ -7329,7 +7335,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E53" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F53" s="11" t="n">
         <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
@@ -7353,7 +7359,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E54" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F54" s="11" t="n">
         <x:f>SQRT((C54-C53)^2+(D54-D53)^2+(E54-E53)^2)</x:f>
@@ -7377,7 +7383,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F55" s="11" t="n">
         <x:f>SQRT((C55-C54)^2+(D55-D54)^2+(E55-E54)^2)</x:f>
@@ -7398,14 +7404,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E56" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F56" s="11" t="n">
         <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
-        <x:v>1.3639999999999999</x:v>
+        <x:v>1.2199999999999998</x:v>
       </x:c>
       <x:c r="G56" s="8" t="str">
         <x:v>Current</x:v>
@@ -7422,14 +7428,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E57" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F57" s="11" t="n">
         <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
         <x:v>Current</x:v>
@@ -7446,7 +7452,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E58" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7477,7 +7483,7 @@
       </x:c>
       <x:c r="F59" s="11" t="n">
         <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
-        <x:v>1.346</x:v>
+        <x:v>1.4900000000000002</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
         <x:v>Current</x:v>
@@ -7638,14 +7644,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E66" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F66" s="11" t="n">
         <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
-        <x:v>1.346</x:v>
+        <x:v>1.4900000000000002</x:v>
       </x:c>
       <x:c r="G66" s="8" t="str">
         <x:v>Current</x:v>
@@ -7662,7 +7668,7 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E67" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7686,7 +7692,7 @@
         <x:v>14.475000000000001</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E68" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7717,7 +7723,7 @@
       </x:c>
       <x:c r="F69" s="11" t="n">
         <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G69" s="8" t="str">
         <x:v>Current</x:v>
@@ -7758,7 +7764,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7789,7 +7795,7 @@
       </x:c>
       <x:c r="F72" s="11" t="n">
         <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G72" s="8" t="str">
         <x:v>Current</x:v>
@@ -7830,7 +7836,7 @@
         <x:v>23.475</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E74" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7861,7 +7867,7 @@
       </x:c>
       <x:c r="F75" s="11" t="n">
         <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G75" s="8" t="str">
         <x:v>Current</x:v>
@@ -7902,7 +7908,7 @@
         <x:v>27.975</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
         <x:v>7.36</x:v>
@@ -7933,7 +7939,7 @@
       </x:c>
       <x:c r="F78" s="11" t="n">
         <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G78" s="8" t="str">
         <x:v>Current</x:v>
@@ -7974,7 +7980,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E80" s="11" t="n">
         <x:v>7.36</x:v>
@@ -8005,7 +8011,7 @@
       </x:c>
       <x:c r="F81" s="11" t="n">
         <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G81" s="8" t="str">
         <x:v>Current</x:v>
@@ -8046,7 +8052,7 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>5.694</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="E83" s="11" t="n">
         <x:v>7.36</x:v>
@@ -8077,7 +8083,7 @@
       </x:c>
       <x:c r="F84" s="11" t="n">
         <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
-        <x:v>2.2439999999999998</x:v>
+        <x:v>2.0999999999999996</x:v>
       </x:c>
       <x:c r="G84" s="8" t="str">
         <x:v>Current</x:v>
@@ -8337,11 +8343,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E95" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F95" s="11" t="n">
         <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G95" s="8" t="str">
         <x:v>Current</x:v>
@@ -8361,7 +8367,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E96" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F96" s="11" t="n">
         <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
@@ -8385,7 +8391,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E97" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F97" s="11" t="n">
         <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
@@ -8409,7 +8415,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E98" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F98" s="11" t="n">
         <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
@@ -8430,14 +8436,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E99" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F99" s="11" t="n">
         <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
-        <x:v>1.396</x:v>
+        <x:v>1.1879999999999997</x:v>
       </x:c>
       <x:c r="G99" s="8" t="str">
         <x:v>Current</x:v>
@@ -8454,14 +8460,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E100" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F100" s="11" t="n">
         <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G100" s="8" t="str">
         <x:v>Current</x:v>
@@ -8478,7 +8484,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E101" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -8509,7 +8515,7 @@
       </x:c>
       <x:c r="F102" s="11" t="n">
         <x:f>SQRT((C102-C101)^2+(D102-D101)^2+(E102-E101)^2)</x:f>
-        <x:v>1.314</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G102" s="8" t="str">
         <x:v>Current</x:v>
@@ -8670,14 +8676,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E109" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F109" s="11" t="n">
         <x:f>SQRT((C109-C108)^2+(D109-D108)^2+(E109-E108)^2)</x:f>
-        <x:v>1.314</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G109" s="8" t="str">
         <x:v>Current</x:v>
@@ -8694,7 +8700,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E110" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -8718,7 +8724,7 @@
         <x:v>2.655</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E111" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -8742,7 +8748,7 @@
         <x:v>2.655</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E112" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -8773,7 +8779,7 @@
       </x:c>
       <x:c r="F113" s="11" t="n">
         <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
-        <x:v>1.948024897171492</x:v>
+        <x:v>2.1537058759264234</x:v>
       </x:c>
       <x:c r="G113" s="8" t="str">
         <x:v>Current</x:v>
@@ -8913,11 +8919,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E119" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F119" s="11" t="n">
         <x:f>SQRT((C119-C118)^2+(D119-D118)^2+(E119-E118)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G119" s="8" t="str">
         <x:v>Current</x:v>
@@ -8937,7 +8943,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E120" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F120" s="11" t="n">
         <x:f>SQRT((C120-C119)^2+(D120-D119)^2+(E120-E119)^2)</x:f>
@@ -8961,7 +8967,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E121" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F121" s="11" t="n">
         <x:f>SQRT((C121-C120)^2+(D121-D120)^2+(E121-E120)^2)</x:f>
@@ -8985,7 +8991,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E122" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F122" s="11" t="n">
         <x:f>SQRT((C122-C121)^2+(D122-D121)^2+(E122-E121)^2)</x:f>
@@ -9006,14 +9012,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D123" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E123" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F123" s="11" t="n">
         <x:f>SQRT((C123-C122)^2+(D123-D122)^2+(E123-E122)^2)</x:f>
-        <x:v>1.396</x:v>
+        <x:v>1.1879999999999997</x:v>
       </x:c>
       <x:c r="G123" s="8" t="str">
         <x:v>Current</x:v>
@@ -9030,14 +9036,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D124" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E124" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F124" s="11" t="n">
         <x:f>SQRT((C124-C123)^2+(D124-D123)^2+(E124-E123)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G124" s="8" t="str">
         <x:v>Current</x:v>
@@ -9054,7 +9060,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D125" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E125" s="11" t="n">
         <x:v>7.36</x:v>
@@ -9085,7 +9091,7 @@
       </x:c>
       <x:c r="F126" s="11" t="n">
         <x:f>SQRT((C126-C125)^2+(D126-D125)^2+(E126-E125)^2)</x:f>
-        <x:v>1.314</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G126" s="8" t="str">
         <x:v>Current</x:v>
@@ -9246,14 +9252,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D133" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E133" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F133" s="11" t="n">
         <x:f>SQRT((C133-C132)^2+(D133-D132)^2+(E133-E132)^2)</x:f>
-        <x:v>1.314</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G133" s="8" t="str">
         <x:v>Current</x:v>
@@ -9270,7 +9276,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D134" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E134" s="11" t="n">
         <x:v>7.36</x:v>
@@ -9294,7 +9300,7 @@
         <x:v>2.655</x:v>
       </x:c>
       <x:c r="D135" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E135" s="11" t="n">
         <x:v>7.36</x:v>
@@ -9318,7 +9324,7 @@
         <x:v>2.655</x:v>
       </x:c>
       <x:c r="D136" s="11" t="n">
-        <x:v>5.726</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E136" s="11" t="n">
         <x:v>7.36</x:v>
@@ -9349,7 +9355,7 @@
       </x:c>
       <x:c r="F137" s="11" t="n">
         <x:f>SQRT((C137-C136)^2+(D137-D136)^2+(E137-E136)^2)</x:f>
-        <x:v>1.948024897171492</x:v>
+        <x:v>2.1537058759264234</x:v>
       </x:c>
       <x:c r="G137" s="8" t="str">
         <x:v>Current</x:v>
@@ -9489,11 +9495,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E143" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F143" s="11" t="n">
         <x:f>SQRT((C143-C142)^2+(D143-D142)^2+(E143-E142)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
         <x:v>Current</x:v>
@@ -9513,7 +9519,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E144" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F144" s="11" t="n">
         <x:f>SQRT((C144-C143)^2+(D144-D143)^2+(E144-E143)^2)</x:f>
@@ -9537,7 +9543,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E145" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F145" s="11" t="n">
         <x:f>SQRT((C145-C144)^2+(D145-D144)^2+(E145-E144)^2)</x:f>
@@ -9561,7 +9567,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E146" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F146" s="11" t="n">
         <x:f>SQRT((C146-C145)^2+(D146-D145)^2+(E146-E145)^2)</x:f>
@@ -9582,14 +9588,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D147" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E147" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F147" s="11" t="n">
         <x:f>SQRT((C147-C146)^2+(D147-D146)^2+(E147-E146)^2)</x:f>
-        <x:v>1.3719999999999999</x:v>
+        <x:v>1.2119999999999997</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
         <x:v>Current</x:v>
@@ -9606,14 +9612,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D148" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E148" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F148" s="11" t="n">
         <x:f>SQRT((C148-C147)^2+(D148-D147)^2+(E148-E147)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G148" s="8" t="str">
         <x:v>Current</x:v>
@@ -9630,7 +9636,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D149" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E149" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -9661,7 +9667,7 @@
       </x:c>
       <x:c r="F150" s="11" t="n">
         <x:f>SQRT((C150-C149)^2+(D150-D149)^2+(E150-E149)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G150" s="8" t="str">
         <x:v>Current</x:v>
@@ -9822,14 +9828,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D157" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E157" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F157" s="11" t="n">
         <x:f>SQRT((C157-C156)^2+(D157-D156)^2+(E157-E156)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G157" s="8" t="str">
         <x:v>Current</x:v>
@@ -9846,7 +9852,7 @@
         <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D158" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E158" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -9870,7 +9876,7 @@
         <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D159" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E159" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -9901,7 +9907,7 @@
       </x:c>
       <x:c r="F160" s="11" t="n">
         <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G160" s="8" t="str">
         <x:v>Current</x:v>
@@ -10014,7 +10020,7 @@
         <x:v>27.03</x:v>
       </x:c>
       <x:c r="D165" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E165" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -10045,7 +10051,7 @@
       </x:c>
       <x:c r="F166" s="11" t="n">
         <x:f>SQRT((C166-C165)^2+(D166-D165)^2+(E166-E165)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G166" s="8" t="str">
         <x:v>Current</x:v>
@@ -10209,11 +10215,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E173" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F173" s="11" t="n">
         <x:f>SQRT((C173-C172)^2+(D173-D172)^2+(E173-E172)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G173" s="8" t="str">
         <x:v>Current</x:v>
@@ -10233,7 +10239,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E174" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F174" s="11" t="n">
         <x:f>SQRT((C174-C173)^2+(D174-D173)^2+(E174-E173)^2)</x:f>
@@ -10257,7 +10263,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E175" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F175" s="11" t="n">
         <x:f>SQRT((C175-C174)^2+(D175-D174)^2+(E175-E174)^2)</x:f>
@@ -10281,7 +10287,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E176" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F176" s="11" t="n">
         <x:f>SQRT((C176-C175)^2+(D176-D175)^2+(E176-E175)^2)</x:f>
@@ -10302,14 +10308,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D177" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E177" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F177" s="11" t="n">
         <x:f>SQRT((C177-C176)^2+(D177-D176)^2+(E177-E176)^2)</x:f>
-        <x:v>1.3719999999999999</x:v>
+        <x:v>1.2119999999999997</x:v>
       </x:c>
       <x:c r="G177" s="8" t="str">
         <x:v>Current</x:v>
@@ -10326,14 +10332,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D178" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E178" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F178" s="11" t="n">
         <x:f>SQRT((C178-C177)^2+(D178-D177)^2+(E178-E177)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G178" s="8" t="str">
         <x:v>Current</x:v>
@@ -10350,7 +10356,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D179" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E179" s="11" t="n">
         <x:v>7.36</x:v>
@@ -10381,7 +10387,7 @@
       </x:c>
       <x:c r="F180" s="11" t="n">
         <x:f>SQRT((C180-C179)^2+(D180-D179)^2+(E180-E179)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G180" s="8" t="str">
         <x:v>Current</x:v>
@@ -10542,14 +10548,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D187" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E187" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F187" s="11" t="n">
         <x:f>SQRT((C187-C186)^2+(D187-D186)^2+(E187-E186)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G187" s="8" t="str">
         <x:v>Current</x:v>
@@ -10566,7 +10572,7 @@
         <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E188" s="11" t="n">
         <x:v>7.36</x:v>
@@ -10590,7 +10596,7 @@
         <x:v>13.530000000000001</x:v>
       </x:c>
       <x:c r="D189" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E189" s="11" t="n">
         <x:v>7.36</x:v>
@@ -10621,7 +10627,7 @@
       </x:c>
       <x:c r="F190" s="11" t="n">
         <x:f>SQRT((C190-C189)^2+(D190-D189)^2+(E190-E189)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G190" s="8" t="str">
         <x:v>Current</x:v>
@@ -10734,7 +10740,7 @@
         <x:v>27.03</x:v>
       </x:c>
       <x:c r="D195" s="11" t="n">
-        <x:v>5.702</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E195" s="11" t="n">
         <x:v>7.36</x:v>
@@ -10765,7 +10771,7 @@
       </x:c>
       <x:c r="F196" s="11" t="n">
         <x:f>SQRT((C196-C195)^2+(D196-D195)^2+(E196-E195)^2)</x:f>
-        <x:v>1.338</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G196" s="8" t="str">
         <x:v>Current</x:v>
@@ -10929,11 +10935,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E203" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F203" s="11" t="n">
         <x:f>SQRT((C203-C202)^2+(D203-D202)^2+(E203-E202)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G203" s="8" t="str">
         <x:v>Current</x:v>
@@ -10953,7 +10959,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F204" s="11" t="n">
         <x:f>SQRT((C204-C203)^2+(D204-D203)^2+(E204-E203)^2)</x:f>
@@ -10977,7 +10983,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E205" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F205" s="11" t="n">
         <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
@@ -11001,7 +11007,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E206" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F206" s="11" t="n">
         <x:f>SQRT((C206-C205)^2+(D206-D205)^2+(E206-E205)^2)</x:f>
@@ -11022,14 +11028,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F207" s="11" t="n">
         <x:f>SQRT((C207-C206)^2+(D207-D206)^2+(E207-E206)^2)</x:f>
-        <x:v>1.38</x:v>
+        <x:v>1.2039999999999997</x:v>
       </x:c>
       <x:c r="G207" s="8" t="str">
         <x:v>Current</x:v>
@@ -11046,14 +11052,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D208" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E208" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F208" s="11" t="n">
         <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G208" s="8" t="str">
         <x:v>Current</x:v>
@@ -11070,7 +11076,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D209" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E209" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11101,7 +11107,7 @@
       </x:c>
       <x:c r="F210" s="11" t="n">
         <x:f>SQRT((C210-C209)^2+(D210-D209)^2+(E210-E209)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G210" s="8" t="str">
         <x:v>Current</x:v>
@@ -11262,14 +11268,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D217" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E217" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F217" s="11" t="n">
         <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G217" s="8" t="str">
         <x:v>Current</x:v>
@@ -11286,7 +11292,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D218" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E218" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11310,7 +11316,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D219" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E219" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11334,7 +11340,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D220" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E220" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11365,7 +11371,7 @@
       </x:c>
       <x:c r="F221" s="11" t="n">
         <x:f>SQRT((C221-C220)^2+(D221-D220)^2+(E221-E220)^2)</x:f>
-        <x:v>1.9400000000000004</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G221" s="8" t="str">
         <x:v>Current</x:v>
@@ -11526,7 +11532,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D228" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E228" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11557,7 +11563,7 @@
       </x:c>
       <x:c r="F229" s="11" t="n">
         <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>1.9400000000000004</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G229" s="8" t="str">
         <x:v>Current</x:v>
@@ -11718,7 +11724,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D236" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E236" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11749,7 +11755,7 @@
       </x:c>
       <x:c r="F237" s="11" t="n">
         <x:f>SQRT((C237-C236)^2+(D237-D236)^2+(E237-E236)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G237" s="8" t="str">
         <x:v>Current</x:v>
@@ -11862,7 +11868,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D242" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E242" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -11893,7 +11899,7 @@
       </x:c>
       <x:c r="F243" s="11" t="n">
         <x:f>SQRT((C243-C242)^2+(D243-D242)^2+(E243-E242)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G243" s="8" t="str">
         <x:v>Current</x:v>
@@ -12057,11 +12063,11 @@
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E250" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F250" s="11" t="n">
         <x:f>SQRT((C250-C249)^2+(D250-D249)^2+(E250-E249)^2)</x:f>
-        <x:v>3.64</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G250" s="8" t="str">
         <x:v>Current</x:v>
@@ -12081,7 +12087,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E251" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F251" s="11" t="n">
         <x:f>SQRT((C251-C250)^2+(D251-D250)^2+(E251-E250)^2)</x:f>
@@ -12105,7 +12111,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E252" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F252" s="11" t="n">
         <x:f>SQRT((C252-C251)^2+(D252-D251)^2+(E252-E251)^2)</x:f>
@@ -12129,7 +12135,7 @@
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E253" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F253" s="11" t="n">
         <x:f>SQRT((C253-C252)^2+(D253-D252)^2+(E253-E252)^2)</x:f>
@@ -12150,14 +12156,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D254" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E254" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F254" s="11" t="n">
         <x:f>SQRT((C254-C253)^2+(D254-D253)^2+(E254-E253)^2)</x:f>
-        <x:v>1.38</x:v>
+        <x:v>1.2039999999999997</x:v>
       </x:c>
       <x:c r="G254" s="8" t="str">
         <x:v>Current</x:v>
@@ -12174,14 +12180,14 @@
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D255" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E255" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F255" s="11" t="n">
         <x:f>SQRT((C255-C254)^2+(D255-D254)^2+(E255-E254)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G255" s="8" t="str">
         <x:v>Current</x:v>
@@ -12198,7 +12204,7 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12229,7 +12235,7 @@
       </x:c>
       <x:c r="F257" s="11" t="n">
         <x:f>SQRT((C257-C256)^2+(D257-D256)^2+(E257-E256)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G257" s="8" t="str">
         <x:v>Current</x:v>
@@ -12390,14 +12396,14 @@
         <x:v>36.975</x:v>
       </x:c>
       <x:c r="D264" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E264" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F264" s="11" t="n">
         <x:f>SQRT((C264-C263)^2+(D264-D263)^2+(E264-E263)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G264" s="8" t="str">
         <x:v>Current</x:v>
@@ -12414,7 +12420,7 @@
         <x:v>5.475</x:v>
       </x:c>
       <x:c r="D265" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E265" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12438,7 +12444,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D266" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E266" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12462,7 +12468,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D267" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E267" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12493,7 +12499,7 @@
       </x:c>
       <x:c r="F268" s="11" t="n">
         <x:f>SQRT((C268-C267)^2+(D268-D267)^2+(E268-E267)^2)</x:f>
-        <x:v>1.9400000000000004</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G268" s="8" t="str">
         <x:v>Current</x:v>
@@ -12654,7 +12660,7 @@
         <x:v>2.35</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12685,7 +12691,7 @@
       </x:c>
       <x:c r="F276" s="11" t="n">
         <x:f>SQRT((C276-C275)^2+(D276-D275)^2+(E276-E275)^2)</x:f>
-        <x:v>1.9400000000000004</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G276" s="8" t="str">
         <x:v>Current</x:v>
@@ -12846,7 +12852,7 @@
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D283" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E283" s="11" t="n">
         <x:v>7.36</x:v>
@@ -12877,7 +12883,7 @@
       </x:c>
       <x:c r="F284" s="11" t="n">
         <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G284" s="8" t="str">
         <x:v>Current</x:v>
@@ -12990,7 +12996,7 @@
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D289" s="11" t="n">
-        <x:v>5.71</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E289" s="11" t="n">
         <x:v>7.36</x:v>
@@ -13021,7 +13027,7 @@
       </x:c>
       <x:c r="F290" s="11" t="n">
         <x:f>SQRT((C290-C289)^2+(D290-D289)^2+(E290-E289)^2)</x:f>
-        <x:v>1.33</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G290" s="8" t="str">
         <x:v>Current</x:v>
@@ -13657,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97240a61f74444f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c8446183b542a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf1a2005141dc4ee7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6eee1d4c752b4ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rda53799242144659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Red4d9f342c714eff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra8d1667b906e4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8e83f6148800417b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R202c9243cb484255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R576729c051ed4e20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
+        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
+        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra838ec4e70b9457c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc59699bc3e6b471e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b3185fd41f34aff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe9378f7647e4509"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c8446183b542a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae8a1eed35914ff7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra8d1667b906e4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8e83f6148800417b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R202c9243cb484255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R576729c051ed4e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1390953555494e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R423c28341d8a457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R8a7fb1b936c04f48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2402a66bdcb243da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
+        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
+        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -972,13 +972,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
         <x:v>wall</x:v>
@@ -993,7 +993,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M7" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 85.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 87 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N7" s="11" t="n">
         <x:v>20</x:v>
@@ -1002,7 +1002,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P7" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q7" s="9"/>
       <x:c r="R7" s="9"/>
@@ -1021,7 +1021,7 @@
         <x:v>drop:AV1:A1:audio:-1:S261</x:v>
       </x:c>
       <x:c r="AC7" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":85.1}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":87}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="96" customHeight="1">
@@ -1041,13 +1041,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>wall</x:v>
@@ -1062,7 +1062,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M8" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 86.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 88.7 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N8" s="11" t="n">
         <x:v>20</x:v>
@@ -1071,7 +1071,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P8" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
@@ -1090,7 +1090,7 @@
         <x:v>drop:AV1:A1:audio:1:S262</x:v>
       </x:c>
       <x:c r="AC8" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":86.2}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":88.7}</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="96" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
         <x:v>wall</x:v>
@@ -1131,7 +1131,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M9" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 72.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 74.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N9" s="11" t="n">
         <x:v>20</x:v>
@@ -1140,7 +1140,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P9" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q9" s="9"/>
       <x:c r="R9" s="9"/>
@@ -1159,7 +1159,7 @@
         <x:v>drop:AV1:A1:audio:-1:S263</x:v>
       </x:c>
       <x:c r="AC9" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":72.2}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":74.1}</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="96" customHeight="1">
@@ -1179,13 +1179,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
         <x:v>wall</x:v>
@@ -1200,7 +1200,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M10" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 73.5 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 76 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N10" s="11" t="n">
         <x:v>20</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P10" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q10" s="9"/>
       <x:c r="R10" s="9"/>
@@ -1228,7 +1228,7 @@
         <x:v>drop:AV1:A1:audio:1:S264</x:v>
       </x:c>
       <x:c r="AC10" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":73.5}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":76}</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96" customHeight="1">
@@ -1248,13 +1248,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
         <x:v>wall</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M11" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 59.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 61.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N11" s="11" t="n">
         <x:v>20</x:v>
@@ -1278,7 +1278,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P11" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q11" s="9"/>
       <x:c r="R11" s="9"/>
@@ -1297,7 +1297,7 @@
         <x:v>drop:AV1:A1:audio:-1:S265</x:v>
       </x:c>
       <x:c r="AC11" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":59.2}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":61.2}</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="96" customHeight="1">
@@ -1317,13 +1317,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I12" s="8" t="str">
         <x:v>wall</x:v>
@@ -1338,7 +1338,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M12" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 60.8 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 63.5 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N12" s="11" t="n">
         <x:v>20</x:v>
@@ -1347,7 +1347,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P12" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q12" s="9"/>
       <x:c r="R12" s="9"/>
@@ -1366,7 +1366,7 @@
         <x:v>drop:AV1:A1:audio:1:S266</x:v>
       </x:c>
       <x:c r="AC12" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":60.8}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":63.5}</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="96" customHeight="1">
@@ -1386,13 +1386,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I13" s="8" t="str">
         <x:v>wall</x:v>
@@ -1407,7 +1407,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M13" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 46.3 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 48.3 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N13" s="11" t="n">
         <x:v>20</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P13" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q13" s="9"/>
       <x:c r="R13" s="9"/>
@@ -1435,7 +1435,7 @@
         <x:v>drop:AV1:A1:audio:-1:S267</x:v>
       </x:c>
       <x:c r="AC13" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":46.3}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":48.3}</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="96" customHeight="1">
@@ -1455,13 +1455,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
         <x:v>wall</x:v>
@@ -1476,7 +1476,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M14" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 48.3 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 51.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N14" s="11" t="n">
         <x:v>20</x:v>
@@ -1485,7 +1485,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P14" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q14" s="9"/>
       <x:c r="R14" s="9"/>
@@ -1504,7 +1504,7 @@
         <x:v>drop:AV1:A1:audio:1:S268</x:v>
       </x:c>
       <x:c r="AC14" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":48.3}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":51.2}</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="96" customHeight="1">
@@ -1524,13 +1524,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I15" s="8" t="str">
         <x:v>wall</x:v>
@@ -1545,7 +1545,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M15" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 33.5 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 35.5 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N15" s="11" t="n">
         <x:v>20</x:v>
@@ -1554,7 +1554,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P15" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q15" s="9"/>
       <x:c r="R15" s="9"/>
@@ -1573,7 +1573,7 @@
         <x:v>drop:AV1:A1:audio:-1:S269</x:v>
       </x:c>
       <x:c r="AC15" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":33.5}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":35.5}</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="96" customHeight="1">
@@ -1593,13 +1593,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I16" s="8" t="str">
         <x:v>wall</x:v>
@@ -1614,7 +1614,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M16" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 36 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 39.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N16" s="11" t="n">
         <x:v>20</x:v>
@@ -1623,7 +1623,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P16" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q16" s="9"/>
       <x:c r="R16" s="9"/>
@@ -1642,7 +1642,7 @@
         <x:v>drop:AV1:A1:audio:1:S270</x:v>
       </x:c>
       <x:c r="AC16" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":36}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":39.1}</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="96" customHeight="1">
@@ -1662,13 +1662,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I17" s="8" t="str">
         <x:v>wall</x:v>
@@ -1683,7 +1683,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M17" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 20.6 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 22.6 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N17" s="11" t="n">
         <x:v>20</x:v>
@@ -1692,7 +1692,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="P17" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q17" s="9"/>
       <x:c r="R17" s="9"/>
@@ -1711,7 +1711,7 @@
         <x:v>drop:AV1:A1:audio:-1:S271</x:v>
       </x:c>
       <x:c r="AC17" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":20.6}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":22.6}</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="96" customHeight="1">
@@ -1731,13 +1731,13 @@
         <x:v>A1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I18" s="8" t="str">
         <x:v>wall</x:v>
@@ -1752,7 +1752,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M18" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 24.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 27.8 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N18" s="11" t="n">
         <x:v>20</x:v>
@@ -1761,7 +1761,7 @@
         <x:v>-140</x:v>
       </x:c>
       <x:c r="P18" s="11" t="n">
-        <x:v>-18</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="Q18" s="9"/>
       <x:c r="R18" s="9"/>
@@ -1780,7 +1780,7 @@
         <x:v>drop:AV1:A1:audio:1:S272</x:v>
       </x:c>
       <x:c r="AC18" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":24.1}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":27.8}</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="96" customHeight="1">
@@ -2856,7 +2856,7 @@
         <x:v>420 × 400 × 400</x:v>
       </x:c>
       <x:c r="M34" s="8" t="str">
-        <x:v>30 W audio rating · Passive / amplifier output · 33.6 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>30 W audio rating · Passive / amplifier output · 33.8 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N34" s="11" t="n">
         <x:v>10</x:v>
@@ -2884,7 +2884,7 @@
         <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="AC34" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":33.6}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":33.8}</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="96" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc59699bc3e6b471e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d339d76e7844d5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3481,7 +3481,7 @@
       </x:c>
       <x:c r="I7" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A7,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>65.21813031117918</x:v>
+        <x:v>65.64813031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -3540,14 +3540,14 @@
       </x:c>
       <x:c r="I8" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A8,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
-        <x:v>65.21813031117918</x:v>
+        <x:v>65.64813031117919</x:v>
       </x:c>
       <x:c r="K8" s="11" t="n">
         <x:f>IF(L8="Full home run",I8+J8,"")</x:f>
-        <x:v>67.60813031117918</x:v>
+        <x:v>67.85813031117918</x:v>
       </x:c>
       <x:c r="L8" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3604,14 +3604,14 @@
       </x:c>
       <x:c r="I9" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A9,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
-        <x:v>60.71813031117919</x:v>
+        <x:v>61.14813031117919</x:v>
       </x:c>
       <x:c r="K9" s="11" t="n">
         <x:f>IF(L9="Full home run",I9+J9,"")</x:f>
-        <x:v>63.10813031117919</x:v>
+        <x:v>63.35813031117919</x:v>
       </x:c>
       <x:c r="L9" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3668,14 +3668,14 @@
       </x:c>
       <x:c r="I10" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A10,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J10" s="11" t="n">
-        <x:v>56.21813031117919</x:v>
+        <x:v>56.64813031117919</x:v>
       </x:c>
       <x:c r="K10" s="11" t="n">
         <x:f>IF(L10="Full home run",I10+J10,"")</x:f>
-        <x:v>58.60813031117919</x:v>
+        <x:v>58.85813031117919</x:v>
       </x:c>
       <x:c r="L10" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3732,14 +3732,14 @@
       </x:c>
       <x:c r="I11" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A11,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J11" s="11" t="n">
-        <x:v>51.71813031117919</x:v>
+        <x:v>52.14813031117919</x:v>
       </x:c>
       <x:c r="K11" s="11" t="n">
         <x:f>IF(L11="Full home run",I11+J11,"")</x:f>
-        <x:v>54.10813031117919</x:v>
+        <x:v>54.35813031117919</x:v>
       </x:c>
       <x:c r="L11" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3796,14 +3796,14 @@
       </x:c>
       <x:c r="I12" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A12,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J12" s="11" t="n">
-        <x:v>47.21813031117919</x:v>
+        <x:v>47.64813031117919</x:v>
       </x:c>
       <x:c r="K12" s="11" t="n">
         <x:f>IF(L12="Full home run",I12+J12,"")</x:f>
-        <x:v>49.60813031117919</x:v>
+        <x:v>49.85813031117919</x:v>
       </x:c>
       <x:c r="L12" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3860,14 +3860,14 @@
       </x:c>
       <x:c r="I13" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A13,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J13" s="11" t="n">
-        <x:v>42.71813031117919</x:v>
+        <x:v>43.14813031117919</x:v>
       </x:c>
       <x:c r="K13" s="11" t="n">
         <x:f>IF(L13="Full home run",I13+J13,"")</x:f>
-        <x:v>45.10813031117919</x:v>
+        <x:v>45.35813031117919</x:v>
       </x:c>
       <x:c r="L13" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -3994,7 +3994,7 @@
       </x:c>
       <x:c r="I15" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A15,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>58.61813031117919</x:v>
+        <x:v>59.04813031117919</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
       <x:c r="K15" s="11" t="str">
@@ -4053,14 +4053,14 @@
       </x:c>
       <x:c r="I16" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A16,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n">
-        <x:v>58.61813031117919</x:v>
+        <x:v>59.04813031117919</x:v>
       </x:c>
       <x:c r="K16" s="11" t="n">
         <x:f>IF(L16="Full home run",I16+J16,"")</x:f>
-        <x:v>61.008130311179194</x:v>
+        <x:v>61.258130311179194</x:v>
       </x:c>
       <x:c r="L16" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4117,14 +4117,14 @@
       </x:c>
       <x:c r="I17" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A17,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J17" s="11" t="n">
-        <x:v>54.11813031117919</x:v>
+        <x:v>54.54813031117919</x:v>
       </x:c>
       <x:c r="K17" s="11" t="n">
         <x:f>IF(L17="Full home run",I17+J17,"")</x:f>
-        <x:v>56.508130311179194</x:v>
+        <x:v>56.758130311179194</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4181,14 +4181,14 @@
       </x:c>
       <x:c r="I18" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A18,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J18" s="11" t="n">
-        <x:v>49.61813031117919</x:v>
+        <x:v>50.04813031117919</x:v>
       </x:c>
       <x:c r="K18" s="11" t="n">
         <x:f>IF(L18="Full home run",I18+J18,"")</x:f>
-        <x:v>52.008130311179194</x:v>
+        <x:v>52.258130311179194</x:v>
       </x:c>
       <x:c r="L18" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4245,14 +4245,14 @@
       </x:c>
       <x:c r="I19" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A19,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J19" s="11" t="n">
-        <x:v>45.11813031117919</x:v>
+        <x:v>45.54813031117919</x:v>
       </x:c>
       <x:c r="K19" s="11" t="n">
         <x:f>IF(L19="Full home run",I19+J19,"")</x:f>
-        <x:v>47.508130311179194</x:v>
+        <x:v>47.758130311179194</x:v>
       </x:c>
       <x:c r="L19" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4309,14 +4309,14 @@
       </x:c>
       <x:c r="I20" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A20,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J20" s="11" t="n">
-        <x:v>40.61813031117919</x:v>
+        <x:v>41.04813031117919</x:v>
       </x:c>
       <x:c r="K20" s="11" t="n">
         <x:f>IF(L20="Full home run",I20+J20,"")</x:f>
-        <x:v>43.008130311179194</x:v>
+        <x:v>43.258130311179194</x:v>
       </x:c>
       <x:c r="L20" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -4373,14 +4373,14 @@
       </x:c>
       <x:c r="I21" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A21,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.3899999999999997</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J21" s="11" t="n">
-        <x:v>36.11813031117919</x:v>
+        <x:v>36.54813031117919</x:v>
       </x:c>
       <x:c r="K21" s="11" t="n">
         <x:f>IF(L21="Full home run",I21+J21,"")</x:f>
-        <x:v>38.508130311179194</x:v>
+        <x:v>38.758130311179194</x:v>
       </x:c>
       <x:c r="L21" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe9378f7647e4509"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R862c95f047944809"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6633,7 +6633,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6643,7 +6643,7 @@
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:f>SQRT((C24-C23)^2+(D24-D23)^2+(E24-E23)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:v>22.93</x:v>
       </x:c>
       <x:c r="G24" s="8" t="str">
         <x:v>Current</x:v>
@@ -6657,7 +6657,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6681,7 +6681,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>3.45</x:v>
@@ -6705,17 +6705,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -6729,7 +6729,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6753,7 +6753,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>3.45</x:v>
@@ -6777,17 +6777,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
         <x:v>Current</x:v>
@@ -6801,7 +6801,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6825,7 +6825,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
         <x:v>3.45</x:v>
@@ -6849,17 +6849,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
         <x:v>Current</x:v>
@@ -6873,7 +6873,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6897,7 +6897,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
         <x:v>3.45</x:v>
@@ -6921,17 +6921,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -6945,7 +6945,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>5.55</x:v>
@@ -6969,7 +6969,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
         <x:v>3.45</x:v>
@@ -6993,17 +6993,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -7017,7 +7017,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7041,7 +7041,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
         <x:v>3.45</x:v>
@@ -7065,17 +7065,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>-7.07</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>Current</x:v>
@@ -7665,7 +7665,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C67" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7675,7 +7675,7 @@
       </x:c>
       <x:c r="F67" s="11" t="n">
         <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
-        <x:v>22.5</x:v>
+        <x:v>22.93</x:v>
       </x:c>
       <x:c r="G67" s="8" t="str">
         <x:v>Current</x:v>
@@ -7689,7 +7689,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C68" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7713,7 +7713,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C69" s="11" t="n">
-        <x:v>14.475000000000001</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
         <x:v>3.45</x:v>
@@ -7737,17 +7737,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C70" s="11" t="n">
-        <x:v>14.475</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E70" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F70" s="11" t="n">
         <x:f>SQRT((C70-C69)^2+(D70-D69)^2+(E70-E69)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G70" s="8" t="str">
         <x:v>Current</x:v>
@@ -7761,7 +7761,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C71" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7785,7 +7785,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C72" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
         <x:v>3.45</x:v>
@@ -7809,17 +7809,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C73" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E73" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F73" s="11" t="n">
         <x:f>SQRT((C73-C72)^2+(D73-D72)^2+(E73-E72)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G73" s="8" t="str">
         <x:v>Current</x:v>
@@ -7833,7 +7833,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C74" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7857,7 +7857,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C75" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
         <x:v>3.45</x:v>
@@ -7881,17 +7881,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C76" s="11" t="n">
-        <x:v>23.475</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E76" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F76" s="11" t="n">
         <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
         <x:v>Current</x:v>
@@ -7905,7 +7905,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C77" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
         <x:v>5.55</x:v>
@@ -7929,7 +7929,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C78" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
         <x:v>3.45</x:v>
@@ -7953,17 +7953,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C79" s="11" t="n">
-        <x:v>27.975</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F79" s="11" t="n">
         <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G79" s="8" t="str">
         <x:v>Current</x:v>
@@ -7977,7 +7977,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C80" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
         <x:v>5.55</x:v>
@@ -8001,7 +8001,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C81" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
         <x:v>3.45</x:v>
@@ -8025,17 +8025,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C82" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E82" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F82" s="11" t="n">
         <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G82" s="8" t="str">
         <x:v>Current</x:v>
@@ -8049,7 +8049,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C83" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
         <x:v>5.55</x:v>
@@ -8073,7 +8073,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C84" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
         <x:v>3.45</x:v>
@@ -8097,17 +8097,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C85" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="E85" s="11" t="n">
-        <x:v>7.07</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F85" s="11" t="n">
         <x:f>SQRT((C85-C84)^2+(D85-D84)^2+(E85-E84)^2)</x:f>
-        <x:v>0.29000000000000004</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G85" s="8" t="str">
         <x:v>Current</x:v>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae8a1eed35914ff7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7300a6a05ff647c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1390953555494e22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R423c28341d8a457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R8a7fb1b936c04f48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2402a66bdcb243da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R94affe3321f1472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd2de26ca86cf4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69ae0181668c4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4d9bf0acf3a34726"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
+        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d339d76e7844d5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red0012ca499d4392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R862c95f047944809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffaab2cce1724c10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7300a6a05ff647c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3a03e5e02d4be4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R94affe3321f1472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd2de26ca86cf4b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R69ae0181668c4459"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4d9bf0acf3a34726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rab6f92eaa49c4232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R06a1ffcfc9774a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5535a7158e4349a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb2ff0fc623e94ded"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
+        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
+        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red0012ca499d4392"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00fe6954cdc3401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffaab2cce1724c10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b967c9114ee4e42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3a03e5e02d4be4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220b41a9bf82436f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rab6f92eaa49c4232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R06a1ffcfc9774a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5535a7158e4349a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb2ff0fc623e94ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R79cbe39487d54ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3c574c008dfb4364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R09a096920f2544c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R745dc05752d54d2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
+        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
+        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00fe6954cdc3401e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bc7363e3154483e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b967c9114ee4e42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re553a592b0fa4fbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220b41a9bf82436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recfd8a4eb45444df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R79cbe39487d54ac4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3c574c008dfb4364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R09a096920f2544c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R745dc05752d54d2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf7de2e79b9074a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R32a53874f3474b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc70fcb3837304a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1827490854334bf7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
+        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
+        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1200,7 +1200,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M10" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 76 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 76.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N10" s="11" t="n">
         <x:v>20</x:v>
@@ -1228,7 +1228,7 @@
         <x:v>drop:AV1:A1:audio:1:S264</x:v>
       </x:c>
       <x:c r="AC10" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":76}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":76.1}</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96" customHeight="1">
@@ -1683,7 +1683,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M17" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 22.6 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 22.7 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N17" s="11" t="n">
         <x:v>20</x:v>
@@ -1711,7 +1711,7 @@
         <x:v>drop:AV1:A1:audio:-1:S271</x:v>
       </x:c>
       <x:c r="AC17" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":22.6}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":22.7}</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="96" customHeight="1">
@@ -1821,7 +1821,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M19" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 94.9 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 95 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N19" s="11" t="n">
         <x:v>20</x:v>
@@ -1849,7 +1849,7 @@
         <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="AC19" s="8" t="str">
-        <x:v>{"dim":1,"level":-9,"delayMs":94.9}</x:v>
+        <x:v>{"dim":1,"level":-9,"delayMs":95}</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="96" customHeight="1">
@@ -2028,7 +2028,7 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M22" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 37.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 37.2 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N22" s="11" t="n">
         <x:v>20</x:v>
@@ -2056,7 +2056,7 @@
         <x:v>drop:AV1:A1:audio:1:S278</x:v>
       </x:c>
       <x:c r="AC22" s="8" t="str">
-        <x:v>{"dim":1,"level":-6,"delayMs":37.1,"anchorY":4.85,"note":"ENGINEERING HOLD: two total wall speakers toward entrance (-X), raised for full fan/return-wall envelope clearance. Speech and feedback still require coordinated validation; product, concealment, fixi"}</x:v>
+        <x:v>{"dim":1,"level":-6,"delayMs":37.2,"anchorY":4.85,"note":"ENGINEERING HOLD: two total wall speakers toward entrance (-X), raised for full fan/return-wall envelope clearance. Speech and feedback still require coordinated validation; product, concealment, fixi"}</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="96" customHeight="1">
@@ -2907,7 +2907,7 @@
         <x:v>41.08</x:v>
       </x:c>
       <x:c r="G35" s="11" t="n">
-        <x:v>1.9</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="H35" s="11" t="n">
         <x:v>-2.62</x:v>
@@ -2976,7 +2976,7 @@
         <x:v>44.45</x:v>
       </x:c>
       <x:c r="G36" s="11" t="n">
-        <x:v>1.88</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="H36" s="11" t="n">
         <x:v>0.45</x:v>
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bc7363e3154483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75dd2a0d543341a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5818,14 +5818,14 @@
       </x:c>
       <x:c r="I44" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A44,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>3.579070753698968</x:v>
+        <x:v>3.6290707536989677</x:v>
       </x:c>
       <x:c r="J44" s="11" t="n">
         <x:v>11.915</x:v>
       </x:c>
       <x:c r="K44" s="11" t="n">
         <x:f>IF(L44="Full home run",I44+J44,"")</x:f>
-        <x:v>15.494070753698967</x:v>
+        <x:v>15.544070753698968</x:v>
       </x:c>
       <x:c r="L44" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5941,14 +5941,14 @@
       </x:c>
       <x:c r="I46" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$316,A46,'Route Points'!$F$7:$F$316)</x:f>
-        <x:v>2.8</x:v>
+        <x:v>2.8499999999999996</x:v>
       </x:c>
       <x:c r="J46" s="11" t="n">
         <x:v>5.744999999999996</x:v>
       </x:c>
       <x:c r="K46" s="11" t="n">
         <x:f>IF(L46="Full home run",I46+J46,"")</x:f>
-        <x:v>8.544999999999995</x:v>
+        <x:v>8.594999999999995</x:v>
       </x:c>
       <x:c r="L46" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re553a592b0fa4fbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ced598bc7594e74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13308,14 +13308,14 @@
         <x:v>41.3</x:v>
       </x:c>
       <x:c r="D302" s="11" t="n">
-        <x:v>1.81</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="E302" s="11" t="n">
         <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F302" s="11" t="n">
         <x:f>SQRT((C302-C301)^2+(D302-D301)^2+(E302-E301)^2)</x:f>
-        <x:v>1.78</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="G302" s="8" t="str">
         <x:v>Current</x:v>
@@ -13332,7 +13332,7 @@
         <x:v>41.08</x:v>
       </x:c>
       <x:c r="D303" s="11" t="n">
-        <x:v>1.7654037921880923</x:v>
+        <x:v>1.8154037921880923</x:v>
       </x:c>
       <x:c r="E303" s="11" t="n">
         <x:v>-2.62</x:v>
@@ -13356,7 +13356,7 @@
         <x:v>41.08</x:v>
       </x:c>
       <x:c r="D304" s="11" t="n">
-        <x:v>1.9</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E304" s="11" t="n">
         <x:v>-2.62</x:v>
@@ -13500,14 +13500,14 @@
         <x:v>44.45</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
-        <x:v>1.88</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="F310" s="11" t="n">
         <x:f>SQRT((C310-C309)^2+(D310-D309)^2+(E310-E309)^2)</x:f>
-        <x:v>1.8499999999999999</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="G310" s="8" t="str">
         <x:v>Current</x:v>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recfd8a4eb45444df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413a39e4613148ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf7de2e79b9074a1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R32a53874f3474b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc70fcb3837304a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1827490854334bf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1e7a90caf97d4fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7f75580b38b74a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R7b0f6e45dbc548c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R360d1db5fcc34e27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
+        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
+        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75dd2a0d543341a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2ac0d743df402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ced598bc7594e74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf29e94e156574de6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413a39e4613148ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309ce3e35dc749da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1e7a90caf97d4fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7f75580b38b74a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R7b0f6e45dbc548c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R360d1db5fcc34e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re704b09c92434306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7ff2bd5087554c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Recffdebe0f5f4cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R998d0bdd697744dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
+        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
+        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref2ac0d743df402a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b0ce4d16eca4404"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf29e94e156574de6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa9f0a8b5474133"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309ce3e35dc749da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c39f101fb17477b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re704b09c92434306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7ff2bd5087554c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Recffdebe0f5f4cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R998d0bdd697744dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7d6cbd0f4f214282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc1cd346b76ae465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R36dec813cc134b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R8a14440b4f2a44d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
+        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
+        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2125,7 +2125,7 @@
         <x:v>drop:AV1:A2:audio:-1:S279</x:v>
       </x:c>
       <x:c r="AC23" s="8" t="str">
-        <x:v>{"dim":1,"level":-7,"delayMs":88.8,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"dim":1,"level":-7,"delayMs":88.8,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="96" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>drop:AV1:A2:audio:-1:S280</x:v>
       </x:c>
       <x:c r="AC24" s="8" t="str">
-        <x:v>{"dim":1,"level":-7,"delayMs":50.9,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"dim":1,"level":-7,"delayMs":50.9,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="96" customHeight="1">
@@ -2263,7 +2263,7 @@
         <x:v>drop:AV1:A2:audio:1:S281</x:v>
       </x:c>
       <x:c r="AC25" s="8" t="str">
-        <x:v>{"dim":1,"level":-7,"delayMs":92.3,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"dim":1,"level":-7,"delayMs":92.3,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="96" customHeight="1">
@@ -2332,7 +2332,7 @@
         <x:v>drop:AV1:A2:audio:1:S282</x:v>
       </x:c>
       <x:c r="AC26" s="8" t="str">
-        <x:v>{"dim":1,"level":-7,"delayMs":56.8,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"dim":1,"level":-7,"delayMs":56.8,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="96" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b0ce4d16eca4404"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R157d07cf4e3e478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa9f0a8b5474133"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R430381b8609c497e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c39f101fb17477b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2c111aa2334176"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7d6cbd0f4f214282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc1cd346b76ae465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R36dec813cc134b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R8a14440b4f2a44d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra97e795d60a44670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re75e9a19d5004be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf87f04cdf87d4200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R99b74bbe783546bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
+        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
+        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R157d07cf4e3e478d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff34bade6d094965"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R430381b8609c497e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra865adb2428a4492"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2c111aa2334176"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7238ce2d3334648"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra97e795d60a44670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re75e9a19d5004be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf87f04cdf87d4200"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R99b74bbe783546bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rbb0d2c404db64f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf706bcd093c74561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R154efc1c805a44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R15d2b1f7c1544cca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
+        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
+        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff34bade6d094965"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R568cc343ce614d99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra865adb2428a4492"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e42878739af4381"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7238ce2d3334648"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7335b27195d14bd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rbb0d2c404db64f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf706bcd093c74561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R154efc1c805a44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R15d2b1f7c1544cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R096dd6c114864fb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0da57672bc9a4c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R89a480f500144732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R494d1e51e34a481d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
+        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
+        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R568cc343ce614d99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb79fe744cdb4c7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e42878739af4381"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0729401ab66643af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7335b27195d14bd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b4565f4f564d20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R096dd6c114864fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0da57672bc9a4c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R89a480f500144732"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R494d1e51e34a481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf54b195d72eb494c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb9f00f07e1d24f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf270a162ef634432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rca86bed77b904523"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
+        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
+        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb79fe744cdb4c7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a2b494da044cf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0729401ab66643af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2494e9b998045ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b4565f4f564d20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca428122b6c64166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf54b195d72eb494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb9f00f07e1d24f6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf270a162ef634432"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rca86bed77b904523"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8ca77b7ece9e4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4d396dd1422542fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5b32db900cfd47a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R777af6f49b904ac6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
+        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
+        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a2b494da044cf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7352f64f07cc46f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2494e9b998045ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57aaefe0044b4d85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca428122b6c64166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a1a381c72f14961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8ca77b7ece9e4288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4d396dd1422542fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5b32db900cfd47a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R777af6f49b904ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6802feb2b31a4e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R94bcfc35ae84415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Refd90ac7de534959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rbe70556e7a954b21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
+        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7352f64f07cc46f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59911086c33f462d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57aaefe0044b4d85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13da464f462f4ab5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a1a381c72f14961"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2460ae0e56a64ad4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6802feb2b31a4e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R94bcfc35ae84415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Refd90ac7de534959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rbe70556e7a954b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc5085f644e6a4999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R957f368b8df640fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb8ae331b441348c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9b7c0f4612554938"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
+        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
+        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3183,7 +3183,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59911086c33f462d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9b1eb9831d94008"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6123,7 +6123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13da464f462f4ab5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re89881c094a24576"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13663,7 +13663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2460ae0e56a64ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9256b21bdb174887"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5a626ddaa64f40e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R558c359dfadd4bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc1ae74f64f9f4b3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc5b8d295949a4975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R80d4a882bc6142f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Reb68cf8e6454466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd07d2acda7844900"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf32844ddbe6940c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
+        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
+        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4149,7 +4149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07b13e4bb9e4840"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6897406e555748df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7999,7 +7999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raffac8638d354586"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8491899aab2d4c58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16259,7 +16259,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5af26e12589476d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1c373d49d874cae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R80d4a882bc6142f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Reb68cf8e6454466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd07d2acda7844900"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf32844ddbe6940c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rce468aa958a74d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9d2f7868023540f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3a45fb732a3a4cd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R012b78b976314a6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
+        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
+        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4149,7 +4149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6897406e555748df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b7603e4e1b43c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7999,7 +7999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8491899aab2d4c58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dffebb1562a4d0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16259,7 +16259,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1c373d49d874cae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcc03b33bf864529"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rce468aa958a74d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9d2f7868023540f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3a45fb732a3a4cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R012b78b976314a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Reca08c413dd04e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfcb16dca04994202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R07baf9e066c64a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4c2b369a09ee4eda"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
+        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
+        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4149,7 +4149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b7603e4e1b43c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R731da90b58ad4877"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7999,7 +7999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dffebb1562a4d0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e256f0ae5740c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16259,7 +16259,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcc03b33bf864529"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a26321aa8540a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Reca08c413dd04e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfcb16dca04994202"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R07baf9e066c64a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4c2b369a09ee4eda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6faa3054fbd34678"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd93cbec180be4c6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3f68dc74607b4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0cc2d373db4740d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G346" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G342" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-11-01T00:50:08.502Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>b59c831ec1c00c49183c1e83c86ee8d801e0152690935057f3be6f551a8b788b</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>2a343075b78e07a39b50033e252aeaec71194df376aa048789dba03e95d6e972</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1800,7 +1800,7 @@
         <x:v>A5</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
         <x:v>2.5</x:v>
@@ -1821,16 +1821,16 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M19" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 96.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 100.4 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N19" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O19" s="11" t="n">
-        <x:v>-6.476440087185079</x:v>
+        <x:v>-15.231115445344694</x:v>
       </x:c>
       <x:c r="P19" s="11" t="n">
-        <x:v>-14.928147075735074</x:v>
+        <x:v>-31.83856467744374</x:v>
       </x:c>
       <x:c r="Q19" s="9"/>
       <x:c r="R19" s="9"/>
@@ -1849,7 +1849,7 @@
         <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="AC19" s="8" t="str">
-        <x:v>{"dim":1,"level":-9,"delayMs":96.1,"anchorY":2.5}</x:v>
+        <x:v>{"dim":1,"level":-9,"delayMs":100.4,"anchorY":2.5}</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="96" customHeight="1">
@@ -1869,7 +1869,7 @@
         <x:v>A5</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
         <x:v>2.5</x:v>
@@ -1890,16 +1890,16 @@
         <x:v>146 × 600 × 60</x:v>
       </x:c>
       <x:c r="M20" s="8" t="str">
-        <x:v>60 W audio rating · Passive / amplifier output · 97.6 ms delay. Passive speaker; audio rating is not mains demand</x:v>
+        <x:v>60 W audio rating · Passive / amplifier output · 102.1 ms delay. Passive speaker; audio rating is not mains demand</x:v>
       </x:c>
       <x:c r="N20" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="O20" s="11" t="n">
-        <x:v>6.476440087185079</x:v>
+        <x:v>15.231115445344694</x:v>
       </x:c>
       <x:c r="P20" s="11" t="n">
-        <x:v>-14.928147075735074</x:v>
+        <x:v>-31.83856467744374</x:v>
       </x:c>
       <x:c r="Q20" s="9"/>
       <x:c r="R20" s="9"/>
@@ -1918,7 +1918,7 @@
         <x:v>drop:AV1:A5:audio:1:S274</x:v>
       </x:c>
       <x:c r="AC20" s="8" t="str">
-        <x:v>{"dim":1,"level":-9,"delayMs":97.6,"anchorY":2.5}</x:v>
+        <x:v>{"dim":1,"level":-9,"delayMs":102.1,"anchorY":2.5}</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="96" customHeight="1">
@@ -4149,7 +4149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R731da90b58ad4877"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0667b3efbad41db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4446,7 +4446,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A7,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A7,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>65.64813031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
@@ -4505,7 +4505,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A8,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A8,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
@@ -4569,7 +4569,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A9,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A9,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="n">
@@ -4633,7 +4633,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A10,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A10,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J10" s="11" t="n">
@@ -4697,7 +4697,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A11,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A11,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J11" s="11" t="n">
@@ -4761,7 +4761,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A12,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A12,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J12" s="11" t="n">
@@ -4825,7 +4825,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A13,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A13,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J13" s="11" t="n">
@@ -4889,7 +4889,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A14,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A14,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>8.040692614226739</x:v>
       </x:c>
       <x:c r="J14" s="11" t="n">
@@ -4959,7 +4959,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A15,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A15,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>59.04813031117919</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
@@ -5018,7 +5018,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A16,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A16,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n">
@@ -5082,7 +5082,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A17,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A17,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J17" s="11" t="n">
@@ -5146,7 +5146,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A18,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A18,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J18" s="11" t="n">
@@ -5210,7 +5210,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A19,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A19,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J19" s="11" t="n">
@@ -5274,7 +5274,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A20,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A20,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J20" s="11" t="n">
@@ -5338,7 +5338,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A21,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A21,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.16</x:v>
       </x:c>
       <x:c r="J21" s="11" t="n">
@@ -5402,7 +5402,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A22,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A22,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>8.040692614226739</x:v>
       </x:c>
       <x:c r="J22" s="11" t="n">
@@ -5466,8 +5466,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A23,'Route Points'!$F$7:$F$346)</x:f>
-        <x:v>77.07013031117918</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A23,'Route Points'!$F$7:$F$342)</x:f>
+        <x:v>74.24513031117918</x:v>
       </x:c>
       <x:c r="J23" s="11"/>
       <x:c r="K23" s="11" t="str">
@@ -5525,15 +5525,15 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A24,'Route Points'!$F$7:$F$346)</x:f>
-        <x:v>11.918705875926424</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A24,'Route Points'!$F$7:$F$342)</x:f>
+        <x:v>13.208</x:v>
       </x:c>
       <x:c r="J24" s="11" t="n">
-        <x:v>77.07013031117918</x:v>
+        <x:v>74.24513031117918</x:v>
       </x:c>
       <x:c r="K24" s="11" t="n">
         <x:f>IF(L24="Full home run",I24+J24,"")</x:f>
-        <x:v>88.9888361871056</x:v>
+        <x:v>87.45313031117918</x:v>
       </x:c>
       <x:c r="L24" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5546,7 +5546,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P24" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Proposed underfloor return; this location needs a concealed local riser / connection design.</x:v>
       </x:c>
       <x:c r="Q24" s="9"/>
       <x:c r="R24" s="9"/>
@@ -5589,8 +5589,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A25,'Route Points'!$F$7:$F$346)</x:f>
-        <x:v>70.47013031117918</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A25,'Route Points'!$F$7:$F$342)</x:f>
+        <x:v>67.64513031117919</x:v>
       </x:c>
       <x:c r="J25" s="11"/>
       <x:c r="K25" s="11" t="str">
@@ -5648,15 +5648,15 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A26,'Route Points'!$F$7:$F$346)</x:f>
-        <x:v>11.918705875926424</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A26,'Route Points'!$F$7:$F$342)</x:f>
+        <x:v>13.208</x:v>
       </x:c>
       <x:c r="J26" s="11" t="n">
-        <x:v>70.47013031117918</x:v>
+        <x:v>67.64513031117919</x:v>
       </x:c>
       <x:c r="K26" s="11" t="n">
         <x:f>IF(L26="Full home run",I26+J26,"")</x:f>
-        <x:v>82.3888361871056</x:v>
+        <x:v>80.85313031117919</x:v>
       </x:c>
       <x:c r="L26" s="8" t="str">
         <x:v>Full home run</x:v>
@@ -5669,7 +5669,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P26" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Proposed underfloor return; this location needs a concealed local riser / connection design.</x:v>
       </x:c>
       <x:c r="Q26" s="9"/>
       <x:c r="R26" s="9"/>
@@ -5720,7 +5720,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I27" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A27,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A27,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>70.15613031117918</x:v>
       </x:c>
       <x:c r="J27" s="11"/>
@@ -5779,7 +5779,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A28,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A28,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J28" s="11" t="n">
@@ -5843,7 +5843,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I29" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A29,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A29,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J29" s="11" t="n">
@@ -5907,7 +5907,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I30" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A30,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A30,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J30" s="11" t="n">
@@ -5971,7 +5971,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I31" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A31,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A31,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J31" s="11" t="n">
@@ -6035,7 +6035,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I32" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A32,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A32,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J32" s="11" t="n">
@@ -6099,7 +6099,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A33,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A33,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J33" s="11" t="n">
@@ -6163,7 +6163,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A34,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A34,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J34" s="11" t="n">
@@ -6227,7 +6227,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A35,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A35,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J35" s="11" t="n">
@@ -6291,7 +6291,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A36,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A36,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J36" s="11" t="n">
@@ -6363,7 +6363,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I37" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A37,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A37,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>63.55613031117918</x:v>
       </x:c>
       <x:c r="J37" s="11"/>
@@ -6422,7 +6422,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I38" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A38,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A38,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J38" s="11" t="n">
@@ -6486,7 +6486,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I39" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A39,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A39,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J39" s="11" t="n">
@@ -6550,7 +6550,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I40" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A40,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A40,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J40" s="11" t="n">
@@ -6614,7 +6614,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I41" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A41,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A41,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J41" s="11" t="n">
@@ -6678,7 +6678,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I42" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A42,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A42,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J42" s="11" t="n">
@@ -6742,7 +6742,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I43" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A43,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A43,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J43" s="11" t="n">
@@ -6806,7 +6806,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I44" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A44,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A44,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J44" s="11" t="n">
@@ -6870,7 +6870,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I45" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A45,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A45,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J45" s="11" t="n">
@@ -6934,7 +6934,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I46" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A46,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A46,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.951999999999999</x:v>
       </x:c>
       <x:c r="J46" s="11" t="n">
@@ -7001,7 +7001,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I47" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A47,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A47,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>77.35913031117919</x:v>
       </x:c>
       <x:c r="J47" s="11"/>
@@ -7060,7 +7060,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I48" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A48,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A48,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>6.996000000000001</x:v>
       </x:c>
       <x:c r="J48" s="11" t="n">
@@ -7124,7 +7124,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I49" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A49,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A49,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>11.522</x:v>
       </x:c>
       <x:c r="J49" s="11" t="n">
@@ -7188,7 +7188,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I50" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A50,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A50,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J50" s="11" t="n">
@@ -7252,7 +7252,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I51" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A51,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A51,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J51" s="11" t="n">
@@ -7319,7 +7319,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I52" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A52,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A52,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>70.75913031117919</x:v>
       </x:c>
       <x:c r="J52" s="11"/>
@@ -7378,7 +7378,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I53" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A53,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A53,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>6.996000000000001</x:v>
       </x:c>
       <x:c r="J53" s="11" t="n">
@@ -7442,7 +7442,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A54,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A54,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>11.522</x:v>
       </x:c>
       <x:c r="J54" s="11" t="n">
@@ -7506,7 +7506,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A55,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A55,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J55" s="11" t="n">
@@ -7570,7 +7570,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A56,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A56,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>5.694172388861077</x:v>
       </x:c>
       <x:c r="J56" s="11" t="n">
@@ -7634,7 +7634,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I57" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A57,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A57,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>11.915</x:v>
       </x:c>
       <x:c r="J57" s="11"/>
@@ -7693,7 +7693,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A58,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A58,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>3.6290707536989677</x:v>
       </x:c>
       <x:c r="J58" s="11" t="n">
@@ -7757,7 +7757,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A59,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A59,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>5.744999999999996</x:v>
       </x:c>
       <x:c r="J59" s="11"/>
@@ -7816,7 +7816,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I60" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A60,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A60,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>2.8499999999999996</x:v>
       </x:c>
       <x:c r="J60" s="11" t="n">
@@ -7880,7 +7880,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I61" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A61,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A61,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>9.193150773195871</x:v>
       </x:c>
       <x:c r="J61" s="11" t="n">
@@ -7944,7 +7944,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I62" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$346,A62,'Route Points'!$F$7:$F$346)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$342,A62,'Route Points'!$F$7:$F$342)</x:f>
         <x:v>9.193150773195871</x:v>
       </x:c>
       <x:c r="J62" s="11" t="n">
@@ -7999,7 +7999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e256f0ae5740c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafdb4713dc154317"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10573,7 +10573,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C110" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
         <x:v>5.518</x:v>
@@ -10583,7 +10583,7 @@
       </x:c>
       <x:c r="F110" s="11" t="n">
         <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G110" s="8" t="str">
         <x:v>Current</x:v>
@@ -10591,13 +10591,13 @@
     </x:row>
     <x:row r="111" ht="32" customHeight="1">
       <x:c r="A111" s="8" t="str">
-        <x:v>trunk:AV1:A5:audio:-1</x:v>
+        <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="B111" s="8" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C111" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
         <x:v>5.518</x:v>
@@ -10606,8 +10606,8 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F111" s="11" t="n">
-        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
-        <x:v>2.82</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G111" s="8" t="str">
         <x:v>Current</x:v>
@@ -10618,20 +10618,20 @@
         <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="B112" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C112" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>5.518</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E112" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F112" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C112-C111)^2+(D112-D111)^2+(E112-E111)^2)</x:f>
+        <x:v>5.958</x:v>
       </x:c>
       <x:c r="G112" s="8" t="str">
         <x:v>Current</x:v>
@@ -10642,20 +10642,20 @@
         <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="B113" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C113" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E113" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.05</x:v>
       </x:c>
       <x:c r="F113" s="11" t="n">
         <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
-        <x:v>2.1537058759264234</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G113" s="8" t="str">
         <x:v>Current</x:v>
@@ -10666,20 +10666,20 @@
         <x:v>drop:AV1:A5:audio:-1:S273</x:v>
       </x:c>
       <x:c r="B114" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C114" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D114" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="E114" s="11" t="n">
         <x:v>-3.05</x:v>
       </x:c>
       <x:c r="F114" s="11" t="n">
         <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="G114" s="8" t="str">
         <x:v>Current</x:v>
@@ -10687,23 +10687,23 @@
     </x:row>
     <x:row r="115" ht="32" customHeight="1">
       <x:c r="A115" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:-1:S273</x:v>
+        <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B115" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C115" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D115" s="11" t="n">
-        <x:v>2.5</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E115" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F115" s="11" t="n">
-        <x:f>SQRT((C115-C114)^2+(D115-D114)^2+(E115-E114)^2)</x:f>
-        <x:v>5.15</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="8" t="str">
         <x:v>Current</x:v>
@@ -10711,23 +10711,23 @@
     </x:row>
     <x:row r="116" ht="32" customHeight="1">
       <x:c r="A116" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:-1:S273</x:v>
+        <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B116" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C116" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D116" s="11" t="n">
-        <x:v>2.5</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E116" s="11" t="n">
-        <x:v>-3.05</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F116" s="11" t="n">
         <x:f>SQRT((C116-C115)^2+(D116-D115)^2+(E116-E115)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G116" s="8" t="str">
         <x:v>Current</x:v>
@@ -10738,20 +10738,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B117" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C117" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D117" s="11" t="n">
         <x:v>0.95</x:v>
       </x:c>
       <x:c r="E117" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F117" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C117-C116)^2+(D117-D116)^2+(E117-E116)^2)</x:f>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G117" s="8" t="str">
         <x:v>Current</x:v>
@@ -10762,20 +10762,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B118" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C118" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D118" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E118" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F118" s="11" t="n">
         <x:f>SQRT((C118-C117)^2+(D118-D117)^2+(E118-E117)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="G118" s="8" t="str">
         <x:v>Current</x:v>
@@ -10786,20 +10786,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B119" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C119" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D119" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E119" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F119" s="11" t="n">
         <x:f>SQRT((C119-C118)^2+(D119-D118)^2+(E119-E118)^2)</x:f>
-        <x:v>0.8400000000000003</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G119" s="8" t="str">
         <x:v>Current</x:v>
@@ -10810,20 +10810,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B120" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C120" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D120" s="11" t="n">
         <x:v>4.33</x:v>
       </x:c>
       <x:c r="E120" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F120" s="11" t="n">
         <x:f>SQRT((C120-C119)^2+(D120-D119)^2+(E120-E119)^2)</x:f>
-        <x:v>3.38</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G120" s="8" t="str">
         <x:v>Current</x:v>
@@ -10834,20 +10834,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B121" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C121" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D121" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E121" s="11" t="n">
         <x:v>3.3</x:v>
       </x:c>
       <x:c r="F121" s="11" t="n">
         <x:f>SQRT((C121-C120)^2+(D121-D120)^2+(E121-E120)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>1.1879999999999997</x:v>
       </x:c>
       <x:c r="G121" s="8" t="str">
         <x:v>Current</x:v>
@@ -10858,20 +10858,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B122" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C122" s="11" t="n">
         <x:v>53.016</x:v>
       </x:c>
       <x:c r="D122" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E122" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F122" s="11" t="n">
         <x:f>SQRT((C122-C121)^2+(D122-D121)^2+(E122-E121)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G122" s="8" t="str">
         <x:v>Current</x:v>
@@ -10882,20 +10882,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B123" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C123" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D123" s="11" t="n">
         <x:v>5.518</x:v>
       </x:c>
       <x:c r="E123" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F123" s="11" t="n">
         <x:f>SQRT((C123-C122)^2+(D123-D122)^2+(E123-E122)^2)</x:f>
-        <x:v>1.1879999999999997</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G123" s="8" t="str">
         <x:v>Current</x:v>
@@ -10906,20 +10906,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B124" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C124" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D124" s="11" t="n">
-        <x:v>5.518</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E124" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F124" s="11" t="n">
         <x:f>SQRT((C124-C123)^2+(D124-D123)^2+(E124-E123)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G124" s="8" t="str">
         <x:v>Current</x:v>
@@ -10930,20 +10930,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B125" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C125" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D125" s="11" t="n">
-        <x:v>5.518</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E125" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F125" s="11" t="n">
         <x:f>SQRT((C125-C124)^2+(D125-D124)^2+(E125-E124)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G125" s="8" t="str">
         <x:v>Current</x:v>
@@ -10954,20 +10954,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B126" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C126" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D126" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E126" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F126" s="11" t="n">
         <x:f>SQRT((C126-C125)^2+(D126-D125)^2+(E126-E125)^2)</x:f>
-        <x:v>1.5220000000000002</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G126" s="8" t="str">
         <x:v>Current</x:v>
@@ -10978,20 +10978,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B127" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C127" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D127" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E127" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F127" s="11" t="n">
         <x:f>SQRT((C127-C126)^2+(D127-D126)^2+(E127-E126)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G127" s="8" t="str">
         <x:v>Current</x:v>
@@ -11002,20 +11002,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B128" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C128" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D128" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E128" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F128" s="11" t="n">
         <x:f>SQRT((C128-C127)^2+(D128-D127)^2+(E128-E127)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G128" s="8" t="str">
         <x:v>Current</x:v>
@@ -11026,20 +11026,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B129" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C129" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D129" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E129" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F129" s="11" t="n">
         <x:f>SQRT((C129-C128)^2+(D129-D128)^2+(E129-E128)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G129" s="8" t="str">
         <x:v>Current</x:v>
@@ -11050,20 +11050,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B130" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C130" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D130" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E130" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F130" s="11" t="n">
         <x:f>SQRT((C130-C129)^2+(D130-D129)^2+(E130-E129)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G130" s="8" t="str">
         <x:v>Current</x:v>
@@ -11074,20 +11074,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B131" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C131" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D131" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E131" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F131" s="11" t="n">
         <x:f>SQRT((C131-C130)^2+(D131-D130)^2+(E131-E130)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>1.5220000000000002</x:v>
       </x:c>
       <x:c r="G131" s="8" t="str">
         <x:v>Current</x:v>
@@ -11098,20 +11098,20 @@
         <x:v>trunk:AV1:A5:audio:1</x:v>
       </x:c>
       <x:c r="B132" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C132" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D132" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.518</x:v>
       </x:c>
       <x:c r="E132" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F132" s="11" t="n">
         <x:f>SQRT((C132-C131)^2+(D132-D131)^2+(E132-E131)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>31.495</x:v>
       </x:c>
       <x:c r="G132" s="8" t="str">
         <x:v>Current</x:v>
@@ -11119,13 +11119,13 @@
     </x:row>
     <x:row r="133" ht="32" customHeight="1">
       <x:c r="A133" s="8" t="str">
-        <x:v>trunk:AV1:A5:audio:1</x:v>
+        <x:v>drop:AV1:A5:audio:1:S274</x:v>
       </x:c>
       <x:c r="B133" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C133" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D133" s="11" t="n">
         <x:v>5.518</x:v>
@@ -11134,8 +11134,8 @@
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F133" s="11" t="n">
-        <x:f>SQRT((C133-C132)^2+(D133-D132)^2+(E133-E132)^2)</x:f>
-        <x:v>1.5220000000000002</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G133" s="8" t="str">
         <x:v>Current</x:v>
@@ -11143,23 +11143,23 @@
     </x:row>
     <x:row r="134" ht="32" customHeight="1">
       <x:c r="A134" s="8" t="str">
-        <x:v>trunk:AV1:A5:audio:1</x:v>
+        <x:v>drop:AV1:A5:audio:1:S274</x:v>
       </x:c>
       <x:c r="B134" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C134" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="D134" s="11" t="n">
-        <x:v>5.518</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E134" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F134" s="11" t="n">
         <x:f>SQRT((C134-C133)^2+(D134-D133)^2+(E134-E133)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>5.958</x:v>
       </x:c>
       <x:c r="G134" s="8" t="str">
         <x:v>Current</x:v>
@@ -11167,23 +11167,23 @@
     </x:row>
     <x:row r="135" ht="32" customHeight="1">
       <x:c r="A135" s="8" t="str">
-        <x:v>trunk:AV1:A5:audio:1</x:v>
+        <x:v>drop:AV1:A5:audio:1:S274</x:v>
       </x:c>
       <x:c r="B135" s="8" t="n">
-        <x:v>19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C135" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>5.4799999999999995</x:v>
       </x:c>
       <x:c r="D135" s="11" t="n">
-        <x:v>5.518</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="E135" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="F135" s="11" t="n">
         <x:f>SQRT((C135-C134)^2+(D135-D134)^2+(E135-E134)^2)</x:f>
-        <x:v>2.82</x:v>
+        <x:v>4.3100000000000005</x:v>
       </x:c>
       <x:c r="G135" s="8" t="str">
         <x:v>Current</x:v>
@@ -11194,68 +11194,68 @@
         <x:v>drop:AV1:A5:audio:1:S274</x:v>
       </x:c>
       <x:c r="B136" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C136" s="11" t="n">
+        <x:v>5.4799999999999995</x:v>
+      </x:c>
+      <x:c r="D136" s="11" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="E136" s="11" t="n">
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="F136" s="11" t="n">
+        <x:f>SQRT((C136-C135)^2+(D136-D135)^2+(E136-E135)^2)</x:f>
+        <x:v>2.94</x:v>
+      </x:c>
+      <x:c r="G136" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="32" customHeight="1">
+      <x:c r="A137" s="8" t="str">
+        <x:v>trunk:AV1:A2:audio:-1</x:v>
+      </x:c>
+      <x:c r="B137" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C136" s="11" t="n">
-        <x:v>2.655</x:v>
-      </x:c>
-      <x:c r="D136" s="11" t="n">
-        <x:v>5.518</x:v>
-      </x:c>
-      <x:c r="E136" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F136" s="11" t="n">
+      <x:c r="C137" s="11" t="n">
+        <x:v>49.275</x:v>
+      </x:c>
+      <x:c r="D137" s="11" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="E137" s="11" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="F137" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G136" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="32" customHeight="1">
-      <x:c r="A137" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:1:S274</x:v>
-      </x:c>
-      <x:c r="B137" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C137" s="11" t="n">
-        <x:v>2.35</x:v>
-      </x:c>
-      <x:c r="D137" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E137" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F137" s="11" t="n">
-        <x:f>SQRT((C137-C136)^2+(D137-D136)^2+(E137-E136)^2)</x:f>
-        <x:v>2.1537058759264234</x:v>
-      </x:c>
       <x:c r="G137" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="32" customHeight="1">
       <x:c r="A138" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:1:S274</x:v>
+        <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B138" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C138" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D138" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E138" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F138" s="11" t="n">
         <x:f>SQRT((C138-C137)^2+(D138-D137)^2+(E138-E137)^2)</x:f>
-        <x:v>4.3100000000000005</x:v>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G138" s="8" t="str">
         <x:v>Current</x:v>
@@ -11263,23 +11263,23 @@
     </x:row>
     <x:row r="139" ht="32" customHeight="1">
       <x:c r="A139" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:1:S274</x:v>
+        <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B139" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C139" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D139" s="11" t="n">
-        <x:v>2.5</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E139" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F139" s="11" t="n">
         <x:f>SQRT((C139-C138)^2+(D139-D138)^2+(E139-E138)^2)</x:f>
-        <x:v>5.15</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G139" s="8" t="str">
         <x:v>Current</x:v>
@@ -11287,23 +11287,23 @@
     </x:row>
     <x:row r="140" ht="32" customHeight="1">
       <x:c r="A140" s="8" t="str">
-        <x:v>drop:AV1:A5:audio:1:S274</x:v>
+        <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B140" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C140" s="11" t="n">
-        <x:v>2.655</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D140" s="11" t="n">
-        <x:v>2.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E140" s="11" t="n">
-        <x:v>3.05</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F140" s="11" t="n">
         <x:f>SQRT((C140-C139)^2+(D140-D139)^2+(E140-E139)^2)</x:f>
-        <x:v>0.3049999999999997</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="G140" s="8" t="str">
         <x:v>Current</x:v>
@@ -11314,20 +11314,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B141" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C141" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D141" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E141" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F141" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C141-C140)^2+(D141-D140)^2+(E141-E140)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
         <x:v>Current</x:v>
@@ -11338,20 +11338,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B142" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C142" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D142" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E142" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F142" s="11" t="n">
         <x:f>SQRT((C142-C141)^2+(D142-D141)^2+(E142-E141)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G142" s="8" t="str">
         <x:v>Current</x:v>
@@ -11362,20 +11362,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B143" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C143" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D143" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E143" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F143" s="11" t="n">
         <x:f>SQRT((C143-C142)^2+(D143-D142)^2+(E143-E142)^2)</x:f>
-        <x:v>0.8400000000000003</x:v>
+        <x:v>1.2119999999999997</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
         <x:v>Current</x:v>
@@ -11386,20 +11386,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B144" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C144" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D144" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E144" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F144" s="11" t="n">
         <x:f>SQRT((C144-C143)^2+(D144-D143)^2+(E144-E143)^2)</x:f>
-        <x:v>3.38</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G144" s="8" t="str">
         <x:v>Current</x:v>
@@ -11410,20 +11410,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B145" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C145" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D145" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E145" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F145" s="11" t="n">
         <x:f>SQRT((C145-C144)^2+(D145-D144)^2+(E145-E144)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G145" s="8" t="str">
         <x:v>Current</x:v>
@@ -11434,20 +11434,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B146" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C146" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D146" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E146" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F146" s="11" t="n">
         <x:f>SQRT((C146-C145)^2+(D146-D145)^2+(E146-E145)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G146" s="8" t="str">
         <x:v>Current</x:v>
@@ -11458,20 +11458,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B147" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C147" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D147" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E147" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F147" s="11" t="n">
         <x:f>SQRT((C147-C146)^2+(D147-D146)^2+(E147-E146)^2)</x:f>
-        <x:v>1.2119999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
         <x:v>Current</x:v>
@@ -11482,20 +11482,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B148" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C148" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D148" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E148" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F148" s="11" t="n">
         <x:f>SQRT((C148-C147)^2+(D148-D147)^2+(E148-E147)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G148" s="8" t="str">
         <x:v>Current</x:v>
@@ -11506,20 +11506,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B149" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C149" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D149" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E149" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F149" s="11" t="n">
         <x:f>SQRT((C149-C148)^2+(D149-D148)^2+(E149-E148)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G149" s="8" t="str">
         <x:v>Current</x:v>
@@ -11530,20 +11530,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B150" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C150" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D150" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E150" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F150" s="11" t="n">
         <x:f>SQRT((C150-C149)^2+(D150-D149)^2+(E150-E149)^2)</x:f>
-        <x:v>1.4980000000000002</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G150" s="8" t="str">
         <x:v>Current</x:v>
@@ -11554,10 +11554,10 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B151" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C151" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D151" s="11" t="n">
         <x:v>7.04</x:v>
@@ -11567,7 +11567,7 @@
       </x:c>
       <x:c r="F151" s="11" t="n">
         <x:f>SQRT((C151-C150)^2+(D151-D150)^2+(E151-E150)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
         <x:v>Current</x:v>
@@ -11578,20 +11578,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B152" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C152" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D152" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E152" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F152" s="11" t="n">
         <x:f>SQRT((C152-C151)^2+(D152-D151)^2+(E152-E151)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G152" s="8" t="str">
         <x:v>Current</x:v>
@@ -11602,20 +11602,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B153" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C153" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D153" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E153" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F153" s="11" t="n">
         <x:f>SQRT((C153-C152)^2+(D153-D152)^2+(E153-E152)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G153" s="8" t="str">
         <x:v>Current</x:v>
@@ -11626,20 +11626,20 @@
         <x:v>trunk:AV1:A2:audio:-1</x:v>
       </x:c>
       <x:c r="B154" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C154" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>9.545000000000002</x:v>
       </x:c>
       <x:c r="D154" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E154" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F154" s="11" t="n">
         <x:f>SQRT((C154-C153)^2+(D154-D153)^2+(E154-E153)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>27.43</x:v>
       </x:c>
       <x:c r="G154" s="8" t="str">
         <x:v>Current</x:v>
@@ -11647,23 +11647,23 @@
     </x:row>
     <x:row r="155" ht="32" customHeight="1">
       <x:c r="A155" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:-1</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
       </x:c>
       <x:c r="B155" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C155" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D155" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E155" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F155" s="11" t="n">
-        <x:f>SQRT((C155-C154)^2+(D155-D154)^2+(E155-E154)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G155" s="8" t="str">
         <x:v>Current</x:v>
@@ -11671,23 +11671,23 @@
     </x:row>
     <x:row r="156" ht="32" customHeight="1">
       <x:c r="A156" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:-1</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
       </x:c>
       <x:c r="B156" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C156" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D156" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E156" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F156" s="11" t="n">
         <x:f>SQRT((C156-C155)^2+(D156-D155)^2+(E156-E155)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>2.8419999999999996</x:v>
       </x:c>
       <x:c r="G156" s="8" t="str">
         <x:v>Current</x:v>
@@ -11695,23 +11695,23 @@
     </x:row>
     <x:row r="157" ht="32" customHeight="1">
       <x:c r="A157" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:-1</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
       </x:c>
       <x:c r="B157" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C157" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="D157" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E157" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.47</x:v>
       </x:c>
       <x:c r="F157" s="11" t="n">
         <x:f>SQRT((C157-C156)^2+(D157-D156)^2+(E157-E156)^2)</x:f>
-        <x:v>1.4980000000000002</x:v>
+        <x:v>0.10999999999999943</x:v>
       </x:c>
       <x:c r="G157" s="8" t="str">
         <x:v>Current</x:v>
@@ -11719,13 +11719,13 @@
     </x:row>
     <x:row r="158" ht="32" customHeight="1">
       <x:c r="A158" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:-1</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
       </x:c>
       <x:c r="B158" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C158" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D158" s="11" t="n">
         <x:v>5.542</x:v>
@@ -11734,8 +11734,8 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F158" s="11" t="n">
-        <x:f>SQRT((C158-C157)^2+(D158-D157)^2+(E158-E157)^2)</x:f>
-        <x:v>27.43</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G158" s="8" t="str">
         <x:v>Current</x:v>
@@ -11743,599 +11743,599 @@
     </x:row>
     <x:row r="159" ht="32" customHeight="1">
       <x:c r="A159" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
       </x:c>
       <x:c r="B159" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C159" s="11" t="n">
-        <x:v>14.045000000000002</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D159" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E159" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F159" s="11" t="n">
+        <x:f>SQRT((C159-C158)^2+(D159-D158)^2+(E159-E158)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G159" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="32" customHeight="1">
+      <x:c r="A160" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
+      </x:c>
+      <x:c r="B160" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C160" s="11" t="n">
+        <x:v>27.545</x:v>
+      </x:c>
+      <x:c r="D160" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E160" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F160" s="11" t="n">
+        <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G160" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="32" customHeight="1">
+      <x:c r="A161" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
+      </x:c>
+      <x:c r="B161" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C161" s="11" t="n">
+        <x:v>9.545000000000002</x:v>
+      </x:c>
+      <x:c r="D161" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E161" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F161" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G159" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="32" customHeight="1">
-      <x:c r="A160" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
-      </x:c>
-      <x:c r="B160" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C160" s="11" t="n">
-        <x:v>14.045000000000002</x:v>
-      </x:c>
-      <x:c r="D160" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E160" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F160" s="11" t="n">
-        <x:f>SQRT((C160-C159)^2+(D160-D159)^2+(E160-E159)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G160" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="32" customHeight="1">
-      <x:c r="A161" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S279</x:v>
-      </x:c>
-      <x:c r="B161" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C161" s="11" t="n">
-        <x:v>14.045</x:v>
-      </x:c>
-      <x:c r="D161" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E161" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F161" s="11" t="n">
-        <x:f>SQRT((C161-C160)^2+(D161-D160)^2+(E161-E160)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G161" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="32" customHeight="1">
       <x:c r="A162" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
       </x:c>
       <x:c r="B162" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C162" s="11" t="n">
-        <x:v>27.545</x:v>
+        <x:v>9.545000000000002</x:v>
       </x:c>
       <x:c r="D162" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E162" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F162" s="11" t="n">
+        <x:f>SQRT((C162-C161)^2+(D162-D161)^2+(E162-E161)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G162" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="32" customHeight="1">
+      <x:c r="A163" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
+      </x:c>
+      <x:c r="B163" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C163" s="11" t="n">
+        <x:v>9.545</x:v>
+      </x:c>
+      <x:c r="D163" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E163" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F163" s="11" t="n">
+        <x:f>SQRT((C163-C162)^2+(D163-D162)^2+(E163-E162)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G163" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="32" customHeight="1">
+      <x:c r="A164" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
+      </x:c>
+      <x:c r="B164" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C164" s="11" t="n">
+        <x:v>18.545</x:v>
+      </x:c>
+      <x:c r="D164" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E164" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F164" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G162" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" ht="32" customHeight="1">
-      <x:c r="A163" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
-      </x:c>
-      <x:c r="B163" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C163" s="11" t="n">
-        <x:v>27.545</x:v>
-      </x:c>
-      <x:c r="D163" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E163" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F163" s="11" t="n">
-        <x:f>SQRT((C163-C162)^2+(D163-D162)^2+(E163-E162)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G163" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" ht="32" customHeight="1">
-      <x:c r="A164" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S280</x:v>
-      </x:c>
-      <x:c r="B164" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C164" s="11" t="n">
-        <x:v>27.545</x:v>
-      </x:c>
-      <x:c r="D164" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E164" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F164" s="11" t="n">
-        <x:f>SQRT((C164-C163)^2+(D164-D163)^2+(E164-E163)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G164" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="32" customHeight="1">
       <x:c r="A165" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
       </x:c>
       <x:c r="B165" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C165" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D165" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E165" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F165" s="11" t="n">
+        <x:f>SQRT((C165-C164)^2+(D165-D164)^2+(E165-E164)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G165" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="32" customHeight="1">
+      <x:c r="A166" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
+      </x:c>
+      <x:c r="B166" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C166" s="11" t="n">
+        <x:v>18.545</x:v>
+      </x:c>
+      <x:c r="D166" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E166" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F166" s="11" t="n">
+        <x:f>SQRT((C166-C165)^2+(D166-D165)^2+(E166-E165)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G166" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="32" customHeight="1">
+      <x:c r="A167" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
+      </x:c>
+      <x:c r="B167" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C167" s="11" t="n">
+        <x:v>23.045</x:v>
+      </x:c>
+      <x:c r="D167" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E167" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F167" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G165" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" ht="32" customHeight="1">
-      <x:c r="A166" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
-      </x:c>
-      <x:c r="B166" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C166" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
-      </x:c>
-      <x:c r="D166" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E166" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F166" s="11" t="n">
-        <x:f>SQRT((C166-C165)^2+(D166-D165)^2+(E166-E165)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G166" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" ht="32" customHeight="1">
-      <x:c r="A167" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-2P-3</x:v>
-      </x:c>
-      <x:c r="B167" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C167" s="11" t="n">
-        <x:v>9.545</x:v>
-      </x:c>
-      <x:c r="D167" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E167" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F167" s="11" t="n">
-        <x:f>SQRT((C167-C166)^2+(D167-D166)^2+(E167-E166)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G167" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="32" customHeight="1">
       <x:c r="A168" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
       </x:c>
       <x:c r="B168" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C168" s="11" t="n">
-        <x:v>18.545</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D168" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E168" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F168" s="11" t="n">
+        <x:f>SQRT((C168-C167)^2+(D168-D167)^2+(E168-E167)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G168" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="32" customHeight="1">
+      <x:c r="A169" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
+      </x:c>
+      <x:c r="B169" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C169" s="11" t="n">
+        <x:v>23.045</x:v>
+      </x:c>
+      <x:c r="D169" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E169" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F169" s="11" t="n">
+        <x:f>SQRT((C169-C168)^2+(D169-D168)^2+(E169-E168)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G169" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="32" customHeight="1">
+      <x:c r="A170" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
+      </x:c>
+      <x:c r="B170" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C170" s="11" t="n">
+        <x:v>32.045</x:v>
+      </x:c>
+      <x:c r="D170" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E170" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F170" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G168" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" ht="32" customHeight="1">
-      <x:c r="A169" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
-      </x:c>
-      <x:c r="B169" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C169" s="11" t="n">
-        <x:v>18.545</x:v>
-      </x:c>
-      <x:c r="D169" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E169" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F169" s="11" t="n">
-        <x:f>SQRT((C169-C168)^2+(D169-D168)^2+(E169-E168)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G169" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="32" customHeight="1">
-      <x:c r="A170" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-4-5</x:v>
-      </x:c>
-      <x:c r="B170" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C170" s="11" t="n">
-        <x:v>18.545</x:v>
-      </x:c>
-      <x:c r="D170" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E170" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F170" s="11" t="n">
-        <x:f>SQRT((C170-C169)^2+(D170-D169)^2+(E170-E169)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G170" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="32" customHeight="1">
       <x:c r="A171" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
       </x:c>
       <x:c r="B171" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C171" s="11" t="n">
-        <x:v>23.045</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D171" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E171" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F171" s="11" t="n">
+        <x:f>SQRT((C171-C170)^2+(D171-D170)^2+(E171-E170)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G171" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="32" customHeight="1">
+      <x:c r="A172" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
+      </x:c>
+      <x:c r="B172" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C172" s="11" t="n">
+        <x:v>32.045</x:v>
+      </x:c>
+      <x:c r="D172" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E172" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F172" s="11" t="n">
+        <x:f>SQRT((C172-C171)^2+(D172-D171)^2+(E172-E171)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G172" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="32" customHeight="1">
+      <x:c r="A173" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
+      </x:c>
+      <x:c r="B173" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C173" s="11" t="n">
+        <x:v>36.545</x:v>
+      </x:c>
+      <x:c r="D173" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E173" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F173" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G171" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" ht="32" customHeight="1">
-      <x:c r="A172" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
-      </x:c>
-      <x:c r="B172" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C172" s="11" t="n">
-        <x:v>23.045</x:v>
-      </x:c>
-      <x:c r="D172" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E172" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F172" s="11" t="n">
-        <x:f>SQRT((C172-C171)^2+(D172-D171)^2+(E172-E171)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G172" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" ht="32" customHeight="1">
-      <x:c r="A173" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-5-6</x:v>
-      </x:c>
-      <x:c r="B173" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C173" s="11" t="n">
-        <x:v>23.045</x:v>
-      </x:c>
-      <x:c r="D173" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E173" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F173" s="11" t="n">
-        <x:f>SQRT((C173-C172)^2+(D173-D172)^2+(E173-E172)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G173" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="32" customHeight="1">
       <x:c r="A174" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
       </x:c>
       <x:c r="B174" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C174" s="11" t="n">
-        <x:v>32.045</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D174" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E174" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F174" s="11" t="n">
+        <x:f>SQRT((C174-C173)^2+(D174-D173)^2+(E174-E173)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G174" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="32" customHeight="1">
+      <x:c r="A175" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
+      </x:c>
+      <x:c r="B175" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C175" s="11" t="n">
+        <x:v>36.545</x:v>
+      </x:c>
+      <x:c r="D175" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E175" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F175" s="11" t="n">
+        <x:f>SQRT((C175-C174)^2+(D175-D174)^2+(E175-E174)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G175" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="32" customHeight="1">
+      <x:c r="A176" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
+      </x:c>
+      <x:c r="B176" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C176" s="11" t="n">
+        <x:v>48.245</x:v>
+      </x:c>
+      <x:c r="D176" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E176" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F176" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G174" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="32" customHeight="1">
-      <x:c r="A175" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
-      </x:c>
-      <x:c r="B175" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C175" s="11" t="n">
-        <x:v>32.045</x:v>
-      </x:c>
-      <x:c r="D175" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E175" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F175" s="11" t="n">
-        <x:f>SQRT((C175-C174)^2+(D175-D174)^2+(E175-E174)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G175" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" ht="32" customHeight="1">
-      <x:c r="A176" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-7-8</x:v>
-      </x:c>
-      <x:c r="B176" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C176" s="11" t="n">
-        <x:v>32.045</x:v>
-      </x:c>
-      <x:c r="D176" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E176" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F176" s="11" t="n">
-        <x:f>SQRT((C176-C175)^2+(D176-D175)^2+(E176-E175)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G176" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="32" customHeight="1">
       <x:c r="A177" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
       </x:c>
       <x:c r="B177" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C177" s="11" t="n">
-        <x:v>36.545</x:v>
+        <x:v>48.245</x:v>
       </x:c>
       <x:c r="D177" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E177" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F177" s="11" t="n">
+        <x:f>SQRT((C177-C176)^2+(D177-D176)^2+(E177-E176)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G177" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="32" customHeight="1">
+      <x:c r="A178" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
+      </x:c>
+      <x:c r="B178" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C178" s="11" t="n">
+        <x:v>48.245</x:v>
+      </x:c>
+      <x:c r="D178" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E178" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F178" s="11" t="n">
+        <x:f>SQRT((C178-C177)^2+(D178-D177)^2+(E178-E177)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G178" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="32" customHeight="1">
+      <x:c r="A179" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
+      </x:c>
+      <x:c r="B179" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C179" s="11" t="n">
+        <x:v>52.586</x:v>
+      </x:c>
+      <x:c r="D179" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E179" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F179" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G177" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" ht="32" customHeight="1">
-      <x:c r="A178" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
-      </x:c>
-      <x:c r="B178" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C178" s="11" t="n">
-        <x:v>36.545</x:v>
-      </x:c>
-      <x:c r="D178" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E178" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F178" s="11" t="n">
-        <x:f>SQRT((C178-C177)^2+(D178-D177)^2+(E178-E177)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G178" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" ht="32" customHeight="1">
-      <x:c r="A179" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-8-9</x:v>
-      </x:c>
-      <x:c r="B179" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C179" s="11" t="n">
-        <x:v>36.545</x:v>
-      </x:c>
-      <x:c r="D179" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E179" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F179" s="11" t="n">
-        <x:f>SQRT((C179-C178)^2+(D179-D178)^2+(E179-E178)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G179" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="32" customHeight="1">
       <x:c r="A180" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
       </x:c>
       <x:c r="B180" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C180" s="11" t="n">
-        <x:v>48.245</x:v>
+        <x:v>52.586</x:v>
       </x:c>
       <x:c r="D180" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E180" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F180" s="11" t="n">
+        <x:f>SQRT((C180-C179)^2+(D180-D179)^2+(E180-E179)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G180" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="32" customHeight="1">
+      <x:c r="A181" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
+      </x:c>
+      <x:c r="B181" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C181" s="11" t="n">
+        <x:v>52.586</x:v>
+      </x:c>
+      <x:c r="D181" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E181" s="11" t="n">
+        <x:v>-7.47</x:v>
+      </x:c>
+      <x:c r="F181" s="11" t="n">
+        <x:f>SQRT((C181-C180)^2+(D181-D180)^2+(E181-E180)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G181" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="32" customHeight="1">
+      <x:c r="A182" s="8" t="str">
+        <x:v>trunk:AV1:A2:audio:1</x:v>
+      </x:c>
+      <x:c r="B182" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C182" s="11" t="n">
+        <x:v>49.275</x:v>
+      </x:c>
+      <x:c r="D182" s="11" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="E182" s="11" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="F182" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G180" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" ht="32" customHeight="1">
-      <x:c r="A181" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
-      </x:c>
-      <x:c r="B181" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C181" s="11" t="n">
-        <x:v>48.245</x:v>
-      </x:c>
-      <x:c r="D181" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E181" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F181" s="11" t="n">
-        <x:f>SQRT((C181-C180)^2+(D181-D180)^2+(E181-E180)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G181" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" ht="32" customHeight="1">
-      <x:c r="A182" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-10-11</x:v>
-      </x:c>
-      <x:c r="B182" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C182" s="11" t="n">
-        <x:v>48.245</x:v>
-      </x:c>
-      <x:c r="D182" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E182" s="11" t="n">
-        <x:v>-7.47</x:v>
-      </x:c>
-      <x:c r="F182" s="11" t="n">
-        <x:f>SQRT((C182-C181)^2+(D182-D181)^2+(E182-E181)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G182" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="32" customHeight="1">
       <x:c r="A183" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
+        <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B183" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C183" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D183" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E183" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F183" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C183-C182)^2+(D183-D182)^2+(E183-E182)^2)</x:f>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G183" s="8" t="str">
         <x:v>Current</x:v>
@@ -12343,23 +12343,23 @@
     </x:row>
     <x:row r="184" ht="32" customHeight="1">
       <x:c r="A184" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
+        <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B184" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C184" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D184" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E184" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F184" s="11" t="n">
         <x:f>SQRT((C184-C183)^2+(D184-D183)^2+(E184-E183)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G184" s="8" t="str">
         <x:v>Current</x:v>
@@ -12367,23 +12367,23 @@
     </x:row>
     <x:row r="185" ht="32" customHeight="1">
       <x:c r="A185" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:-1:S-PORCH-B-11-12</x:v>
+        <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B185" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C185" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D185" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E185" s="11" t="n">
-        <x:v>-7.47</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F185" s="11" t="n">
         <x:f>SQRT((C185-C184)^2+(D185-D184)^2+(E185-E184)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="G185" s="8" t="str">
         <x:v>Current</x:v>
@@ -12394,20 +12394,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B186" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C186" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D186" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E186" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F186" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C186-C185)^2+(D186-D185)^2+(E186-E185)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G186" s="8" t="str">
         <x:v>Current</x:v>
@@ -12418,20 +12418,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B187" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C187" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D187" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E187" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F187" s="11" t="n">
         <x:f>SQRT((C187-C186)^2+(D187-D186)^2+(E187-E186)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G187" s="8" t="str">
         <x:v>Current</x:v>
@@ -12442,20 +12442,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B188" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C188" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E188" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F188" s="11" t="n">
         <x:f>SQRT((C188-C187)^2+(D188-D187)^2+(E188-E187)^2)</x:f>
-        <x:v>0.8400000000000003</x:v>
+        <x:v>1.2119999999999997</x:v>
       </x:c>
       <x:c r="G188" s="8" t="str">
         <x:v>Current</x:v>
@@ -12466,20 +12466,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B189" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C189" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D189" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E189" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F189" s="11" t="n">
         <x:f>SQRT((C189-C188)^2+(D189-D188)^2+(E189-E188)^2)</x:f>
-        <x:v>3.38</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G189" s="8" t="str">
         <x:v>Current</x:v>
@@ -12490,20 +12490,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B190" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C190" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D190" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E190" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F190" s="11" t="n">
         <x:f>SQRT((C190-C189)^2+(D190-D189)^2+(E190-E189)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G190" s="8" t="str">
         <x:v>Current</x:v>
@@ -12514,20 +12514,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B191" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C191" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D191" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E191" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F191" s="11" t="n">
         <x:f>SQRT((C191-C190)^2+(D191-D190)^2+(E191-E190)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G191" s="8" t="str">
         <x:v>Current</x:v>
@@ -12538,20 +12538,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B192" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C192" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D192" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E192" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F192" s="11" t="n">
         <x:f>SQRT((C192-C191)^2+(D192-D191)^2+(E192-E191)^2)</x:f>
-        <x:v>1.2119999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G192" s="8" t="str">
         <x:v>Current</x:v>
@@ -12562,20 +12562,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B193" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C193" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D193" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E193" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F193" s="11" t="n">
         <x:f>SQRT((C193-C192)^2+(D193-D192)^2+(E193-E192)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G193" s="8" t="str">
         <x:v>Current</x:v>
@@ -12586,20 +12586,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B194" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C194" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D194" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E194" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F194" s="11" t="n">
         <x:f>SQRT((C194-C193)^2+(D194-D193)^2+(E194-E193)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G194" s="8" t="str">
         <x:v>Current</x:v>
@@ -12610,20 +12610,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B195" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C195" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D195" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E195" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F195" s="11" t="n">
         <x:f>SQRT((C195-C194)^2+(D195-D194)^2+(E195-E194)^2)</x:f>
-        <x:v>1.4980000000000002</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G195" s="8" t="str">
         <x:v>Current</x:v>
@@ -12634,10 +12634,10 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B196" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C196" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D196" s="11" t="n">
         <x:v>7.04</x:v>
@@ -12647,7 +12647,7 @@
       </x:c>
       <x:c r="F196" s="11" t="n">
         <x:f>SQRT((C196-C195)^2+(D196-D195)^2+(E196-E195)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G196" s="8" t="str">
         <x:v>Current</x:v>
@@ -12658,20 +12658,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B197" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C197" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D197" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E197" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F197" s="11" t="n">
         <x:f>SQRT((C197-C196)^2+(D197-D196)^2+(E197-E196)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G197" s="8" t="str">
         <x:v>Current</x:v>
@@ -12682,20 +12682,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B198" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C198" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D198" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E198" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F198" s="11" t="n">
         <x:f>SQRT((C198-C197)^2+(D198-D197)^2+(E198-E197)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.4980000000000002</x:v>
       </x:c>
       <x:c r="G198" s="8" t="str">
         <x:v>Current</x:v>
@@ -12706,20 +12706,20 @@
         <x:v>trunk:AV1:A2:audio:1</x:v>
       </x:c>
       <x:c r="B199" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C199" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>9.545000000000002</x:v>
       </x:c>
       <x:c r="D199" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E199" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F199" s="11" t="n">
         <x:f>SQRT((C199-C198)^2+(D199-D198)^2+(E199-E198)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>27.43</x:v>
       </x:c>
       <x:c r="G199" s="8" t="str">
         <x:v>Current</x:v>
@@ -12727,23 +12727,23 @@
     </x:row>
     <x:row r="200" ht="32" customHeight="1">
       <x:c r="A200" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:1</x:v>
+        <x:v>drop:AV1:A2:audio:1:S281</x:v>
       </x:c>
       <x:c r="B200" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C200" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D200" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.542</x:v>
       </x:c>
       <x:c r="E200" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F200" s="11" t="n">
-        <x:f>SQRT((C200-C199)^2+(D200-D199)^2+(E200-E199)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G200" s="8" t="str">
         <x:v>Current</x:v>
@@ -12751,23 +12751,23 @@
     </x:row>
     <x:row r="201" ht="32" customHeight="1">
       <x:c r="A201" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:1</x:v>
+        <x:v>drop:AV1:A2:audio:1:S281</x:v>
       </x:c>
       <x:c r="B201" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C201" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>14.045000000000002</x:v>
       </x:c>
       <x:c r="D201" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E201" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F201" s="11" t="n">
         <x:f>SQRT((C201-C200)^2+(D201-D200)^2+(E201-E200)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>2.8419999999999996</x:v>
       </x:c>
       <x:c r="G201" s="8" t="str">
         <x:v>Current</x:v>
@@ -12775,23 +12775,23 @@
     </x:row>
     <x:row r="202" ht="32" customHeight="1">
       <x:c r="A202" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:1</x:v>
+        <x:v>drop:AV1:A2:audio:1:S281</x:v>
       </x:c>
       <x:c r="B202" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C202" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>14.045</x:v>
       </x:c>
       <x:c r="D202" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E202" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="F202" s="11" t="n">
         <x:f>SQRT((C202-C201)^2+(D202-D201)^2+(E202-E201)^2)</x:f>
-        <x:v>1.4980000000000002</x:v>
+        <x:v>0.10999999999999943</x:v>
       </x:c>
       <x:c r="G202" s="8" t="str">
         <x:v>Current</x:v>
@@ -12799,13 +12799,13 @@
     </x:row>
     <x:row r="203" ht="32" customHeight="1">
       <x:c r="A203" s="8" t="str">
-        <x:v>trunk:AV1:A2:audio:1</x:v>
+        <x:v>drop:AV1:A2:audio:1:S282</x:v>
       </x:c>
       <x:c r="B203" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C203" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D203" s="11" t="n">
         <x:v>5.542</x:v>
@@ -12814,8 +12814,8 @@
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F203" s="11" t="n">
-        <x:f>SQRT((C203-C202)^2+(D203-D202)^2+(E203-E202)^2)</x:f>
-        <x:v>27.43</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G203" s="8" t="str">
         <x:v>Current</x:v>
@@ -12823,599 +12823,599 @@
     </x:row>
     <x:row r="204" ht="32" customHeight="1">
       <x:c r="A204" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S281</x:v>
+        <x:v>drop:AV1:A2:audio:1:S282</x:v>
       </x:c>
       <x:c r="B204" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C204" s="11" t="n">
-        <x:v>14.045000000000002</x:v>
+        <x:v>27.545</x:v>
       </x:c>
       <x:c r="D204" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F204" s="11" t="n">
+        <x:f>SQRT((C204-C203)^2+(D204-D203)^2+(E204-E203)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G204" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="32" customHeight="1">
+      <x:c r="A205" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S282</x:v>
+      </x:c>
+      <x:c r="B205" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C205" s="11" t="n">
+        <x:v>27.545</x:v>
+      </x:c>
+      <x:c r="D205" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E205" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F205" s="11" t="n">
+        <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G205" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="32" customHeight="1">
+      <x:c r="A206" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
+      </x:c>
+      <x:c r="B206" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C206" s="11" t="n">
+        <x:v>9.545000000000002</x:v>
+      </x:c>
+      <x:c r="D206" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E206" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F206" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G204" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" ht="32" customHeight="1">
-      <x:c r="A205" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S281</x:v>
-      </x:c>
-      <x:c r="B205" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C205" s="11" t="n">
-        <x:v>14.045000000000002</x:v>
-      </x:c>
-      <x:c r="D205" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E205" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F205" s="11" t="n">
-        <x:f>SQRT((C205-C204)^2+(D205-D204)^2+(E205-E204)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G205" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" ht="32" customHeight="1">
-      <x:c r="A206" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S281</x:v>
-      </x:c>
-      <x:c r="B206" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C206" s="11" t="n">
-        <x:v>14.045</x:v>
-      </x:c>
-      <x:c r="D206" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E206" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F206" s="11" t="n">
-        <x:f>SQRT((C206-C205)^2+(D206-D205)^2+(E206-E205)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G206" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="32" customHeight="1">
       <x:c r="A207" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S282</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
       </x:c>
       <x:c r="B207" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C207" s="11" t="n">
-        <x:v>27.545</x:v>
+        <x:v>9.545000000000002</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F207" s="11" t="n">
+        <x:f>SQRT((C207-C206)^2+(D207-D206)^2+(E207-E206)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G207" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="32" customHeight="1">
+      <x:c r="A208" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
+      </x:c>
+      <x:c r="B208" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C208" s="11" t="n">
+        <x:v>9.545</x:v>
+      </x:c>
+      <x:c r="D208" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E208" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F208" s="11" t="n">
+        <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G208" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="32" customHeight="1">
+      <x:c r="A209" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
+      </x:c>
+      <x:c r="B209" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C209" s="11" t="n">
+        <x:v>18.545</x:v>
+      </x:c>
+      <x:c r="D209" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E209" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F209" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G207" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" ht="32" customHeight="1">
-      <x:c r="A208" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S282</x:v>
-      </x:c>
-      <x:c r="B208" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C208" s="11" t="n">
-        <x:v>27.545</x:v>
-      </x:c>
-      <x:c r="D208" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E208" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F208" s="11" t="n">
-        <x:f>SQRT((C208-C207)^2+(D208-D207)^2+(E208-E207)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G208" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" ht="32" customHeight="1">
-      <x:c r="A209" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S282</x:v>
-      </x:c>
-      <x:c r="B209" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C209" s="11" t="n">
-        <x:v>27.545</x:v>
-      </x:c>
-      <x:c r="D209" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E209" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F209" s="11" t="n">
-        <x:f>SQRT((C209-C208)^2+(D209-D208)^2+(E209-E208)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G209" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="32" customHeight="1">
       <x:c r="A210" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
       </x:c>
       <x:c r="B210" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C210" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
+        <x:v>18.545</x:v>
       </x:c>
       <x:c r="D210" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E210" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F210" s="11" t="n">
+        <x:f>SQRT((C210-C209)^2+(D210-D209)^2+(E210-E209)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G210" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="32" customHeight="1">
+      <x:c r="A211" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
+      </x:c>
+      <x:c r="B211" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C211" s="11" t="n">
+        <x:v>18.545</x:v>
+      </x:c>
+      <x:c r="D211" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E211" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F211" s="11" t="n">
+        <x:f>SQRT((C211-C210)^2+(D211-D210)^2+(E211-E210)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G211" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="32" customHeight="1">
+      <x:c r="A212" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
+      </x:c>
+      <x:c r="B212" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C212" s="11" t="n">
+        <x:v>23.045</x:v>
+      </x:c>
+      <x:c r="D212" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E212" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F212" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G210" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" ht="32" customHeight="1">
-      <x:c r="A211" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
-      </x:c>
-      <x:c r="B211" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C211" s="11" t="n">
-        <x:v>9.545000000000002</x:v>
-      </x:c>
-      <x:c r="D211" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E211" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F211" s="11" t="n">
-        <x:f>SQRT((C211-C210)^2+(D211-D210)^2+(E211-E210)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G211" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" ht="32" customHeight="1">
-      <x:c r="A212" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-2P-3</x:v>
-      </x:c>
-      <x:c r="B212" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C212" s="11" t="n">
-        <x:v>9.545</x:v>
-      </x:c>
-      <x:c r="D212" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E212" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F212" s="11" t="n">
-        <x:f>SQRT((C212-C211)^2+(D212-D211)^2+(E212-E211)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G212" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="32" customHeight="1">
       <x:c r="A213" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
       </x:c>
       <x:c r="B213" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C213" s="11" t="n">
-        <x:v>18.545</x:v>
+        <x:v>23.045</x:v>
       </x:c>
       <x:c r="D213" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E213" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F213" s="11" t="n">
+        <x:f>SQRT((C213-C212)^2+(D213-D212)^2+(E213-E212)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G213" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="32" customHeight="1">
+      <x:c r="A214" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
+      </x:c>
+      <x:c r="B214" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C214" s="11" t="n">
+        <x:v>23.045</x:v>
+      </x:c>
+      <x:c r="D214" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E214" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F214" s="11" t="n">
+        <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G214" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="32" customHeight="1">
+      <x:c r="A215" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
+      </x:c>
+      <x:c r="B215" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C215" s="11" t="n">
+        <x:v>32.045</x:v>
+      </x:c>
+      <x:c r="D215" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E215" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F215" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G213" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" ht="32" customHeight="1">
-      <x:c r="A214" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
-      </x:c>
-      <x:c r="B214" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C214" s="11" t="n">
-        <x:v>18.545</x:v>
-      </x:c>
-      <x:c r="D214" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E214" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F214" s="11" t="n">
-        <x:f>SQRT((C214-C213)^2+(D214-D213)^2+(E214-E213)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G214" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" ht="32" customHeight="1">
-      <x:c r="A215" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-4-5</x:v>
-      </x:c>
-      <x:c r="B215" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C215" s="11" t="n">
-        <x:v>18.545</x:v>
-      </x:c>
-      <x:c r="D215" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E215" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F215" s="11" t="n">
-        <x:f>SQRT((C215-C214)^2+(D215-D214)^2+(E215-E214)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G215" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="32" customHeight="1">
       <x:c r="A216" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
       </x:c>
       <x:c r="B216" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C216" s="11" t="n">
-        <x:v>23.045</x:v>
+        <x:v>32.045</x:v>
       </x:c>
       <x:c r="D216" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E216" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F216" s="11" t="n">
+        <x:f>SQRT((C216-C215)^2+(D216-D215)^2+(E216-E215)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G216" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="32" customHeight="1">
+      <x:c r="A217" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
+      </x:c>
+      <x:c r="B217" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C217" s="11" t="n">
+        <x:v>32.045</x:v>
+      </x:c>
+      <x:c r="D217" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E217" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F217" s="11" t="n">
+        <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G217" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="32" customHeight="1">
+      <x:c r="A218" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
+      </x:c>
+      <x:c r="B218" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C218" s="11" t="n">
+        <x:v>36.545</x:v>
+      </x:c>
+      <x:c r="D218" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E218" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F218" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G216" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" ht="32" customHeight="1">
-      <x:c r="A217" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
-      </x:c>
-      <x:c r="B217" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C217" s="11" t="n">
-        <x:v>23.045</x:v>
-      </x:c>
-      <x:c r="D217" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E217" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F217" s="11" t="n">
-        <x:f>SQRT((C217-C216)^2+(D217-D216)^2+(E217-E216)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G217" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" ht="32" customHeight="1">
-      <x:c r="A218" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-5-6</x:v>
-      </x:c>
-      <x:c r="B218" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C218" s="11" t="n">
-        <x:v>23.045</x:v>
-      </x:c>
-      <x:c r="D218" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E218" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F218" s="11" t="n">
-        <x:f>SQRT((C218-C217)^2+(D218-D217)^2+(E218-E217)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G218" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="32" customHeight="1">
       <x:c r="A219" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
       </x:c>
       <x:c r="B219" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C219" s="11" t="n">
-        <x:v>32.045</x:v>
+        <x:v>36.545</x:v>
       </x:c>
       <x:c r="D219" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E219" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F219" s="11" t="n">
+        <x:f>SQRT((C219-C218)^2+(D219-D218)^2+(E219-E218)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G219" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="32" customHeight="1">
+      <x:c r="A220" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
+      </x:c>
+      <x:c r="B220" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C220" s="11" t="n">
+        <x:v>36.545</x:v>
+      </x:c>
+      <x:c r="D220" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E220" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F220" s="11" t="n">
+        <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G220" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="32" customHeight="1">
+      <x:c r="A221" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
+      </x:c>
+      <x:c r="B221" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C221" s="11" t="n">
+        <x:v>48.245</x:v>
+      </x:c>
+      <x:c r="D221" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E221" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F221" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G219" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" ht="32" customHeight="1">
-      <x:c r="A220" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
-      </x:c>
-      <x:c r="B220" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C220" s="11" t="n">
-        <x:v>32.045</x:v>
-      </x:c>
-      <x:c r="D220" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E220" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F220" s="11" t="n">
-        <x:f>SQRT((C220-C219)^2+(D220-D219)^2+(E220-E219)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G220" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" ht="32" customHeight="1">
-      <x:c r="A221" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-7-8</x:v>
-      </x:c>
-      <x:c r="B221" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C221" s="11" t="n">
-        <x:v>32.045</x:v>
-      </x:c>
-      <x:c r="D221" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E221" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F221" s="11" t="n">
-        <x:f>SQRT((C221-C220)^2+(D221-D220)^2+(E221-E220)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G221" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="32" customHeight="1">
       <x:c r="A222" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
       </x:c>
       <x:c r="B222" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C222" s="11" t="n">
-        <x:v>36.545</x:v>
+        <x:v>48.245</x:v>
       </x:c>
       <x:c r="D222" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E222" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F222" s="11" t="n">
+        <x:f>SQRT((C222-C221)^2+(D222-D221)^2+(E222-E221)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G222" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="32" customHeight="1">
+      <x:c r="A223" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
+      </x:c>
+      <x:c r="B223" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C223" s="11" t="n">
+        <x:v>48.245</x:v>
+      </x:c>
+      <x:c r="D223" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E223" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F223" s="11" t="n">
+        <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G223" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="32" customHeight="1">
+      <x:c r="A224" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
+      </x:c>
+      <x:c r="B224" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C224" s="11" t="n">
+        <x:v>52.586</x:v>
+      </x:c>
+      <x:c r="D224" s="11" t="n">
+        <x:v>5.542</x:v>
+      </x:c>
+      <x:c r="E224" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F224" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G222" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" ht="32" customHeight="1">
-      <x:c r="A223" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
-      </x:c>
-      <x:c r="B223" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C223" s="11" t="n">
-        <x:v>36.545</x:v>
-      </x:c>
-      <x:c r="D223" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E223" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F223" s="11" t="n">
-        <x:f>SQRT((C223-C222)^2+(D223-D222)^2+(E223-E222)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G223" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" ht="32" customHeight="1">
-      <x:c r="A224" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-8-9</x:v>
-      </x:c>
-      <x:c r="B224" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C224" s="11" t="n">
-        <x:v>36.545</x:v>
-      </x:c>
-      <x:c r="D224" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E224" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F224" s="11" t="n">
-        <x:f>SQRT((C224-C223)^2+(D224-D223)^2+(E224-E223)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G224" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="32" customHeight="1">
       <x:c r="A225" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
       </x:c>
       <x:c r="B225" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C225" s="11" t="n">
-        <x:v>48.245</x:v>
+        <x:v>52.586</x:v>
       </x:c>
       <x:c r="D225" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="E225" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F225" s="11" t="n">
+        <x:f>SQRT((C225-C224)^2+(D225-D224)^2+(E225-E224)^2)</x:f>
+        <x:v>2.8419999999999996</x:v>
+      </x:c>
+      <x:c r="G225" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="32" customHeight="1">
+      <x:c r="A226" s="8" t="str">
+        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
+      </x:c>
+      <x:c r="B226" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C226" s="11" t="n">
+        <x:v>52.586</x:v>
+      </x:c>
+      <x:c r="D226" s="11" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="E226" s="11" t="n">
+        <x:v>7.47</x:v>
+      </x:c>
+      <x:c r="F226" s="11" t="n">
+        <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
+        <x:v>0.10999999999999943</x:v>
+      </x:c>
+      <x:c r="G226" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="32" customHeight="1">
+      <x:c r="A227" s="8" t="str">
+        <x:v>trunk:AV1:A3:audio:-1</x:v>
+      </x:c>
+      <x:c r="B227" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C227" s="11" t="n">
+        <x:v>49.275</x:v>
+      </x:c>
+      <x:c r="D227" s="11" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="E227" s="11" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="F227" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G225" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" ht="32" customHeight="1">
-      <x:c r="A226" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
-      </x:c>
-      <x:c r="B226" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C226" s="11" t="n">
-        <x:v>48.245</x:v>
-      </x:c>
-      <x:c r="D226" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E226" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F226" s="11" t="n">
-        <x:f>SQRT((C226-C225)^2+(D226-D225)^2+(E226-E225)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
-      </x:c>
-      <x:c r="G226" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" ht="32" customHeight="1">
-      <x:c r="A227" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-10-11</x:v>
-      </x:c>
-      <x:c r="B227" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C227" s="11" t="n">
-        <x:v>48.245</x:v>
-      </x:c>
-      <x:c r="D227" s="11" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="E227" s="11" t="n">
-        <x:v>7.47</x:v>
-      </x:c>
-      <x:c r="F227" s="11" t="n">
-        <x:f>SQRT((C227-C226)^2+(D227-D226)^2+(E227-E226)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
-      </x:c>
       <x:c r="G227" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="32" customHeight="1">
       <x:c r="A228" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
+        <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B228" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C228" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D228" s="11" t="n">
-        <x:v>5.542</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E228" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F228" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C228-C227)^2+(D228-D227)^2+(E228-E227)^2)</x:f>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G228" s="8" t="str">
         <x:v>Current</x:v>
@@ -13423,23 +13423,23 @@
     </x:row>
     <x:row r="229" ht="32" customHeight="1">
       <x:c r="A229" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
+        <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B229" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C229" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D229" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E229" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F229" s="11" t="n">
         <x:f>SQRT((C229-C228)^2+(D229-D228)^2+(E229-E228)^2)</x:f>
-        <x:v>2.8419999999999996</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G229" s="8" t="str">
         <x:v>Current</x:v>
@@ -13447,23 +13447,23 @@
     </x:row>
     <x:row r="230" ht="32" customHeight="1">
       <x:c r="A230" s="8" t="str">
-        <x:v>drop:AV1:A2:audio:1:S-PORCH-H-11-12</x:v>
+        <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B230" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C230" s="11" t="n">
-        <x:v>52.586</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D230" s="11" t="n">
-        <x:v>2.7</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E230" s="11" t="n">
-        <x:v>7.47</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F230" s="11" t="n">
         <x:f>SQRT((C230-C229)^2+(D230-D229)^2+(E230-E229)^2)</x:f>
-        <x:v>0.10999999999999943</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="G230" s="8" t="str">
         <x:v>Current</x:v>
@@ -13474,20 +13474,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B231" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C231" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D231" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E231" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F231" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C231-C230)^2+(D231-D230)^2+(E231-E230)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G231" s="8" t="str">
         <x:v>Current</x:v>
@@ -13498,20 +13498,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B232" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C232" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D232" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E232" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F232" s="11" t="n">
         <x:f>SQRT((C232-C231)^2+(D232-D231)^2+(E232-E231)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G232" s="8" t="str">
         <x:v>Current</x:v>
@@ -13522,20 +13522,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B233" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C233" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D233" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E233" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F233" s="11" t="n">
         <x:f>SQRT((C233-C232)^2+(D233-D232)^2+(E233-E232)^2)</x:f>
-        <x:v>0.8400000000000003</x:v>
+        <x:v>1.2039999999999997</x:v>
       </x:c>
       <x:c r="G233" s="8" t="str">
         <x:v>Current</x:v>
@@ -13546,20 +13546,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B234" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C234" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D234" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E234" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F234" s="11" t="n">
         <x:f>SQRT((C234-C233)^2+(D234-D233)^2+(E234-E233)^2)</x:f>
-        <x:v>3.38</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G234" s="8" t="str">
         <x:v>Current</x:v>
@@ -13570,20 +13570,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B235" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C235" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D235" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E235" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F235" s="11" t="n">
         <x:f>SQRT((C235-C234)^2+(D235-D234)^2+(E235-E234)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G235" s="8" t="str">
         <x:v>Current</x:v>
@@ -13594,20 +13594,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B236" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C236" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D236" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E236" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F236" s="11" t="n">
         <x:f>SQRT((C236-C235)^2+(D236-D235)^2+(E236-E235)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G236" s="8" t="str">
         <x:v>Current</x:v>
@@ -13618,20 +13618,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B237" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C237" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D237" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E237" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F237" s="11" t="n">
         <x:f>SQRT((C237-C236)^2+(D237-D236)^2+(E237-E236)^2)</x:f>
-        <x:v>1.2039999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G237" s="8" t="str">
         <x:v>Current</x:v>
@@ -13642,20 +13642,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B238" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C238" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D238" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E238" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F238" s="11" t="n">
         <x:f>SQRT((C238-C237)^2+(D238-D237)^2+(E238-E237)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G238" s="8" t="str">
         <x:v>Current</x:v>
@@ -13666,20 +13666,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B239" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C239" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D239" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E239" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F239" s="11" t="n">
         <x:f>SQRT((C239-C238)^2+(D239-D238)^2+(E239-E238)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G239" s="8" t="str">
         <x:v>Current</x:v>
@@ -13690,20 +13690,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B240" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C240" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D240" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E240" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F240" s="11" t="n">
         <x:f>SQRT((C240-C239)^2+(D240-D239)^2+(E240-E239)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G240" s="8" t="str">
         <x:v>Current</x:v>
@@ -13714,10 +13714,10 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B241" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C241" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D241" s="11" t="n">
         <x:v>7.04</x:v>
@@ -13727,7 +13727,7 @@
       </x:c>
       <x:c r="F241" s="11" t="n">
         <x:f>SQRT((C241-C240)^2+(D241-D240)^2+(E241-E240)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G241" s="8" t="str">
         <x:v>Current</x:v>
@@ -13738,20 +13738,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B242" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C242" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D242" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E242" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F242" s="11" t="n">
         <x:f>SQRT((C242-C241)^2+(D242-D241)^2+(E242-E241)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G242" s="8" t="str">
         <x:v>Current</x:v>
@@ -13762,20 +13762,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B243" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C243" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D243" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E243" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F243" s="11" t="n">
         <x:f>SQRT((C243-C242)^2+(D243-D242)^2+(E243-E242)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G243" s="8" t="str">
         <x:v>Current</x:v>
@@ -13786,20 +13786,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B244" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C244" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D244" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E244" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F244" s="11" t="n">
         <x:f>SQRT((C244-C243)^2+(D244-D243)^2+(E244-E243)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G244" s="8" t="str">
         <x:v>Current</x:v>
@@ -13810,20 +13810,20 @@
         <x:v>trunk:AV1:A3:audio:-1</x:v>
       </x:c>
       <x:c r="B245" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C245" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D245" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E245" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F245" s="11" t="n">
         <x:f>SQRT((C245-C244)^2+(D245-D244)^2+(E245-E244)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>3.1249999999999996</x:v>
       </x:c>
       <x:c r="G245" s="8" t="str">
         <x:v>Current</x:v>
@@ -13831,23 +13831,23 @@
     </x:row>
     <x:row r="246" ht="32" customHeight="1">
       <x:c r="A246" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:-1</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B246" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C246" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D246" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E246" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F246" s="11" t="n">
-        <x:f>SQRT((C246-C245)^2+(D246-D245)^2+(E246-E245)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G246" s="8" t="str">
         <x:v>Current</x:v>
@@ -13855,23 +13855,23 @@
     </x:row>
     <x:row r="247" ht="32" customHeight="1">
       <x:c r="A247" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:-1</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B247" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C247" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D247" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E247" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F247" s="11" t="n">
         <x:f>SQRT((C247-C246)^2+(D247-D246)^2+(E247-E246)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G247" s="8" t="str">
         <x:v>Current</x:v>
@@ -13879,23 +13879,23 @@
     </x:row>
     <x:row r="248" ht="32" customHeight="1">
       <x:c r="A248" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:-1</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B248" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C248" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D248" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E248" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.703</x:v>
       </x:c>
       <x:c r="F248" s="11" t="n">
         <x:f>SQRT((C248-C247)^2+(D248-D247)^2+(E248-E247)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>0.34299999999999997</x:v>
       </x:c>
       <x:c r="G248" s="8" t="str">
         <x:v>Current</x:v>
@@ -13903,23 +13903,23 @@
     </x:row>
     <x:row r="249" ht="32" customHeight="1">
       <x:c r="A249" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:-1</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B249" s="8" t="n">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C249" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D249" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E249" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.703</x:v>
       </x:c>
       <x:c r="F249" s="11" t="n">
         <x:f>SQRT((C249-C248)^2+(D249-D248)^2+(E249-E248)^2)</x:f>
-        <x:v>3.1249999999999996</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="G249" s="8" t="str">
         <x:v>Current</x:v>
@@ -13930,20 +13930,20 @@
         <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B250" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C250" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D250" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E250" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.9430000000000005</x:v>
       </x:c>
       <x:c r="F250" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C250-C249)^2+(D250-D249)^2+(E250-E249)^2)</x:f>
+        <x:v>0.2400000000000002</x:v>
       </x:c>
       <x:c r="G250" s="8" t="str">
         <x:v>Current</x:v>
@@ -13954,20 +13954,20 @@
         <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B251" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C251" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D251" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E251" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-7.9430000000000005</x:v>
       </x:c>
       <x:c r="F251" s="11" t="n">
         <x:f>SQRT((C251-C250)^2+(D251-D250)^2+(E251-E250)^2)</x:f>
-        <x:v>2.1160000000000005</x:v>
+        <x:v>1.4500000000000002</x:v>
       </x:c>
       <x:c r="G251" s="8" t="str">
         <x:v>Current</x:v>
@@ -13978,20 +13978,20 @@
         <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B252" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C252" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D252" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E252" s="11" t="n">
-        <x:v>-7.703</x:v>
+        <x:v>-8.3</x:v>
       </x:c>
       <x:c r="F252" s="11" t="n">
         <x:f>SQRT((C252-C251)^2+(D252-D251)^2+(E252-E251)^2)</x:f>
-        <x:v>0.34299999999999997</x:v>
+        <x:v>0.3570000000000002</x:v>
       </x:c>
       <x:c r="G252" s="8" t="str">
         <x:v>Current</x:v>
@@ -14002,20 +14002,20 @@
         <x:v>drop:AV1:A3:audio:-1:S283</x:v>
       </x:c>
       <x:c r="B253" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C253" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D253" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E253" s="11" t="n">
-        <x:v>-7.703</x:v>
+        <x:v>-8.3</x:v>
       </x:c>
       <x:c r="F253" s="11" t="n">
         <x:f>SQRT((C253-C252)^2+(D253-D252)^2+(E253-E252)^2)</x:f>
-        <x:v>2.35</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="G253" s="8" t="str">
         <x:v>Current</x:v>
@@ -14023,23 +14023,23 @@
     </x:row>
     <x:row r="254" ht="32" customHeight="1">
       <x:c r="A254" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B254" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C254" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D254" s="11" t="n">
+        <x:v>5.534</x:v>
+      </x:c>
+      <x:c r="E254" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F254" s="11" t="n">
+        <x:f>0</x:f>
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D254" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E254" s="11" t="n">
-        <x:v>-7.9430000000000005</x:v>
-      </x:c>
-      <x:c r="F254" s="11" t="n">
-        <x:f>SQRT((C254-C253)^2+(D254-D253)^2+(E254-E253)^2)</x:f>
-        <x:v>0.2400000000000002</x:v>
       </x:c>
       <x:c r="G254" s="8" t="str">
         <x:v>Current</x:v>
@@ -14047,23 +14047,23 @@
     </x:row>
     <x:row r="255" ht="32" customHeight="1">
       <x:c r="A255" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B255" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C255" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D255" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E255" s="11" t="n">
-        <x:v>-7.9430000000000005</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F255" s="11" t="n">
         <x:f>SQRT((C255-C254)^2+(D255-D254)^2+(E255-E254)^2)</x:f>
-        <x:v>1.4500000000000002</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G255" s="8" t="str">
         <x:v>Current</x:v>
@@ -14071,23 +14071,23 @@
     </x:row>
     <x:row r="256" ht="32" customHeight="1">
       <x:c r="A256" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B256" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C256" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
-        <x:v>-8.3</x:v>
+        <x:v>-7.703</x:v>
       </x:c>
       <x:c r="F256" s="11" t="n">
         <x:f>SQRT((C256-C255)^2+(D256-D255)^2+(E256-E255)^2)</x:f>
-        <x:v>0.3570000000000002</x:v>
+        <x:v>0.34299999999999997</x:v>
       </x:c>
       <x:c r="G256" s="8" t="str">
         <x:v>Current</x:v>
@@ -14095,23 +14095,23 @@
     </x:row>
     <x:row r="257" ht="32" customHeight="1">
       <x:c r="A257" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S283</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B257" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C257" s="11" t="n">
-        <x:v>-0.14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D257" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E257" s="11" t="n">
-        <x:v>-8.3</x:v>
+        <x:v>-7.703</x:v>
       </x:c>
       <x:c r="F257" s="11" t="n">
         <x:f>SQRT((C257-C256)^2+(D257-D256)^2+(E257-E256)^2)</x:f>
-        <x:v>0.14</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="G257" s="8" t="str">
         <x:v>Current</x:v>
@@ -14122,20 +14122,20 @@
         <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B258" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C258" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D258" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E258" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-12.363</x:v>
       </x:c>
       <x:c r="F258" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C258-C257)^2+(D258-D257)^2+(E258-E257)^2)</x:f>
+        <x:v>4.659999999999999</x:v>
       </x:c>
       <x:c r="G258" s="8" t="str">
         <x:v>Current</x:v>
@@ -14146,20 +14146,20 @@
         <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B259" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C259" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D259" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E259" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-12.363</x:v>
       </x:c>
       <x:c r="F259" s="11" t="n">
         <x:f>SQRT((C259-C258)^2+(D259-D258)^2+(E259-E258)^2)</x:f>
-        <x:v>2.1160000000000005</x:v>
+        <x:v>1.4500000000000002</x:v>
       </x:c>
       <x:c r="G259" s="8" t="str">
         <x:v>Current</x:v>
@@ -14170,20 +14170,20 @@
         <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B260" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C260" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D260" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E260" s="11" t="n">
-        <x:v>-7.703</x:v>
+        <x:v>-11.9</x:v>
       </x:c>
       <x:c r="F260" s="11" t="n">
         <x:f>SQRT((C260-C259)^2+(D260-D259)^2+(E260-E259)^2)</x:f>
-        <x:v>0.34299999999999997</x:v>
+        <x:v>0.4629999999999992</x:v>
       </x:c>
       <x:c r="G260" s="8" t="str">
         <x:v>Current</x:v>
@@ -14194,20 +14194,20 @@
         <x:v>drop:AV1:A3:audio:-1:S284</x:v>
       </x:c>
       <x:c r="B261" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C261" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D261" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E261" s="11" t="n">
-        <x:v>-7.703</x:v>
+        <x:v>-11.9</x:v>
       </x:c>
       <x:c r="F261" s="11" t="n">
         <x:f>SQRT((C261-C260)^2+(D261-D260)^2+(E261-E260)^2)</x:f>
-        <x:v>2.35</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="G261" s="8" t="str">
         <x:v>Current</x:v>
@@ -14215,23 +14215,23 @@
     </x:row>
     <x:row r="262" ht="32" customHeight="1">
       <x:c r="A262" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B262" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C262" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="D262" s="11" t="n">
+        <x:v>5.534</x:v>
+      </x:c>
+      <x:c r="E262" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F262" s="11" t="n">
+        <x:f>0</x:f>
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D262" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E262" s="11" t="n">
-        <x:v>-12.363</x:v>
-      </x:c>
-      <x:c r="F262" s="11" t="n">
-        <x:f>SQRT((C262-C261)^2+(D262-D261)^2+(E262-E261)^2)</x:f>
-        <x:v>4.659999999999999</x:v>
       </x:c>
       <x:c r="G262" s="8" t="str">
         <x:v>Current</x:v>
@@ -14239,23 +14239,23 @@
     </x:row>
     <x:row r="263" ht="32" customHeight="1">
       <x:c r="A263" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B263" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C263" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D263" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E263" s="11" t="n">
-        <x:v>-12.363</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F263" s="11" t="n">
         <x:f>SQRT((C263-C262)^2+(D263-D262)^2+(E263-E262)^2)</x:f>
-        <x:v>1.4500000000000002</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G263" s="8" t="str">
         <x:v>Current</x:v>
@@ -14263,23 +14263,23 @@
     </x:row>
     <x:row r="264" ht="32" customHeight="1">
       <x:c r="A264" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B264" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C264" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D264" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.932586272843179</x:v>
       </x:c>
       <x:c r="E264" s="11" t="n">
-        <x:v>-11.9</x:v>
+        <x:v>-7.438307692307693</x:v>
       </x:c>
       <x:c r="F264" s="11" t="n">
         <x:f>SQRT((C264-C263)^2+(D264-D263)^2+(E264-E263)^2)</x:f>
-        <x:v>0.4629999999999992</x:v>
+        <x:v>0.13292781295227982</x:v>
       </x:c>
       <x:c r="G264" s="8" t="str">
         <x:v>Current</x:v>
@@ -14287,23 +14287,23 @@
     </x:row>
     <x:row r="265" ht="32" customHeight="1">
       <x:c r="A265" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S284</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B265" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C265" s="11" t="n">
-        <x:v>-0.14</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D265" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.270864640883978</x:v>
       </x:c>
       <x:c r="E265" s="11" t="n">
-        <x:v>-11.9</x:v>
+        <x:v>-10.414</x:v>
       </x:c>
       <x:c r="F265" s="11" t="n">
         <x:f>SQRT((C265-C264)^2+(D265-D264)^2+(E265-E264)^2)</x:f>
-        <x:v>0.14</x:v>
+        <x:v>3.048379935024818</x:v>
       </x:c>
       <x:c r="G265" s="8" t="str">
         <x:v>Current</x:v>
@@ -14314,20 +14314,20 @@
         <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B266" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C266" s="11" t="n">
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D266" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E266" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-10.414</x:v>
       </x:c>
       <x:c r="F266" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C266-C265)^2+(D266-D265)^2+(E266-E265)^2)</x:f>
+        <x:v>0.6708646408839787</x:v>
       </x:c>
       <x:c r="G266" s="8" t="str">
         <x:v>Current</x:v>
@@ -14338,20 +14338,20 @@
         <x:v>drop:AV1:A3:audio:-1:S285</x:v>
       </x:c>
       <x:c r="B267" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C267" s="11" t="n">
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D267" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E267" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-10.75</x:v>
       </x:c>
       <x:c r="F267" s="11" t="n">
         <x:f>SQRT((C267-C266)^2+(D267-D266)^2+(E267-E266)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>0.3360000000000003</x:v>
       </x:c>
       <x:c r="G267" s="8" t="str">
         <x:v>Current</x:v>
@@ -14359,23 +14359,23 @@
     </x:row>
     <x:row r="268" ht="32" customHeight="1">
       <x:c r="A268" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B268" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C268" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D268" s="11" t="n">
-        <x:v>6.932586272843179</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E268" s="11" t="n">
-        <x:v>-7.438307692307693</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F268" s="11" t="n">
-        <x:f>SQRT((C268-C267)^2+(D268-D267)^2+(E268-E267)^2)</x:f>
-        <x:v>0.13292781295227982</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="8" t="str">
         <x:v>Current</x:v>
@@ -14383,23 +14383,23 @@
     </x:row>
     <x:row r="269" ht="32" customHeight="1">
       <x:c r="A269" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B269" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C269" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D269" s="11" t="n">
-        <x:v>6.270864640883978</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E269" s="11" t="n">
-        <x:v>-10.414</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F269" s="11" t="n">
         <x:f>SQRT((C269-C268)^2+(D269-D268)^2+(E269-E268)^2)</x:f>
-        <x:v>3.048379935024818</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G269" s="8" t="str">
         <x:v>Current</x:v>
@@ -14407,23 +14407,23 @@
     </x:row>
     <x:row r="270" ht="32" customHeight="1">
       <x:c r="A270" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B270" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C270" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D270" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.932586272843179</x:v>
       </x:c>
       <x:c r="E270" s="11" t="n">
-        <x:v>-10.414</x:v>
+        <x:v>-7.438307692307693</x:v>
       </x:c>
       <x:c r="F270" s="11" t="n">
         <x:f>SQRT((C270-C269)^2+(D270-D269)^2+(E270-E269)^2)</x:f>
-        <x:v>0.6708646408839787</x:v>
+        <x:v>0.13292781295227982</x:v>
       </x:c>
       <x:c r="G270" s="8" t="str">
         <x:v>Current</x:v>
@@ -14431,23 +14431,23 @@
     </x:row>
     <x:row r="271" ht="32" customHeight="1">
       <x:c r="A271" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S285</x:v>
+        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B271" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C271" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D271" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.270864640883978</x:v>
       </x:c>
       <x:c r="E271" s="11" t="n">
-        <x:v>-10.75</x:v>
+        <x:v>-10.414</x:v>
       </x:c>
       <x:c r="F271" s="11" t="n">
         <x:f>SQRT((C271-C270)^2+(D271-D270)^2+(E271-E270)^2)</x:f>
-        <x:v>0.3360000000000003</x:v>
+        <x:v>3.048379935024818</x:v>
       </x:c>
       <x:c r="G271" s="8" t="str">
         <x:v>Current</x:v>
@@ -14458,20 +14458,20 @@
         <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B272" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C272" s="11" t="n">
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D272" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E272" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-10.414</x:v>
       </x:c>
       <x:c r="F272" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C272-C271)^2+(D272-D271)^2+(E272-E271)^2)</x:f>
+        <x:v>0.6708646408839787</x:v>
       </x:c>
       <x:c r="G272" s="8" t="str">
         <x:v>Current</x:v>
@@ -14482,20 +14482,20 @@
         <x:v>drop:AV1:A3:audio:-1:S286</x:v>
       </x:c>
       <x:c r="B273" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C273" s="11" t="n">
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D273" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E273" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-10.75</x:v>
       </x:c>
       <x:c r="F273" s="11" t="n">
         <x:f>SQRT((C273-C272)^2+(D273-D272)^2+(E273-E272)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>0.3360000000000003</x:v>
       </x:c>
       <x:c r="G273" s="8" t="str">
         <x:v>Current</x:v>
@@ -14503,23 +14503,23 @@
     </x:row>
     <x:row r="274" ht="32" customHeight="1">
       <x:c r="A274" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
+        <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B274" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C274" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D274" s="11" t="n">
-        <x:v>6.932586272843179</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E274" s="11" t="n">
-        <x:v>-7.438307692307693</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F274" s="11" t="n">
-        <x:f>SQRT((C274-C273)^2+(D274-D273)^2+(E274-E273)^2)</x:f>
-        <x:v>0.13292781295227982</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G274" s="8" t="str">
         <x:v>Current</x:v>
@@ -14527,23 +14527,23 @@
     </x:row>
     <x:row r="275" ht="32" customHeight="1">
       <x:c r="A275" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
+        <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B275" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C275" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
-        <x:v>6.270864640883978</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
-        <x:v>-10.414</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F275" s="11" t="n">
         <x:f>SQRT((C275-C274)^2+(D275-D274)^2+(E275-E274)^2)</x:f>
-        <x:v>3.048379935024818</x:v>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G275" s="8" t="str">
         <x:v>Current</x:v>
@@ -14551,23 +14551,23 @@
     </x:row>
     <x:row r="276" ht="32" customHeight="1">
       <x:c r="A276" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
+        <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B276" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C276" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D276" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E276" s="11" t="n">
-        <x:v>-10.414</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F276" s="11" t="n">
         <x:f>SQRT((C276-C275)^2+(D276-D275)^2+(E276-E275)^2)</x:f>
-        <x:v>0.6708646408839787</x:v>
+        <x:v>0.8400000000000003</x:v>
       </x:c>
       <x:c r="G276" s="8" t="str">
         <x:v>Current</x:v>
@@ -14575,23 +14575,23 @@
     </x:row>
     <x:row r="277" ht="32" customHeight="1">
       <x:c r="A277" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:-1:S286</x:v>
+        <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B277" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C277" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D277" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E277" s="11" t="n">
-        <x:v>-10.75</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="F277" s="11" t="n">
         <x:f>SQRT((C277-C276)^2+(D277-D276)^2+(E277-E276)^2)</x:f>
-        <x:v>0.3360000000000003</x:v>
+        <x:v>3.38</x:v>
       </x:c>
       <x:c r="G277" s="8" t="str">
         <x:v>Current</x:v>
@@ -14602,20 +14602,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B278" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C278" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D278" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E278" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F278" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C278-C277)^2+(D278-D277)^2+(E278-E277)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G278" s="8" t="str">
         <x:v>Current</x:v>
@@ -14626,20 +14626,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B279" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C279" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D279" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E279" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F279" s="11" t="n">
         <x:f>SQRT((C279-C278)^2+(D279-D278)^2+(E279-E278)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G279" s="8" t="str">
         <x:v>Current</x:v>
@@ -14650,20 +14650,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B280" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C280" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D280" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E280" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="F280" s="11" t="n">
         <x:f>SQRT((C280-C279)^2+(D280-D279)^2+(E280-E279)^2)</x:f>
-        <x:v>0.8400000000000003</x:v>
+        <x:v>1.2039999999999997</x:v>
       </x:c>
       <x:c r="G280" s="8" t="str">
         <x:v>Current</x:v>
@@ -14674,20 +14674,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B281" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C281" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D281" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E281" s="11" t="n">
-        <x:v>2.24</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F281" s="11" t="n">
         <x:f>SQRT((C281-C280)^2+(D281-D280)^2+(E281-E280)^2)</x:f>
-        <x:v>3.38</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G281" s="8" t="str">
         <x:v>Current</x:v>
@@ -14698,20 +14698,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B282" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C282" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D282" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E282" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F282" s="11" t="n">
         <x:f>SQRT((C282-C281)^2+(D282-D281)^2+(E282-E281)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G282" s="8" t="str">
         <x:v>Current</x:v>
@@ -14722,20 +14722,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B283" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C283" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D283" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E283" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F283" s="11" t="n">
         <x:f>SQRT((C283-C282)^2+(D283-D282)^2+(E283-E282)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G283" s="8" t="str">
         <x:v>Current</x:v>
@@ -14746,20 +14746,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B284" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C284" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D284" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E284" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F284" s="11" t="n">
         <x:f>SQRT((C284-C283)^2+(D284-D283)^2+(E284-E283)^2)</x:f>
-        <x:v>1.2039999999999997</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G284" s="8" t="str">
         <x:v>Current</x:v>
@@ -14770,20 +14770,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B285" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C285" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D285" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E285" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F285" s="11" t="n">
         <x:f>SQRT((C285-C284)^2+(D285-D284)^2+(E285-E284)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G285" s="8" t="str">
         <x:v>Current</x:v>
@@ -14794,20 +14794,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B286" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C286" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D286" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E286" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F286" s="11" t="n">
         <x:f>SQRT((C286-C285)^2+(D286-D285)^2+(E286-E285)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G286" s="8" t="str">
         <x:v>Current</x:v>
@@ -14818,20 +14818,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B287" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C287" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D287" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E287" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F287" s="11" t="n">
         <x:f>SQRT((C287-C286)^2+(D287-D286)^2+(E287-E286)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G287" s="8" t="str">
         <x:v>Current</x:v>
@@ -14842,10 +14842,10 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B288" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C288" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D288" s="11" t="n">
         <x:v>7.04</x:v>
@@ -14855,7 +14855,7 @@
       </x:c>
       <x:c r="F288" s="11" t="n">
         <x:f>SQRT((C288-C287)^2+(D288-D287)^2+(E288-E287)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G288" s="8" t="str">
         <x:v>Current</x:v>
@@ -14866,20 +14866,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B289" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C289" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D289" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E289" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F289" s="11" t="n">
         <x:f>SQRT((C289-C288)^2+(D289-D288)^2+(E289-E288)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G289" s="8" t="str">
         <x:v>Current</x:v>
@@ -14890,20 +14890,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B290" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C290" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D290" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E290" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F290" s="11" t="n">
         <x:f>SQRT((C290-C289)^2+(D290-D289)^2+(E290-E289)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G290" s="8" t="str">
         <x:v>Current</x:v>
@@ -14914,20 +14914,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B291" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C291" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D291" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E291" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F291" s="11" t="n">
         <x:f>SQRT((C291-C290)^2+(D291-D290)^2+(E291-E290)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G291" s="8" t="str">
         <x:v>Current</x:v>
@@ -14938,20 +14938,20 @@
         <x:v>trunk:AV1:A3:audio:1</x:v>
       </x:c>
       <x:c r="B292" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C292" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D292" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E292" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F292" s="11" t="n">
         <x:f>SQRT((C292-C291)^2+(D292-D291)^2+(E292-E291)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>3.1249999999999996</x:v>
       </x:c>
       <x:c r="G292" s="8" t="str">
         <x:v>Current</x:v>
@@ -14959,23 +14959,23 @@
     </x:row>
     <x:row r="293" ht="32" customHeight="1">
       <x:c r="A293" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:1</x:v>
+        <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B293" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C293" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D293" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E293" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F293" s="11" t="n">
-        <x:f>SQRT((C293-C292)^2+(D293-D292)^2+(E293-E292)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G293" s="8" t="str">
         <x:v>Current</x:v>
@@ -14983,23 +14983,23 @@
     </x:row>
     <x:row r="294" ht="32" customHeight="1">
       <x:c r="A294" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:1</x:v>
+        <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B294" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C294" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D294" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E294" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F294" s="11" t="n">
         <x:f>SQRT((C294-C293)^2+(D294-D293)^2+(E294-E293)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G294" s="8" t="str">
         <x:v>Current</x:v>
@@ -15007,23 +15007,23 @@
     </x:row>
     <x:row r="295" ht="32" customHeight="1">
       <x:c r="A295" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:1</x:v>
+        <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B295" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C295" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D295" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E295" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.703</x:v>
       </x:c>
       <x:c r="F295" s="11" t="n">
         <x:f>SQRT((C295-C294)^2+(D295-D294)^2+(E295-E294)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>0.34299999999999997</x:v>
       </x:c>
       <x:c r="G295" s="8" t="str">
         <x:v>Current</x:v>
@@ -15031,23 +15031,23 @@
     </x:row>
     <x:row r="296" ht="32" customHeight="1">
       <x:c r="A296" s="8" t="str">
-        <x:v>trunk:AV1:A3:audio:1</x:v>
+        <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B296" s="8" t="n">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C296" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D296" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E296" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.703</x:v>
       </x:c>
       <x:c r="F296" s="11" t="n">
         <x:f>SQRT((C296-C295)^2+(D296-D295)^2+(E296-E295)^2)</x:f>
-        <x:v>3.1249999999999996</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="G296" s="8" t="str">
         <x:v>Current</x:v>
@@ -15058,20 +15058,20 @@
         <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B297" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C297" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D297" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E297" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.9430000000000005</x:v>
       </x:c>
       <x:c r="F297" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C297-C296)^2+(D297-D296)^2+(E297-E296)^2)</x:f>
+        <x:v>0.2400000000000002</x:v>
       </x:c>
       <x:c r="G297" s="8" t="str">
         <x:v>Current</x:v>
@@ -15082,20 +15082,20 @@
         <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B298" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C298" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D298" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E298" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>7.9430000000000005</x:v>
       </x:c>
       <x:c r="F298" s="11" t="n">
         <x:f>SQRT((C298-C297)^2+(D298-D297)^2+(E298-E297)^2)</x:f>
-        <x:v>2.1160000000000005</x:v>
+        <x:v>1.4500000000000002</x:v>
       </x:c>
       <x:c r="G298" s="8" t="str">
         <x:v>Current</x:v>
@@ -15106,20 +15106,20 @@
         <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B299" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C299" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D299" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E299" s="11" t="n">
-        <x:v>7.703</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="F299" s="11" t="n">
         <x:f>SQRT((C299-C298)^2+(D299-D298)^2+(E299-E298)^2)</x:f>
-        <x:v>0.34299999999999997</x:v>
+        <x:v>0.3570000000000002</x:v>
       </x:c>
       <x:c r="G299" s="8" t="str">
         <x:v>Current</x:v>
@@ -15130,20 +15130,20 @@
         <x:v>drop:AV1:A3:audio:1:S287</x:v>
       </x:c>
       <x:c r="B300" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C300" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D300" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E300" s="11" t="n">
-        <x:v>7.703</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="F300" s="11" t="n">
         <x:f>SQRT((C300-C299)^2+(D300-D299)^2+(E300-E299)^2)</x:f>
-        <x:v>2.35</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="G300" s="8" t="str">
         <x:v>Current</x:v>
@@ -15151,23 +15151,23 @@
     </x:row>
     <x:row r="301" ht="32" customHeight="1">
       <x:c r="A301" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S287</x:v>
+        <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B301" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C301" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D301" s="11" t="n">
+        <x:v>5.534</x:v>
+      </x:c>
+      <x:c r="E301" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F301" s="11" t="n">
+        <x:f>0</x:f>
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D301" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E301" s="11" t="n">
-        <x:v>7.9430000000000005</x:v>
-      </x:c>
-      <x:c r="F301" s="11" t="n">
-        <x:f>SQRT((C301-C300)^2+(D301-D300)^2+(E301-E300)^2)</x:f>
-        <x:v>0.2400000000000002</x:v>
       </x:c>
       <x:c r="G301" s="8" t="str">
         <x:v>Current</x:v>
@@ -15175,23 +15175,23 @@
     </x:row>
     <x:row r="302" ht="32" customHeight="1">
       <x:c r="A302" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S287</x:v>
+        <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B302" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C302" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D302" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E302" s="11" t="n">
-        <x:v>7.9430000000000005</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F302" s="11" t="n">
         <x:f>SQRT((C302-C301)^2+(D302-D301)^2+(E302-E301)^2)</x:f>
-        <x:v>1.4500000000000002</x:v>
+        <x:v>2.1160000000000005</x:v>
       </x:c>
       <x:c r="G302" s="8" t="str">
         <x:v>Current</x:v>
@@ -15199,23 +15199,23 @@
     </x:row>
     <x:row r="303" ht="32" customHeight="1">
       <x:c r="A303" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S287</x:v>
+        <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B303" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C303" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D303" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E303" s="11" t="n">
-        <x:v>8.3</x:v>
+        <x:v>7.703</x:v>
       </x:c>
       <x:c r="F303" s="11" t="n">
         <x:f>SQRT((C303-C302)^2+(D303-D302)^2+(E303-E302)^2)</x:f>
-        <x:v>0.3570000000000002</x:v>
+        <x:v>0.34299999999999997</x:v>
       </x:c>
       <x:c r="G303" s="8" t="str">
         <x:v>Current</x:v>
@@ -15223,23 +15223,23 @@
     </x:row>
     <x:row r="304" ht="32" customHeight="1">
       <x:c r="A304" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S287</x:v>
+        <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B304" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C304" s="11" t="n">
-        <x:v>-0.14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D304" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E304" s="11" t="n">
-        <x:v>8.3</x:v>
+        <x:v>7.703</x:v>
       </x:c>
       <x:c r="F304" s="11" t="n">
         <x:f>SQRT((C304-C303)^2+(D304-D303)^2+(E304-E303)^2)</x:f>
-        <x:v>0.14</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="G304" s="8" t="str">
         <x:v>Current</x:v>
@@ -15250,20 +15250,20 @@
         <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B305" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C305" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D305" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E305" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>12.363</x:v>
       </x:c>
       <x:c r="F305" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C305-C304)^2+(D305-D304)^2+(E305-E304)^2)</x:f>
+        <x:v>4.659999999999999</x:v>
       </x:c>
       <x:c r="G305" s="8" t="str">
         <x:v>Current</x:v>
@@ -15274,20 +15274,20 @@
         <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B306" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C306" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D306" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E306" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>12.363</x:v>
       </x:c>
       <x:c r="F306" s="11" t="n">
         <x:f>SQRT((C306-C305)^2+(D306-D305)^2+(E306-E305)^2)</x:f>
-        <x:v>2.1160000000000005</x:v>
+        <x:v>1.4500000000000002</x:v>
       </x:c>
       <x:c r="G306" s="8" t="str">
         <x:v>Current</x:v>
@@ -15298,20 +15298,20 @@
         <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B307" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C307" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D307" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E307" s="11" t="n">
-        <x:v>7.703</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="F307" s="11" t="n">
         <x:f>SQRT((C307-C306)^2+(D307-D306)^2+(E307-E306)^2)</x:f>
-        <x:v>0.34299999999999997</x:v>
+        <x:v>0.4629999999999992</x:v>
       </x:c>
       <x:c r="G307" s="8" t="str">
         <x:v>Current</x:v>
@@ -15322,20 +15322,20 @@
         <x:v>drop:AV1:A3:audio:1:S288</x:v>
       </x:c>
       <x:c r="B308" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C308" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D308" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E308" s="11" t="n">
-        <x:v>7.703</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="F308" s="11" t="n">
         <x:f>SQRT((C308-C307)^2+(D308-D307)^2+(E308-E307)^2)</x:f>
-        <x:v>2.35</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="G308" s="8" t="str">
         <x:v>Current</x:v>
@@ -15343,23 +15343,23 @@
     </x:row>
     <x:row r="309" ht="32" customHeight="1">
       <x:c r="A309" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S288</x:v>
+        <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B309" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C309" s="11" t="n">
+        <x:v>18.975</x:v>
+      </x:c>
+      <x:c r="D309" s="11" t="n">
+        <x:v>5.534</x:v>
+      </x:c>
+      <x:c r="E309" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F309" s="11" t="n">
+        <x:f>0</x:f>
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D309" s="11" t="n">
-        <x:v>7.65</x:v>
-      </x:c>
-      <x:c r="E309" s="11" t="n">
-        <x:v>12.363</x:v>
-      </x:c>
-      <x:c r="F309" s="11" t="n">
-        <x:f>SQRT((C309-C308)^2+(D309-D308)^2+(E309-E308)^2)</x:f>
-        <x:v>4.659999999999999</x:v>
       </x:c>
       <x:c r="G309" s="8" t="str">
         <x:v>Current</x:v>
@@ -15367,23 +15367,23 @@
     </x:row>
     <x:row r="310" ht="32" customHeight="1">
       <x:c r="A310" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S288</x:v>
+        <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B310" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C310" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
-        <x:v>12.363</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F310" s="11" t="n">
         <x:f>SQRT((C310-C309)^2+(D310-D309)^2+(E310-E309)^2)</x:f>
-        <x:v>1.4500000000000002</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G310" s="8" t="str">
         <x:v>Current</x:v>
@@ -15391,23 +15391,23 @@
     </x:row>
     <x:row r="311" ht="32" customHeight="1">
       <x:c r="A311" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S288</x:v>
+        <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B311" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C311" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D311" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.932586272843179</x:v>
       </x:c>
       <x:c r="E311" s="11" t="n">
-        <x:v>11.9</x:v>
+        <x:v>7.438307692307693</x:v>
       </x:c>
       <x:c r="F311" s="11" t="n">
         <x:f>SQRT((C311-C310)^2+(D311-D310)^2+(E311-E310)^2)</x:f>
-        <x:v>0.4629999999999992</x:v>
+        <x:v>0.13292781295227982</x:v>
       </x:c>
       <x:c r="G311" s="8" t="str">
         <x:v>Current</x:v>
@@ -15415,23 +15415,23 @@
     </x:row>
     <x:row r="312" ht="32" customHeight="1">
       <x:c r="A312" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S288</x:v>
+        <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B312" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C312" s="11" t="n">
-        <x:v>-0.14</x:v>
+        <x:v>18.975</x:v>
       </x:c>
       <x:c r="D312" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.270864640883978</x:v>
       </x:c>
       <x:c r="E312" s="11" t="n">
-        <x:v>11.9</x:v>
+        <x:v>10.414</x:v>
       </x:c>
       <x:c r="F312" s="11" t="n">
         <x:f>SQRT((C312-C311)^2+(D312-D311)^2+(E312-E311)^2)</x:f>
-        <x:v>0.14</x:v>
+        <x:v>3.048379935024818</x:v>
       </x:c>
       <x:c r="G312" s="8" t="str">
         <x:v>Current</x:v>
@@ -15442,20 +15442,20 @@
         <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B313" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C313" s="11" t="n">
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D313" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E313" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>10.414</x:v>
       </x:c>
       <x:c r="F313" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C313-C312)^2+(D313-D312)^2+(E313-E312)^2)</x:f>
+        <x:v>0.6708646408839787</x:v>
       </x:c>
       <x:c r="G313" s="8" t="str">
         <x:v>Current</x:v>
@@ -15466,20 +15466,20 @@
         <x:v>drop:AV1:A3:audio:1:S289</x:v>
       </x:c>
       <x:c r="B314" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C314" s="11" t="n">
         <x:v>18.975</x:v>
       </x:c>
       <x:c r="D314" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E314" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F314" s="11" t="n">
         <x:f>SQRT((C314-C313)^2+(D314-D313)^2+(E314-E313)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>0.3360000000000003</x:v>
       </x:c>
       <x:c r="G314" s="8" t="str">
         <x:v>Current</x:v>
@@ -15487,23 +15487,23 @@
     </x:row>
     <x:row r="315" ht="32" customHeight="1">
       <x:c r="A315" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S289</x:v>
+        <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B315" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C315" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D315" s="11" t="n">
-        <x:v>6.932586272843179</x:v>
+        <x:v>5.534</x:v>
       </x:c>
       <x:c r="E315" s="11" t="n">
-        <x:v>7.438307692307693</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F315" s="11" t="n">
-        <x:f>SQRT((C315-C314)^2+(D315-D314)^2+(E315-E314)^2)</x:f>
-        <x:v>0.13292781295227982</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G315" s="8" t="str">
         <x:v>Current</x:v>
@@ -15511,23 +15511,23 @@
     </x:row>
     <x:row r="316" ht="32" customHeight="1">
       <x:c r="A316" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S289</x:v>
+        <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B316" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C316" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D316" s="11" t="n">
-        <x:v>6.270864640883978</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E316" s="11" t="n">
-        <x:v>10.414</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F316" s="11" t="n">
         <x:f>SQRT((C316-C315)^2+(D316-D315)^2+(E316-E315)^2)</x:f>
-        <x:v>3.048379935024818</x:v>
+        <x:v>1.5060000000000002</x:v>
       </x:c>
       <x:c r="G316" s="8" t="str">
         <x:v>Current</x:v>
@@ -15535,23 +15535,23 @@
     </x:row>
     <x:row r="317" ht="32" customHeight="1">
       <x:c r="A317" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S289</x:v>
+        <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B317" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C317" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D317" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.932586272843179</x:v>
       </x:c>
       <x:c r="E317" s="11" t="n">
-        <x:v>10.414</x:v>
+        <x:v>7.438307692307693</x:v>
       </x:c>
       <x:c r="F317" s="11" t="n">
         <x:f>SQRT((C317-C316)^2+(D317-D316)^2+(E317-E316)^2)</x:f>
-        <x:v>0.6708646408839787</x:v>
+        <x:v>0.13292781295227982</x:v>
       </x:c>
       <x:c r="G317" s="8" t="str">
         <x:v>Current</x:v>
@@ -15559,23 +15559,23 @@
     </x:row>
     <x:row r="318" ht="32" customHeight="1">
       <x:c r="A318" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S289</x:v>
+        <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B318" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C318" s="11" t="n">
-        <x:v>18.975</x:v>
+        <x:v>32.475</x:v>
       </x:c>
       <x:c r="D318" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>6.270864640883978</x:v>
       </x:c>
       <x:c r="E318" s="11" t="n">
-        <x:v>10.75</x:v>
+        <x:v>10.414</x:v>
       </x:c>
       <x:c r="F318" s="11" t="n">
         <x:f>SQRT((C318-C317)^2+(D318-D317)^2+(E318-E317)^2)</x:f>
-        <x:v>0.3360000000000003</x:v>
+        <x:v>3.048379935024818</x:v>
       </x:c>
       <x:c r="G318" s="8" t="str">
         <x:v>Current</x:v>
@@ -15586,20 +15586,20 @@
         <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B319" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C319" s="11" t="n">
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D319" s="11" t="n">
-        <x:v>5.534</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E319" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>10.414</x:v>
       </x:c>
       <x:c r="F319" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C319-C318)^2+(D319-D318)^2+(E319-E318)^2)</x:f>
+        <x:v>0.6708646408839787</x:v>
       </x:c>
       <x:c r="G319" s="8" t="str">
         <x:v>Current</x:v>
@@ -15610,20 +15610,20 @@
         <x:v>drop:AV1:A3:audio:1:S290</x:v>
       </x:c>
       <x:c r="B320" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C320" s="11" t="n">
         <x:v>32.475</x:v>
       </x:c>
       <x:c r="D320" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E320" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F320" s="11" t="n">
         <x:f>SQRT((C320-C319)^2+(D320-D319)^2+(E320-E319)^2)</x:f>
-        <x:v>1.5060000000000002</x:v>
+        <x:v>0.3360000000000003</x:v>
       </x:c>
       <x:c r="G320" s="8" t="str">
         <x:v>Current</x:v>
@@ -15631,23 +15631,23 @@
     </x:row>
     <x:row r="321" ht="32" customHeight="1">
       <x:c r="A321" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S290</x:v>
+        <x:v>trunk:AV1:MIC:mic:-1</x:v>
       </x:c>
       <x:c r="B321" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C321" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D321" s="11" t="n">
-        <x:v>6.932586272843179</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E321" s="11" t="n">
-        <x:v>7.438307692307693</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F321" s="11" t="n">
-        <x:f>SQRT((C321-C320)^2+(D321-D320)^2+(E321-E320)^2)</x:f>
-        <x:v>0.13292781295227982</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G321" s="8" t="str">
         <x:v>Current</x:v>
@@ -15655,23 +15655,23 @@
     </x:row>
     <x:row r="322" ht="32" customHeight="1">
       <x:c r="A322" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S290</x:v>
+        <x:v>trunk:AV1:MIC:mic:-1</x:v>
       </x:c>
       <x:c r="B322" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C322" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D322" s="11" t="n">
-        <x:v>6.270864640883978</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E322" s="11" t="n">
-        <x:v>10.414</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F322" s="11" t="n">
         <x:f>SQRT((C322-C321)^2+(D322-D321)^2+(E322-E321)^2)</x:f>
-        <x:v>3.048379935024818</x:v>
+        <x:v>0.9199999999999999</x:v>
       </x:c>
       <x:c r="G322" s="8" t="str">
         <x:v>Current</x:v>
@@ -15679,23 +15679,23 @@
     </x:row>
     <x:row r="323" ht="32" customHeight="1">
       <x:c r="A323" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S290</x:v>
+        <x:v>trunk:AV1:MIC:mic:-1</x:v>
       </x:c>
       <x:c r="B323" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C323" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D323" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E323" s="11" t="n">
-        <x:v>10.414</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="F323" s="11" t="n">
         <x:f>SQRT((C323-C322)^2+(D323-D322)^2+(E323-E322)^2)</x:f>
-        <x:v>0.6708646408839787</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="G323" s="8" t="str">
         <x:v>Current</x:v>
@@ -15703,23 +15703,23 @@
     </x:row>
     <x:row r="324" ht="32" customHeight="1">
       <x:c r="A324" s="8" t="str">
-        <x:v>drop:AV1:A3:audio:1:S290</x:v>
+        <x:v>trunk:AV1:MIC:mic:-1</x:v>
       </x:c>
       <x:c r="B324" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C324" s="11" t="n">
-        <x:v>32.475</x:v>
+        <x:v>41.08</x:v>
       </x:c>
       <x:c r="D324" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E324" s="11" t="n">
-        <x:v>10.75</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="F324" s="11" t="n">
         <x:f>SQRT((C324-C323)^2+(D324-D323)^2+(E324-E323)^2)</x:f>
-        <x:v>0.3360000000000003</x:v>
+        <x:v>8.195</x:v>
       </x:c>
       <x:c r="G324" s="8" t="str">
         <x:v>Current</x:v>
@@ -15727,19 +15727,19 @@
     </x:row>
     <x:row r="325" ht="32" customHeight="1">
       <x:c r="A325" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:-1</x:v>
+        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B325" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C325" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>41.08</x:v>
       </x:c>
       <x:c r="D325" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E325" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="F325" s="11" t="n">
         <x:f>0</x:f>
@@ -15751,23 +15751,23 @@
     </x:row>
     <x:row r="326" ht="32" customHeight="1">
       <x:c r="A326" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:-1</x:v>
+        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B326" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C326" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>41.08</x:v>
       </x:c>
       <x:c r="D326" s="11" t="n">
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="E326" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F326" s="11" t="n">
         <x:f>SQRT((C326-C325)^2+(D326-D325)^2+(E326-E325)^2)</x:f>
-        <x:v>0.9199999999999999</x:v>
+        <x:v>1.2200000000000002</x:v>
       </x:c>
       <x:c r="G326" s="8" t="str">
         <x:v>Current</x:v>
@@ -15775,23 +15775,23 @@
     </x:row>
     <x:row r="327" ht="32" customHeight="1">
       <x:c r="A327" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:-1</x:v>
+        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B327" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C327" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>41.3</x:v>
       </x:c>
       <x:c r="D327" s="11" t="n">
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="E327" s="11" t="n">
-        <x:v>-1.4</x:v>
+        <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F327" s="11" t="n">
         <x:f>SQRT((C327-C326)^2+(D327-D326)^2+(E327-E326)^2)</x:f>
-        <x:v>2.8</x:v>
+        <x:v>0.21999999999999886</x:v>
       </x:c>
       <x:c r="G327" s="8" t="str">
         <x:v>Current</x:v>
@@ -15799,23 +15799,23 @@
     </x:row>
     <x:row r="328" ht="32" customHeight="1">
       <x:c r="A328" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:-1</x:v>
+        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B328" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C328" s="11" t="n">
-        <x:v>41.08</x:v>
+        <x:v>41.3</x:v>
       </x:c>
       <x:c r="D328" s="11" t="n">
-        <x:v>0.03</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="E328" s="11" t="n">
-        <x:v>-1.4</x:v>
+        <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F328" s="11" t="n">
         <x:f>SQRT((C328-C327)^2+(D328-D327)^2+(E328-E327)^2)</x:f>
-        <x:v>8.195</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="G328" s="8" t="str">
         <x:v>Current</x:v>
@@ -15826,20 +15826,20 @@
         <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B329" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C329" s="11" t="n">
         <x:v>41.08</x:v>
       </x:c>
       <x:c r="D329" s="11" t="n">
-        <x:v>0.03</x:v>
+        <x:v>1.8154037921880923</x:v>
       </x:c>
       <x:c r="E329" s="11" t="n">
-        <x:v>-1.4</x:v>
+        <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F329" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C329-C328)^2+(D329-D328)^2+(E329-E328)^2)</x:f>
+        <x:v>0.22447454588706126</x:v>
       </x:c>
       <x:c r="G329" s="8" t="str">
         <x:v>Current</x:v>
@@ -15850,20 +15850,20 @@
         <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
       </x:c>
       <x:c r="B330" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C330" s="11" t="n">
         <x:v>41.08</x:v>
       </x:c>
       <x:c r="D330" s="11" t="n">
-        <x:v>0.03</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E330" s="11" t="n">
         <x:v>-2.62</x:v>
       </x:c>
       <x:c r="F330" s="11" t="n">
         <x:f>SQRT((C330-C329)^2+(D330-D329)^2+(E330-E329)^2)</x:f>
-        <x:v>1.2200000000000002</x:v>
+        <x:v>0.13459620781190762</x:v>
       </x:c>
       <x:c r="G330" s="8" t="str">
         <x:v>Current</x:v>
@@ -15871,23 +15871,23 @@
     </x:row>
     <x:row r="331" ht="32" customHeight="1">
       <x:c r="A331" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
+        <x:v>trunk:AV1:MIC:mic:1</x:v>
       </x:c>
       <x:c r="B331" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C331" s="11" t="n">
-        <x:v>41.3</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D331" s="11" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E331" s="11" t="n">
-        <x:v>-2.62</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F331" s="11" t="n">
-        <x:f>SQRT((C331-C330)^2+(D331-D330)^2+(E331-E330)^2)</x:f>
-        <x:v>0.21999999999999886</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G331" s="8" t="str">
         <x:v>Current</x:v>
@@ -15895,23 +15895,23 @@
     </x:row>
     <x:row r="332" ht="32" customHeight="1">
       <x:c r="A332" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
+        <x:v>trunk:AV1:MIC:mic:1</x:v>
       </x:c>
       <x:c r="B332" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C332" s="11" t="n">
-        <x:v>41.3</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D332" s="11" t="n">
-        <x:v>1.86</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E332" s="11" t="n">
-        <x:v>-2.62</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F332" s="11" t="n">
         <x:f>SQRT((C332-C331)^2+(D332-D331)^2+(E332-E331)^2)</x:f>
-        <x:v>1.83</x:v>
+        <x:v>0.9199999999999999</x:v>
       </x:c>
       <x:c r="G332" s="8" t="str">
         <x:v>Current</x:v>
@@ -15919,23 +15919,23 @@
     </x:row>
     <x:row r="333" ht="32" customHeight="1">
       <x:c r="A333" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
+        <x:v>trunk:AV1:MIC:mic:1</x:v>
       </x:c>
       <x:c r="B333" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C333" s="11" t="n">
-        <x:v>41.08</x:v>
+        <x:v>44.45</x:v>
       </x:c>
       <x:c r="D333" s="11" t="n">
-        <x:v>1.8154037921880923</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E333" s="11" t="n">
-        <x:v>-2.62</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F333" s="11" t="n">
         <x:f>SQRT((C333-C332)^2+(D333-D332)^2+(E333-E332)^2)</x:f>
-        <x:v>0.22447454588706126</x:v>
+        <x:v>4.824999999999996</x:v>
       </x:c>
       <x:c r="G333" s="8" t="str">
         <x:v>Current</x:v>
@@ -15943,23 +15943,23 @@
     </x:row>
     <x:row r="334" ht="32" customHeight="1">
       <x:c r="A334" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:-1:S291</x:v>
+        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
       </x:c>
       <x:c r="B334" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C334" s="11" t="n">
-        <x:v>41.08</x:v>
+        <x:v>44.45</x:v>
       </x:c>
       <x:c r="D334" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="E334" s="11" t="n">
-        <x:v>-2.62</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F334" s="11" t="n">
-        <x:f>SQRT((C334-C333)^2+(D334-D333)^2+(E334-E333)^2)</x:f>
-        <x:v>0.13459620781190762</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G334" s="8" t="str">
         <x:v>Current</x:v>
@@ -15967,167 +15967,167 @@
     </x:row>
     <x:row r="335" ht="32" customHeight="1">
       <x:c r="A335" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:1</x:v>
+        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
       </x:c>
       <x:c r="B335" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C335" s="11" t="n">
+        <x:v>44.45</x:v>
+      </x:c>
+      <x:c r="D335" s="11" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="E335" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="F335" s="11" t="n">
+        <x:f>SQRT((C335-C334)^2+(D335-D334)^2+(E335-E334)^2)</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="G335" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="32" customHeight="1">
+      <x:c r="A336" s="8" t="str">
+        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
+      </x:c>
+      <x:c r="B336" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C336" s="11" t="n">
+        <x:v>44.45</x:v>
+      </x:c>
+      <x:c r="D336" s="11" t="n">
+        <x:v>1.93</x:v>
+      </x:c>
+      <x:c r="E336" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="F336" s="11" t="n">
+        <x:f>SQRT((C336-C335)^2+(D336-D335)^2+(E336-E335)^2)</x:f>
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="G336" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="32" customHeight="1">
+      <x:c r="A337" s="8" t="str">
+        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
+      </x:c>
+      <x:c r="B337" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C335" s="11" t="n">
-        <x:v>49.275</x:v>
-      </x:c>
-      <x:c r="D335" s="11" t="n">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="E335" s="11" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="F335" s="11" t="n">
+      <x:c r="C337" s="11" t="n">
+        <x:v>38.94</x:v>
+      </x:c>
+      <x:c r="D337" s="11" t="n">
+        <x:v>7.953150773195872</x:v>
+      </x:c>
+      <x:c r="E337" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F337" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G335" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="336" ht="32" customHeight="1">
-      <x:c r="A336" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:1</x:v>
-      </x:c>
-      <x:c r="B336" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C336" s="11" t="n">
-        <x:v>49.275</x:v>
-      </x:c>
-      <x:c r="D336" s="11" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="E336" s="11" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="F336" s="11" t="n">
-        <x:f>SQRT((C336-C335)^2+(D336-D335)^2+(E336-E335)^2)</x:f>
-        <x:v>0.9199999999999999</x:v>
-      </x:c>
-      <x:c r="G336" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="337" ht="32" customHeight="1">
-      <x:c r="A337" s="8" t="str">
-        <x:v>trunk:AV1:MIC:mic:1</x:v>
-      </x:c>
-      <x:c r="B337" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C337" s="11" t="n">
-        <x:v>44.45</x:v>
-      </x:c>
-      <x:c r="D337" s="11" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="E337" s="11" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="F337" s="11" t="n">
-        <x:f>SQRT((C337-C336)^2+(D337-D336)^2+(E337-E336)^2)</x:f>
-        <x:v>4.824999999999996</x:v>
-      </x:c>
       <x:c r="G337" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="32" customHeight="1">
       <x:c r="A338" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
+        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
       </x:c>
       <x:c r="B338" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C338" s="11" t="n">
+        <x:v>38.94</x:v>
+      </x:c>
+      <x:c r="D338" s="11" t="n">
+        <x:v>7.953150773195873</x:v>
+      </x:c>
+      <x:c r="E338" s="11" t="n">
+        <x:v>-11.6</x:v>
+      </x:c>
+      <x:c r="F338" s="11" t="n">
+        <x:f>SQRT((C338-C337)^2+(D338-D337)^2+(E338-E337)^2)</x:f>
+        <x:v>4.239999999999999</x:v>
+      </x:c>
+      <x:c r="G338" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="32" customHeight="1">
+      <x:c r="A339" s="8" t="str">
+        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
+      </x:c>
+      <x:c r="B339" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C339" s="11" t="n">
+        <x:v>38.94</x:v>
+      </x:c>
+      <x:c r="D339" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E339" s="11" t="n">
+        <x:v>-11.6</x:v>
+      </x:c>
+      <x:c r="F339" s="11" t="n">
+        <x:f>SQRT((C339-C338)^2+(D339-D338)^2+(E339-E338)^2)</x:f>
+        <x:v>4.953150773195873</x:v>
+      </x:c>
+      <x:c r="G339" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="32" customHeight="1">
+      <x:c r="A340" s="8" t="str">
+        <x:v>drop:AV1:A1:audio:1:S277</x:v>
+      </x:c>
+      <x:c r="B340" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C338" s="11" t="n">
-        <x:v>44.45</x:v>
-      </x:c>
-      <x:c r="D338" s="11" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="E338" s="11" t="n">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="F338" s="11" t="n">
+      <x:c r="C340" s="11" t="n">
+        <x:v>38.94</x:v>
+      </x:c>
+      <x:c r="D340" s="11" t="n">
+        <x:v>7.953150773195872</x:v>
+      </x:c>
+      <x:c r="E340" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F340" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G338" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="339" ht="32" customHeight="1">
-      <x:c r="A339" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
-      </x:c>
-      <x:c r="B339" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C339" s="11" t="n">
-        <x:v>44.45</x:v>
-      </x:c>
-      <x:c r="D339" s="11" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="E339" s="11" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="F339" s="11" t="n">
-        <x:f>SQRT((C339-C338)^2+(D339-D338)^2+(E339-E338)^2)</x:f>
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="G339" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="340" ht="32" customHeight="1">
-      <x:c r="A340" s="8" t="str">
-        <x:v>drop:AV1:MIC:mic:1:S292</x:v>
-      </x:c>
-      <x:c r="B340" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C340" s="11" t="n">
-        <x:v>44.45</x:v>
-      </x:c>
-      <x:c r="D340" s="11" t="n">
-        <x:v>1.93</x:v>
-      </x:c>
-      <x:c r="E340" s="11" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="F340" s="11" t="n">
-        <x:f>SQRT((C340-C339)^2+(D340-D339)^2+(E340-E339)^2)</x:f>
-        <x:v>1.9</x:v>
-      </x:c>
       <x:c r="G340" s="8" t="str">
-        <x:v>Current</x:v>
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="32" customHeight="1">
       <x:c r="A341" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
+        <x:v>drop:AV1:A1:audio:1:S277</x:v>
       </x:c>
       <x:c r="B341" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C341" s="11" t="n">
         <x:v>38.94</x:v>
       </x:c>
       <x:c r="D341" s="11" t="n">
-        <x:v>7.953150773195872</x:v>
+        <x:v>7.953150773195873</x:v>
       </x:c>
       <x:c r="E341" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="F341" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C341-C340)^2+(D341-D340)^2+(E341-E340)^2)</x:f>
+        <x:v>4.239999999999999</x:v>
       </x:c>
       <x:c r="G341" s="8" t="str">
         <x:v>Retired</x:v>
@@ -16135,131 +16135,35 @@
     </x:row>
     <x:row r="342" ht="32" customHeight="1">
       <x:c r="A342" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
+        <x:v>drop:AV1:A1:audio:1:S277</x:v>
       </x:c>
       <x:c r="B342" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C342" s="11" t="n">
         <x:v>38.94</x:v>
       </x:c>
       <x:c r="D342" s="11" t="n">
-        <x:v>7.953150773195873</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E342" s="11" t="n">
-        <x:v>-11.6</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="F342" s="11" t="n">
         <x:f>SQRT((C342-C341)^2+(D342-D341)^2+(E342-E341)^2)</x:f>
-        <x:v>4.239999999999999</x:v>
+        <x:v>4.953150773195873</x:v>
       </x:c>
       <x:c r="G342" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
-    <x:row r="343" ht="32" customHeight="1">
-      <x:c r="A343" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:-1:S275</x:v>
-      </x:c>
-      <x:c r="B343" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C343" s="11" t="n">
-        <x:v>38.94</x:v>
-      </x:c>
-      <x:c r="D343" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E343" s="11" t="n">
-        <x:v>-11.6</x:v>
-      </x:c>
-      <x:c r="F343" s="11" t="n">
-        <x:f>SQRT((C343-C342)^2+(D343-D342)^2+(E343-E342)^2)</x:f>
-        <x:v>4.953150773195873</x:v>
-      </x:c>
-      <x:c r="G343" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="344" ht="32" customHeight="1">
-      <x:c r="A344" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:1:S277</x:v>
-      </x:c>
-      <x:c r="B344" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C344" s="11" t="n">
-        <x:v>38.94</x:v>
-      </x:c>
-      <x:c r="D344" s="11" t="n">
-        <x:v>7.953150773195872</x:v>
-      </x:c>
-      <x:c r="E344" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F344" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G344" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="345" ht="32" customHeight="1">
-      <x:c r="A345" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:1:S277</x:v>
-      </x:c>
-      <x:c r="B345" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C345" s="11" t="n">
-        <x:v>38.94</x:v>
-      </x:c>
-      <x:c r="D345" s="11" t="n">
-        <x:v>7.953150773195873</x:v>
-      </x:c>
-      <x:c r="E345" s="11" t="n">
-        <x:v>11.6</x:v>
-      </x:c>
-      <x:c r="F345" s="11" t="n">
-        <x:f>SQRT((C345-C344)^2+(D345-D344)^2+(E345-E344)^2)</x:f>
-        <x:v>4.239999999999999</x:v>
-      </x:c>
-      <x:c r="G345" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="346" ht="32" customHeight="1">
-      <x:c r="A346" s="8" t="str">
-        <x:v>drop:AV1:A1:audio:1:S277</x:v>
-      </x:c>
-      <x:c r="B346" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C346" s="11" t="n">
-        <x:v>38.94</x:v>
-      </x:c>
-      <x:c r="D346" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E346" s="11" t="n">
-        <x:v>11.6</x:v>
-      </x:c>
-      <x:c r="F346" s="11" t="n">
-        <x:f>SQRT((C346-C345)^2+(D346-D345)^2+(E346-E345)^2)</x:f>
-        <x:v>4.953150773195873</x:v>
-      </x:c>
-      <x:c r="G346" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G346">
+  <x:conditionalFormatting sqref="G7:G342">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a26321aa8540a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re758098a59ce4ae0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/sound/register.xlsx
+++ b/docs/electrical-grid/categories/sound/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Reca08c413dd04e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfcb16dca04994202"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R07baf9e066c64a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4c2b369a09ee4eda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4ee88fdd4ffc4dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Red6d26e8b80045fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra0950f0142744a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R771a3c4b9e004696"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Sound. Loudspeakers, microphones, indoor speech and outdoor overflow. Model snapshot: 2026-11-01T01:42:20.339Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>50118e5af402ff0efaabf2d570ac3f0129d03efc89e10e7eeb51b8d67485750c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>0fb0ba42a427dbbe355fa325c0efcf0641bfb0dae62bd4f360bc65584cfd7d81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -4149,7 +4149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R731da90b58ad4877"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1305c568654a7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7999,7 +7999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e256f0ae5740c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc61ed3dd48ad4b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16259,7 +16259,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a26321aa8540a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4050bb7742eb4640"/>
   </x:tableParts>
 </x:worksheet>
 </file>